--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -493,10 +493,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Validator</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B12" t="str">
-        <v>ICC 프로파일 검증기</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="13">
@@ -629,10 +629,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Validator · powered by IccProfLib</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B29" t="str">
-        <v>ICC 프로파일 검증기 · IccProfLib 기반</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="30">

--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B69"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -643,9 +643,321 @@
         <v>오류:</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B31" t="str">
+        <v>XML로 변환</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B32" t="str">
+        <v>JSON으로 변환</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B33" t="str">
+        <v>ICC로 변환</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B34" t="str">
+        <v>XML로 변환 중…</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B35" t="str">
+        <v>JSON으로 변환 중…</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B36" t="str">
+        <v>ICC로 변환 중…</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B37" t="str">
+        <v>ICC 프로파일 로드</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B38" t="str">
+        <v>ICC 프로파일 파일용 드롭 영역</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B39" t="str">
+        <v>프로파일 ID</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B40" t="str">
+        <v>태그를 찾을 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B41" t="str">
+        <v>태그 이름</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B42" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B43" t="str">
+        <v>오프셋</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B44" t="str">
+        <v>크기</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B45" t="str">
+        <v>패딩</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B46" t="str">
+        <v>로드 이후 바이트가 변경됨</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B47" t="str">
+        <v>유형</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B48" t="str">
+        <v>{type} 배열</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B49" t="str">
+        <v>(내용 없음)</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B50" t="str">
+        <v>바이트</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B51" t="str">
+        <v>전체 설명을 로드하는 중…</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B52" t="str">
+        <v>전체 설명을 로드할 수 없습니다:</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B53" t="str">
+        <v>검증 출력 없음</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B54" t="str">
+        <v>경고나 오류를 찾지 못했습니다.</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B55" t="str">
+        <v>유효</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B56" t="str">
+        <v>경고</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B57" t="str">
+        <v>오류</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B58" t="str">
+        <v>알 수 없음</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B59" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B60" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B61" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B62" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B63" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B64" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B65" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B66" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B67" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B68" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Profile written from edits, but re-validation failed:</v>
+      </c>
+      <c r="B69" t="str">
+        <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B79"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -869,95 +869,175 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B59" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B60" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B61" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B62" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B63" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B64" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B65" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B66" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B67" t="str">
-        <v>들여쓰기</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B68" t="str">
-        <v>키 정렬</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B69" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B70" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B71" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B72" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B73" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B74" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B75" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B76" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B77" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B78" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B69" t="str">
+      <c r="B79" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B79"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B81"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -821,223 +821,239 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B53" t="str">
-        <v>검증 출력 없음</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B54" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B55" t="str">
-        <v>유효</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B56" t="str">
-        <v>경고</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B57" t="str">
-        <v>오류</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B58" t="str">
-        <v>알 수 없음</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B59" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B60" t="str">
-        <v>검증 세부 정보</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B61" t="str">
-        <v>트리거 항목</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B62" t="str">
-        <v>항목</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B63" t="str">
-        <v>현재 값</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B64" t="str">
-        <v>필수: 0</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B65" t="str">
-        <v>예상: {value}</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B66" t="str">
-        <v>잘못됨</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B67" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B68" t="str">
-        <v>닫기</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B69" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B70" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B71" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B72" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B73" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B74" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B75" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B76" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B77" t="str">
-        <v>들여쓰기</v>
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B78" t="str">
-        <v>키 정렬</v>
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B79" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B80" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B79" t="str">
+      <c r="B81" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B81"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B87"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -845,215 +845,263 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B56" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B57" t="str">
-        <v>유효</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Warning</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B58" t="str">
-        <v>경고</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Error</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B59" t="str">
-        <v>오류</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B60" t="str">
-        <v>알 수 없음</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B61" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B62" t="str">
-        <v>검증 세부 정보</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B63" t="str">
-        <v>트리거 항목</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B64" t="str">
-        <v>항목</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B65" t="str">
-        <v>현재 값</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B66" t="str">
-        <v>필수: 0</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Expected: {value}</v>
+        <v>View in context</v>
       </c>
       <c r="B67" t="str">
-        <v>예상: {value}</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Invalid</v>
+        <v>Validation detail</v>
       </c>
       <c r="B68" t="str">
-        <v>잘못됨</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Triggered by</v>
       </c>
       <c r="B69" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Close</v>
+        <v>Field</v>
       </c>
       <c r="B70" t="str">
-        <v>닫기</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Loading XML editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B71" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B72" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B73" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B74" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>● unsaved XML edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B75" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Close</v>
       </c>
       <c r="B76" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B77" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B78" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>indent</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B79" t="str">
-        <v>들여쓰기</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B80" t="str">
-        <v>키 정렬</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B81" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B82" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B83" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B84" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B85" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B86" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B81" t="str">
+      <c r="B87" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B87"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B98"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -605,503 +605,591 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Raw Output</v>
+        <v>Profile Assessment WG</v>
       </c>
       <c r="B26" t="str">
-        <v>원시 출력</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B27" t="str">
-        <v>XML</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>JSON</v>
       </c>
       <c r="B29" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Error:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B30" t="str">
-        <v>오류:</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Convert to XML</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B31" t="str">
-        <v>XML로 변환</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Convert to JSON</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B32" t="str">
-        <v>JSON으로 변환</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Convert to ICC</v>
+        <v>Security</v>
       </c>
       <c r="B33" t="str">
-        <v>ICC로 변환</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Converting to XML…</v>
+        <v>Conformance</v>
       </c>
       <c r="B34" t="str">
-        <v>XML로 변환 중…</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Converting to JSON…</v>
+        <v>Quality</v>
       </c>
       <c r="B35" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Converting to ICC…</v>
+        <v>REPORT</v>
       </c>
       <c r="B36" t="str">
-        <v>ICC로 변환 중…</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Load ICC profile</v>
+        <v>FAIL</v>
       </c>
       <c r="B37" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>checks</v>
       </c>
       <c r="B38" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Profile ID</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B39" t="str">
-        <v>프로파일 ID</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B40" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B41" t="str">
-        <v>태그 이름</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B42" t="str">
-        <v>ID</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B43" t="str">
-        <v>오프셋</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B44" t="str">
-        <v>크기</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B45" t="str">
-        <v>패딩</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B46" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B47" t="str">
-        <v>유형</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B48" t="str">
-        <v>{type} 배열</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B49" t="str">
-        <v>(내용 없음)</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B50" t="str">
-        <v>바이트</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B51" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B52" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B53" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B54" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B55" t="str">
-        <v>검증 출력 없음</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B56" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B57" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B58" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B59" t="str">
-        <v>심각한 검증 오류</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B60" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B61" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B62" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B63" t="str">
-        <v>유효</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B64" t="str">
-        <v>경고</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B65" t="str">
-        <v>오류</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B66" t="str">
-        <v>알 수 없음</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B67" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B68" t="str">
-        <v>검증 세부 정보</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B69" t="str">
-        <v>트리거 항목</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B70" t="str">
-        <v>항목</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B71" t="str">
-        <v>현재 값</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B72" t="str">
-        <v>필수: 0</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B73" t="str">
-        <v>예상: {value}</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B74" t="str">
-        <v>잘못됨</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B75" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B76" t="str">
-        <v>닫기</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B77" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B78" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B79" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B80" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B81" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B82" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B83" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B84" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B85" t="str">
-        <v>들여쓰기</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B86" t="str">
-        <v>키 정렬</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B87" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B88" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B89" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B90" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B91" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B92" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B93" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B94" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B95" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B96" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B97" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B87" t="str">
+      <c r="B98" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B100"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -637,23 +637,23 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -661,7 +661,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Security</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -669,7 +669,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Conformance</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -677,7 +677,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Quality</v>
+        <v>Security</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -685,7 +685,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>REPORT</v>
+        <v>Conformance</v>
       </c>
       <c r="B36" t="str">
         <v/>
@@ -693,7 +693,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FAIL</v>
+        <v>Quality</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -701,7 +701,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -709,7 +709,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B39" t="str">
         <v/>
@@ -717,479 +717,495 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B40" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Error:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B41" t="str">
-        <v>오류:</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Convert to XML</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B42" t="str">
-        <v>XML로 변환</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B43" t="str">
-        <v>JSON으로 변환</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B44" t="str">
-        <v>ICC로 변환</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B45" t="str">
-        <v>XML로 변환 중…</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B46" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B47" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B48" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B49" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B50" t="str">
-        <v>프로파일 ID</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B51" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B52" t="str">
-        <v>태그 이름</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B53" t="str">
-        <v>ID</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B54" t="str">
-        <v>오프셋</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B55" t="str">
-        <v>크기</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B56" t="str">
-        <v>패딩</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B57" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B58" t="str">
-        <v>유형</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B59" t="str">
-        <v>{type} 배열</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B60" t="str">
-        <v>(내용 없음)</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B61" t="str">
-        <v>바이트</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B62" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B63" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B64" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B65" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B66" t="str">
-        <v>검증 출력 없음</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B67" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B68" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B69" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B70" t="str">
-        <v>심각한 검증 오류</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B71" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B72" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B73" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B74" t="str">
-        <v>유효</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B75" t="str">
-        <v>경고</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B76" t="str">
-        <v>오류</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B77" t="str">
-        <v>알 수 없음</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B78" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B79" t="str">
-        <v>검증 세부 정보</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B80" t="str">
-        <v>트리거 항목</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B81" t="str">
-        <v>항목</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B82" t="str">
-        <v>현재 값</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B83" t="str">
-        <v>필수: 0</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B84" t="str">
-        <v>예상: {value}</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B85" t="str">
-        <v>잘못됨</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B86" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B87" t="str">
-        <v>닫기</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B88" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B89" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B90" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B91" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B92" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B93" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B94" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B95" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B96" t="str">
-        <v>들여쓰기</v>
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B97" t="str">
-        <v>키 정렬</v>
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B98" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B99" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B100" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B129"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -517,695 +517,927 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>reference implementation.</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B15" t="str">
-        <v>참조 구현으로 검증합니다.</v>
+        <v>데모 구현으로 검증합니다.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Validating…</v>
+        <v>Based on</v>
       </c>
       <c r="B16" t="str">
-        <v>검증 중…</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Save ICC profile</v>
+        <v>demo implementation</v>
       </c>
       <c r="B17" t="str">
-        <v>ICC 프로파일 저장</v>
+        <v>데모 구현 기반</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Validating…</v>
       </c>
       <c r="B18" t="str">
-        <v>● 변경됨 — 저장되지 않음</v>
+        <v>검증 중…</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B19" t="str">
-        <v>ICC 프로파일을 여기에 놓기</v>
+        <v>ICC 프로파일 저장</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>or</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B20" t="str">
-        <v>또는</v>
+        <v>● 변경됨 — 저장되지 않음</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Choose file</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B21" t="str">
-        <v>파일 선택</v>
+        <v>ICC 프로파일을 여기에 놓기</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>.icc and .icm files</v>
+        <v>or</v>
       </c>
       <c r="B22" t="str">
-        <v>.icc 및 .icm 파일</v>
+        <v>또는</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Header</v>
+        <v>Choose file</v>
       </c>
       <c r="B23" t="str">
-        <v>헤더</v>
+        <v>파일 선택</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Tags</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B24" t="str">
-        <v>태그</v>
+        <v>.icc 및 .icm 파일</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Validation</v>
+        <v>Header</v>
       </c>
       <c r="B25" t="str">
-        <v>검증</v>
+        <v>헤더</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Profile Assessment WG</v>
+        <v>Tags</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>태그</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Raw Output</v>
+        <v>Validation</v>
       </c>
       <c r="B27" t="str">
-        <v>원시 출력</v>
+        <v>검증</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>XML</v>
+        <v>Plot</v>
       </c>
       <c r="B28" t="str">
-        <v>XML</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>JSON</v>
+        <v>Raw Output</v>
       </c>
       <c r="B29" t="str">
-        <v>JSON</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Invalid profile URL:</v>
+        <v>XML</v>
       </c>
       <c r="B30" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>JSON</v>
       </c>
       <c r="B31" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Curves</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>곡선</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Input curves</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Output curves</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Security</v>
+        <v>CLUT image</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Conformance</v>
+        <v>Gamut image</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Quality</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>색도</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>REPORT</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>산점도</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>FAIL</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>checks</v>
+        <v>Curve table</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Tables</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>표</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Data</v>
       </c>
       <c r="B42" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Error:</v>
+        <v>Evaluate</v>
       </c>
       <c r="B43" t="str">
-        <v>오류:</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to XML</v>
+        <v>Loading…</v>
       </c>
       <c r="B44" t="str">
-        <v>XML로 변환</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Convert to JSON</v>
+        <v>Input</v>
       </c>
       <c r="B45" t="str">
-        <v>JSON으로 변환</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Convert to ICC</v>
+        <v>Output</v>
       </c>
       <c r="B46" t="str">
-        <v>ICC로 변환</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to XML…</v>
+        <v>Floating point</v>
       </c>
       <c r="B47" t="str">
-        <v>XML로 변환 중…</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Converting to JSON…</v>
+        <v>Grid point</v>
       </c>
       <c r="B48" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Converting to ICC…</v>
+        <v>Normalized</v>
       </c>
       <c r="B49" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Load ICC profile</v>
+        <v>Human</v>
       </c>
       <c r="B50" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B51" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Profile ID</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B52" t="str">
-        <v>프로파일 ID</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No tags found.</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B53" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag Name</v>
+        <v>Loading…</v>
       </c>
       <c r="B54" t="str">
-        <v>태그 이름</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ID</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B55" t="str">
-        <v>ID</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Offset</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B56" t="str">
-        <v>오프셋</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Size</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B57" t="str">
-        <v>크기</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Pad</v>
+        <v>Loading plot module…</v>
       </c>
       <c r="B58" t="str">
-        <v>패딩</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bytes changed since load</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B59" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Type</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B60" t="str">
-        <v>유형</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Array of {type}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B61" t="str">
-        <v>{type} 배열</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>(No content)</v>
+        <v>Security</v>
       </c>
       <c r="B62" t="str">
-        <v>(내용 없음)</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>bytes</v>
+        <v>Conformance</v>
       </c>
       <c r="B63" t="str">
-        <v>바이트</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Loading full description…</v>
+        <v>Quality</v>
       </c>
       <c r="B64" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Could not load full description:</v>
+        <v>REPORT</v>
       </c>
       <c r="B65" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>FAIL</v>
       </c>
       <c r="B66" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>checks</v>
       </c>
       <c r="B67" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No validation output</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B68" t="str">
-        <v>검증 출력 없음</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is valid</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B69" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Error:</v>
       </c>
       <c r="B70" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B71" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical validation error</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B72" t="str">
-        <v>심각한 검증 오류</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Unknown validation status</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B73" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B74" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B75" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B76" t="str">
-        <v>유효</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Warning</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B77" t="str">
-        <v>경고</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Error</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B78" t="str">
-        <v>오류</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Unknown</v>
+        <v>Profile ID</v>
       </c>
       <c r="B79" t="str">
-        <v>알 수 없음</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>View in context</v>
+        <v>No tags found.</v>
       </c>
       <c r="B80" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Validation detail</v>
+        <v>Tag Name</v>
       </c>
       <c r="B81" t="str">
-        <v>검증 세부 정보</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Triggered by</v>
+        <v>ID</v>
       </c>
       <c r="B82" t="str">
-        <v>트리거 항목</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Field</v>
+        <v>Offset</v>
       </c>
       <c r="B83" t="str">
-        <v>항목</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Current value</v>
+        <v>Size</v>
       </c>
       <c r="B84" t="str">
-        <v>현재 값</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Required: 0</v>
+        <v>Pad</v>
       </c>
       <c r="B85" t="str">
-        <v>필수: 0</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Expected: {value}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B86" t="str">
-        <v>예상: {value}</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Invalid</v>
+        <v>Type</v>
       </c>
       <c r="B87" t="str">
-        <v>잘못됨</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B88" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Close</v>
+        <v>(No content)</v>
       </c>
       <c r="B89" t="str">
-        <v>닫기</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading XML editor…</v>
+        <v>bytes</v>
       </c>
       <c r="B90" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B91" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B92" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B93" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B94" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>No validation output</v>
       </c>
       <c r="B95" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B96" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B97" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>indent</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B98" t="str">
-        <v>들여쓰기</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>sort keys</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B99" t="str">
-        <v>키 정렬</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B100" t="str">
+        <v>알 수 없는 검증 상태</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B101" t="str">
+        <v>심각 — 검사용으로만 표시</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B102" t="str">
+        <v>경고나 오류를 찾지 못했습니다.</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B103" t="str">
+        <v>유효</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B104" t="str">
+        <v>경고</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B105" t="str">
+        <v>오류</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B106" t="str">
+        <v>알 수 없음</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B107" t="str">
+        <v>통과</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B108" t="str">
+        <v>실패</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B109" t="str">
+        <v>컨텍스트에서 보기</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B110" t="str">
+        <v>검증 세부 정보</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B111" t="str">
+        <v>트리거 항목</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B112" t="str">
+        <v>항목</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B113" t="str">
+        <v>현재 값</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B114" t="str">
+        <v>필수: 0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B115" t="str">
+        <v>예상: {value}</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B116" t="str">
+        <v>잘못됨</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B117" t="str">
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B118" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B119" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B120" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B121" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B122" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B123" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B124" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B125" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B126" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B127" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B128" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B129" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B129"/>
+  <dimension ref="A1:B128"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -861,583 +861,575 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading plot module…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Security</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>보안</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Security</v>
+        <v>Conformance</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>적합성</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Conformance</v>
+        <v>Quality</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>품질</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Quality</v>
+        <v>REPORT</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>보고서</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>REPORT</v>
+        <v>FAIL</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>실패</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>FAIL</v>
+        <v>checks</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>checks</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Error:</v>
       </c>
       <c r="B69" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Error:</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B70" t="str">
-        <v>오류:</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to XML</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B71" t="str">
-        <v>XML로 변환</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B72" t="str">
-        <v>JSON으로 변환</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B73" t="str">
-        <v>ICC로 변환</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to XML…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B74" t="str">
-        <v>XML로 변환 중…</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B75" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to ICC…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B76" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Load ICC profile</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B77" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Profile ID</v>
       </c>
       <c r="B78" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Profile ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B79" t="str">
-        <v>프로파일 ID</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>No tags found.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B80" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Tag Name</v>
+        <v>ID</v>
       </c>
       <c r="B81" t="str">
-        <v>태그 이름</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ID</v>
+        <v>Offset</v>
       </c>
       <c r="B82" t="str">
-        <v>ID</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Offset</v>
+        <v>Size</v>
       </c>
       <c r="B83" t="str">
-        <v>오프셋</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Size</v>
+        <v>Pad</v>
       </c>
       <c r="B84" t="str">
-        <v>크기</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Pad</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B85" t="str">
-        <v>패딩</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Bytes changed since load</v>
+        <v>Type</v>
       </c>
       <c r="B86" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Type</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B87" t="str">
-        <v>유형</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Array of {type}</v>
+        <v>(No content)</v>
       </c>
       <c r="B88" t="str">
-        <v>{type} 배열</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>(No content)</v>
+        <v>bytes</v>
       </c>
       <c r="B89" t="str">
-        <v>(내용 없음)</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>bytes</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B90" t="str">
-        <v>바이트</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading full description…</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B91" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not load full description:</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B92" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B93" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>No validation output</v>
       </c>
       <c r="B94" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>No validation output</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B95" t="str">
-        <v>검증 출력 없음</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile is valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B96" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B97" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B98" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Critical validation error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B99" t="str">
-        <v>심각한 검증 오류</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B100" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B101" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Valid</v>
       </c>
       <c r="B102" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Valid</v>
+        <v>Warning</v>
       </c>
       <c r="B103" t="str">
-        <v>유효</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Warning</v>
+        <v>Error</v>
       </c>
       <c r="B104" t="str">
-        <v>경고</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Error</v>
+        <v>Unknown</v>
       </c>
       <c r="B105" t="str">
-        <v>오류</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Unknown</v>
+        <v>Pass</v>
       </c>
       <c r="B106" t="str">
-        <v>알 수 없음</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="B107" t="str">
-        <v>통과</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Fail</v>
+        <v>View in context</v>
       </c>
       <c r="B108" t="str">
-        <v>실패</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>View in context</v>
+        <v>Validation detail</v>
       </c>
       <c r="B109" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Validation detail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B110" t="str">
-        <v>검증 세부 정보</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Triggered by</v>
+        <v>Field</v>
       </c>
       <c r="B111" t="str">
-        <v>트리거 항목</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Field</v>
+        <v>Current value</v>
       </c>
       <c r="B112" t="str">
-        <v>항목</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Current value</v>
+        <v>Required: 0</v>
       </c>
       <c r="B113" t="str">
-        <v>현재 값</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Required: 0</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B114" t="str">
-        <v>필수: 0</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid</v>
       </c>
       <c r="B115" t="str">
-        <v>예상: {value}</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Invalid</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B116" t="str">
-        <v>잘못됨</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Close</v>
       </c>
       <c r="B117" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Close</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B118" t="str">
-        <v>닫기</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading XML editor…</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B119" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Loading JSON editor…</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B120" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B121" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B122" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved XML edits</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B123" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B124" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B125" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>indent</v>
       </c>
       <c r="B126" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>들여쓰기</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>indent</v>
+        <v>sort keys</v>
       </c>
       <c r="B127" t="str">
-        <v>들여쓰기</v>
+        <v>키 정렬</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>sort keys</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B128" t="str">
-        <v>키 정렬</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B129" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B128"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B131"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -477,959 +477,983 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Help</v>
+        <v>Number format</v>
       </c>
       <c r="B10" t="str">
-        <v>도움말</v>
+        <v>숫자 형식</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Contact</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B11" t="str">
-        <v>문의</v>
+        <v>16진수</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Decimal</v>
       </c>
       <c r="B12" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>10진수</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Help</v>
       </c>
       <c r="B13" t="str">
-        <v>ICC 프로파일을 업로드하여</v>
+        <v>도움말</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>specification using the</v>
+        <v>Contact</v>
       </c>
       <c r="B14" t="str">
-        <v>사양을</v>
+        <v>문의</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>demo implementation.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B15" t="str">
-        <v>데모 구현으로 검증합니다.</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Based on</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B16" t="str">
-        <v/>
+        <v>ICC 프로파일을 업로드하여</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>demo implementation</v>
+        <v>specification using the</v>
       </c>
       <c r="B17" t="str">
-        <v>데모 구현 기반</v>
+        <v>사양을</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Validating…</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B18" t="str">
-        <v>검증 중…</v>
+        <v>데모 구현으로 검증합니다.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Save ICC profile</v>
+        <v>Based on</v>
       </c>
       <c r="B19" t="str">
-        <v>ICC 프로파일 저장</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>demo implementation</v>
       </c>
       <c r="B20" t="str">
-        <v>● 변경됨 — 저장되지 않음</v>
+        <v>데모 구현 기반</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Validating…</v>
       </c>
       <c r="B21" t="str">
-        <v>ICC 프로파일을 여기에 놓기</v>
+        <v>검증 중…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>or</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B22" t="str">
-        <v>또는</v>
+        <v>ICC 프로파일 저장</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Choose file</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B23" t="str">
-        <v>파일 선택</v>
+        <v>● 변경됨 — 저장되지 않음</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>.icc and .icm files</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B24" t="str">
-        <v>.icc 및 .icm 파일</v>
+        <v>ICC 프로파일을 여기에 놓기</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Header</v>
+        <v>or</v>
       </c>
       <c r="B25" t="str">
-        <v>헤더</v>
+        <v>또는</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Tags</v>
+        <v>Choose file</v>
       </c>
       <c r="B26" t="str">
-        <v>태그</v>
+        <v>파일 선택</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Validation</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B27" t="str">
-        <v>검증</v>
+        <v>.icc 및 .icm 파일</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Plot</v>
+        <v>Header</v>
       </c>
       <c r="B28" t="str">
-        <v>플롯</v>
+        <v>헤더</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Raw Output</v>
+        <v>Tags</v>
       </c>
       <c r="B29" t="str">
-        <v>원시 출력</v>
+        <v>태그</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>XML</v>
+        <v>Validation</v>
       </c>
       <c r="B30" t="str">
-        <v>XML</v>
+        <v>검증</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>JSON</v>
+        <v>Plot</v>
       </c>
       <c r="B31" t="str">
-        <v>JSON</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B32" t="str">
-        <v>곡선</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Input curves</v>
+        <v>XML</v>
       </c>
       <c r="B33" t="str">
-        <v>입력 곡선</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Output curves</v>
+        <v>JSON</v>
       </c>
       <c r="B34" t="str">
-        <v>출력 곡선</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CLUT image</v>
+        <v>Curves</v>
       </c>
       <c r="B35" t="str">
-        <v>CLUT 이미지</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Gamut image</v>
+        <v>Input curves</v>
       </c>
       <c r="B36" t="str">
-        <v>색역 이미지</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Chromaticity</v>
+        <v>Output curves</v>
       </c>
       <c r="B37" t="str">
-        <v>색도</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Scatter plot</v>
+        <v>CLUT image</v>
       </c>
       <c r="B38" t="str">
-        <v>산점도</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Tone response curve</v>
+        <v>Gamut image</v>
       </c>
       <c r="B39" t="str">
-        <v>톤 응답 곡선</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Curve table</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B40" t="str">
-        <v>곡선 표</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tables</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B41" t="str">
-        <v>표</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Data</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B42" t="str">
-        <v>데이터</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Evaluate</v>
+        <v>Curve table</v>
       </c>
       <c r="B43" t="str">
-        <v>평가</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Loading…</v>
+        <v>Tables</v>
       </c>
       <c r="B44" t="str">
-        <v>불러오는 중…</v>
+        <v>표</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Input</v>
+        <v>Data</v>
       </c>
       <c r="B45" t="str">
-        <v>입력</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Output</v>
+        <v>Evaluate</v>
       </c>
       <c r="B46" t="str">
-        <v>출력</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Floating point</v>
+        <v>Loading…</v>
       </c>
       <c r="B47" t="str">
-        <v>부동 소수점</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Grid point</v>
+        <v>Input</v>
       </c>
       <c r="B48" t="str">
-        <v>격자점</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Normalized</v>
+        <v>Output</v>
       </c>
       <c r="B49" t="str">
-        <v>정규화</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Human</v>
+        <v>Floating point</v>
       </c>
       <c r="B50" t="str">
-        <v>사람용</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Device → PCS</v>
+        <v>Grid point</v>
       </c>
       <c r="B51" t="str">
-        <v>장치 → PCS</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PCS → Device</v>
+        <v>Normalized</v>
       </c>
       <c r="B52" t="str">
-        <v>PCS → 장치</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No CLUT grid</v>
+        <v>Human</v>
       </c>
       <c r="B53" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Loading…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B54" t="str">
-        <v>불러오는 중…</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B55" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Invalid profile URL:</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B56" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Loading…</v>
       </c>
       <c r="B57" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B58" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B59" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B60" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Security</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B61" t="str">
-        <v>보안</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Conformance</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B62" t="str">
-        <v>적합성</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Quality</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B63" t="str">
-        <v>품질</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>REPORT</v>
+        <v>Security</v>
       </c>
       <c r="B64" t="str">
-        <v>보고서</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>FAIL</v>
+        <v>Conformance</v>
       </c>
       <c r="B65" t="str">
-        <v>실패</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>checks</v>
+        <v>Quality</v>
       </c>
       <c r="B66" t="str">
-        <v>개 검사</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>REPORT</v>
       </c>
       <c r="B67" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>FAIL</v>
       </c>
       <c r="B68" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Error:</v>
+        <v>checks</v>
       </c>
       <c r="B69" t="str">
-        <v>오류:</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Convert to XML</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B70" t="str">
-        <v>XML로 변환</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to JSON</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B71" t="str">
-        <v>JSON으로 변환</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to ICC</v>
+        <v>Error:</v>
       </c>
       <c r="B72" t="str">
-        <v>ICC로 변환</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B73" t="str">
-        <v>XML로 변환 중…</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B74" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B75" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B76" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B77" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Profile ID</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B78" t="str">
-        <v>프로파일 ID</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>No tags found.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B79" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Tag Name</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B80" t="str">
-        <v>태그 이름</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ID</v>
+        <v>Profile ID</v>
       </c>
       <c r="B81" t="str">
-        <v>ID</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Offset</v>
+        <v>No tags found.</v>
       </c>
       <c r="B82" t="str">
-        <v>오프셋</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Size</v>
+        <v>Tag Name</v>
       </c>
       <c r="B83" t="str">
-        <v>크기</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Pad</v>
+        <v>ID</v>
       </c>
       <c r="B84" t="str">
-        <v>패딩</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bytes changed since load</v>
+        <v>Offset</v>
       </c>
       <c r="B85" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Type</v>
+        <v>Size</v>
       </c>
       <c r="B86" t="str">
-        <v>유형</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Array of {type}</v>
+        <v>Pad</v>
       </c>
       <c r="B87" t="str">
-        <v>{type} 배열</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>(No content)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B88" t="str">
-        <v>(내용 없음)</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>bytes</v>
+        <v>Type</v>
       </c>
       <c r="B89" t="str">
-        <v>바이트</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading full description…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B90" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Could not load full description:</v>
+        <v>(No content)</v>
       </c>
       <c r="B91" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>bytes</v>
       </c>
       <c r="B92" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B93" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>No validation output</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B94" t="str">
-        <v>검증 출력 없음</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Profile is valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B95" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B96" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile is non-compliant</v>
+        <v>No validation output</v>
       </c>
       <c r="B97" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B98" t="str">
-        <v>심각한 검증 오류</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B99" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B100" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B101" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Valid</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B102" t="str">
-        <v>유효</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Warning</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B103" t="str">
-        <v>경고</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B104" t="str">
-        <v>오류</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Unknown</v>
+        <v>Valid</v>
       </c>
       <c r="B105" t="str">
-        <v>알 수 없음</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Pass</v>
+        <v>Warning</v>
       </c>
       <c r="B106" t="str">
-        <v>통과</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Fail</v>
+        <v>Error</v>
       </c>
       <c r="B107" t="str">
-        <v>실패</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>View in context</v>
+        <v>Unknown</v>
       </c>
       <c r="B108" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Validation detail</v>
+        <v>Pass</v>
       </c>
       <c r="B109" t="str">
-        <v>검증 세부 정보</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Triggered by</v>
+        <v>Fail</v>
       </c>
       <c r="B110" t="str">
-        <v>트리거 항목</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Field</v>
+        <v>View in context</v>
       </c>
       <c r="B111" t="str">
-        <v>항목</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Current value</v>
+        <v>Validation detail</v>
       </c>
       <c r="B112" t="str">
-        <v>현재 값</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Required: 0</v>
+        <v>Triggered by</v>
       </c>
       <c r="B113" t="str">
-        <v>필수: 0</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Expected: {value}</v>
+        <v>Field</v>
       </c>
       <c r="B114" t="str">
-        <v>예상: {value}</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Invalid</v>
+        <v>Current value</v>
       </c>
       <c r="B115" t="str">
-        <v>잘못됨</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B116" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Close</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B117" t="str">
-        <v>닫기</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Loading XML editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B118" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading JSON editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B119" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B120" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B121" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B123" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B125" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>indent</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B126" t="str">
-        <v>들여쓰기</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B127" t="str">
-        <v>키 정렬</v>
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B128" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B129" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B130" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B128" t="str">
+      <c r="B131" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B128"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B131"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B132"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -885,575 +885,583 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B61" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B62" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B63" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B64" t="str">
-        <v>보안</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B65" t="str">
-        <v>적합성</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B66" t="str">
-        <v>품질</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B67" t="str">
-        <v>보고서</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B68" t="str">
-        <v>실패</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B69" t="str">
-        <v>개 검사</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B70" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B71" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Error:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B72" t="str">
-        <v>오류:</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B73" t="str">
-        <v>XML로 변환</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B74" t="str">
-        <v>JSON으로 변환</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B75" t="str">
-        <v>ICC로 변환</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B76" t="str">
-        <v>XML로 변환 중…</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B77" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B78" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B79" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B80" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B81" t="str">
-        <v>프로파일 ID</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B82" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B83" t="str">
-        <v>태그 이름</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B84" t="str">
-        <v>ID</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B85" t="str">
-        <v>오프셋</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B86" t="str">
-        <v>크기</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B87" t="str">
-        <v>패딩</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B88" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B89" t="str">
-        <v>유형</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B90" t="str">
-        <v>{type} 배열</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B91" t="str">
-        <v>(내용 없음)</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B92" t="str">
-        <v>바이트</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B93" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B94" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B95" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B96" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B97" t="str">
-        <v>검증 출력 없음</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B98" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B99" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B100" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B101" t="str">
-        <v>심각한 검증 오류</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B102" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B103" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B104" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B105" t="str">
-        <v>유효</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B106" t="str">
-        <v>경고</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B107" t="str">
-        <v>오류</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B108" t="str">
-        <v>알 수 없음</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B109" t="str">
-        <v>통과</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B110" t="str">
-        <v>실패</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B111" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B112" t="str">
-        <v>검증 세부 정보</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B113" t="str">
-        <v>트리거 항목</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B114" t="str">
-        <v>항목</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B115" t="str">
-        <v>현재 값</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B116" t="str">
-        <v>필수: 0</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B117" t="str">
-        <v>예상: {value}</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B118" t="str">
-        <v>잘못됨</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B119" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B120" t="str">
-        <v>닫기</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B121" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B123" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B125" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B126" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B127" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B128" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B129" t="str">
-        <v>들여쓰기</v>
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B130" t="str">
-        <v>키 정렬</v>
+        <v>들여쓰기</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B131" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B131" t="str">
+      <c r="B132" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B131"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B132"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B132"/>
+  <dimension ref="A1:B181"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -645,823 +645,1215 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Plot</v>
+        <v>Analysis</v>
       </c>
       <c r="B31" t="str">
-        <v>플롯</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Raw Output</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B32" t="str">
-        <v>원시 출력</v>
+        <v>중립축 잉킹</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>XML</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B33" t="str">
-        <v>XML</v>
+        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>JSON</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B34" t="str">
-        <v>JSON</v>
+        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Curves</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B35" t="str">
-        <v>곡선</v>
+        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Input curves</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B36" t="str">
-        <v>입력 곡선</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Output curves</v>
+        <v>% ink</v>
       </c>
       <c r="B37" t="str">
-        <v>출력 곡선</v>
+        <v>% 잉크</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CLUT image</v>
+        <v>Perceptual</v>
       </c>
       <c r="B38" t="str">
-        <v>CLUT 이미지</v>
+        <v>지각적</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Gamut image</v>
+        <v>Relative colorimetric</v>
       </c>
       <c r="B39" t="str">
-        <v>색역 이미지</v>
+        <v>상대 색도</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Chromaticity</v>
+        <v>Saturation</v>
       </c>
       <c r="B40" t="str">
-        <v>색도</v>
+        <v>채도</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Scatter plot</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B41" t="str">
-        <v>산점도</v>
+        <v>반전이 많은 채널은 ΔL* 기준 상위 {shown}개만 표시합니다.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Tone response curve</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B42" t="str">
-        <v>톤 응답 곡선</v>
+        <v>더 보기({n})</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Curve table</v>
+        <v>All</v>
       </c>
       <c r="B43" t="str">
-        <v>곡선 표</v>
+        <v>전체</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Tables</v>
+        <v>Analysing…</v>
       </c>
       <c r="B44" t="str">
-        <v>표</v>
+        <v>분석 중…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Data</v>
+        <v>Analysis</v>
       </c>
       <c r="B45" t="str">
-        <v>데이터</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Evaluate</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B46" t="str">
-        <v>평가</v>
+        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Loading…</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B47" t="str">
-        <v>불러오는 중…</v>
+        <v>L* 톤 반전</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Input</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B48" t="str">
-        <v>입력</v>
+        <v>잉크를 더해도 색이 밝아져서는 안 됩니다. 각 장치 채널을 훑으면서 나머지는 고정하고, L*가 올라가는 구간을 표시합니다. 알고리즘은 원래 Harold Boll이 고안했습니다.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Output</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B49" t="str">
-        <v>출력</v>
+        <v>이 프로파일에는 장치→PCS CLUT가 없으므로 L* 반전 검사가 적용되지 않습니다(예: 매트릭스/TRC 디스플레이 프로파일).</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Floating point</v>
+        <v>LUT table</v>
       </c>
       <c r="B50" t="str">
-        <v>부동 소수점</v>
+        <v>LUT 테이블</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Grid point</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B51" t="str">
-        <v>격자점</v>
+        <v>ΔL* 임계값 (ε)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Normalized</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B52" t="str">
-        <v>정규화</v>
+        <v>ε = {eps} 초과 반전: {n}</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Human</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B53" t="str">
-        <v>사람용</v>
+        <v>ε = {eps}을 초과하는 L* 반전 없음</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Device → PCS</v>
+        <v>Channel</v>
       </c>
       <c r="B54" t="str">
-        <v>장치 → PCS</v>
+        <v>채널</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PCS → Device</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B55" t="str">
-        <v>PCS → 장치</v>
+        <v>잉크(낮음 → 높음)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No CLUT grid</v>
+        <v>Plot</v>
       </c>
       <c r="B56" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Loading…</v>
+        <v>Raw Output</v>
       </c>
       <c r="B57" t="str">
-        <v>불러오는 중…</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>XML</v>
       </c>
       <c r="B58" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Invalid profile URL:</v>
+        <v>JSON</v>
       </c>
       <c r="B59" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curves</v>
       </c>
       <c r="B60" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Input curves</v>
       </c>
       <c r="B61" t="str">
-        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Output curves</v>
       </c>
       <c r="B62" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B63" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Gamut image</v>
       </c>
       <c r="B64" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Security</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B65" t="str">
-        <v>보안</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Conformance</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B66" t="str">
-        <v>적합성</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Quality</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B67" t="str">
-        <v>품질</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>REPORT</v>
+        <v>Curve table</v>
       </c>
       <c r="B68" t="str">
-        <v>보고서</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>FAIL</v>
+        <v>Tables</v>
       </c>
       <c r="B69" t="str">
-        <v>실패</v>
+        <v>표</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>checks</v>
+        <v>Data</v>
       </c>
       <c r="B70" t="str">
-        <v>개 검사</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B71" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading…</v>
       </c>
       <c r="B72" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Error:</v>
+        <v>Input</v>
       </c>
       <c r="B73" t="str">
-        <v>오류:</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to XML</v>
+        <v>Output</v>
       </c>
       <c r="B74" t="str">
-        <v>XML로 변환</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to JSON</v>
+        <v>Floating point</v>
       </c>
       <c r="B75" t="str">
-        <v>JSON으로 변환</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Convert to ICC</v>
+        <v>Grid point</v>
       </c>
       <c r="B76" t="str">
-        <v>ICC로 변환</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to XML…</v>
+        <v>Normalized</v>
       </c>
       <c r="B77" t="str">
-        <v>XML로 변환 중…</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to JSON…</v>
+        <v>Human</v>
       </c>
       <c r="B78" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B79" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Load ICC profile</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B80" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B81" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Profile ID</v>
+        <v>Loading…</v>
       </c>
       <c r="B82" t="str">
-        <v>프로파일 ID</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>No tags found.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B83" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Tag Name</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B84" t="str">
-        <v>태그 이름</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ID</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B85" t="str">
-        <v>ID</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Offset</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B86" t="str">
-        <v>오프셋</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Size</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B87" t="str">
-        <v>크기</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Pad</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B88" t="str">
-        <v>패딩</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B89" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Type</v>
+        <v>Security</v>
       </c>
       <c r="B90" t="str">
-        <v>유형</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Array of {type}</v>
+        <v>Conformance</v>
       </c>
       <c r="B91" t="str">
-        <v>{type} 배열</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>(No content)</v>
+        <v>Quality</v>
       </c>
       <c r="B92" t="str">
-        <v>(내용 없음)</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>bytes</v>
+        <v>REPORT</v>
       </c>
       <c r="B93" t="str">
-        <v>바이트</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading full description…</v>
+        <v>FAIL</v>
       </c>
       <c r="B94" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Could not load full description:</v>
+        <v>checks</v>
       </c>
       <c r="B95" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B96" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B97" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>No validation output</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B98" t="str">
-        <v>검증 출력 없음</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile is valid</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B99" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B100" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B101" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Critical validation error</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B102" t="str">
-        <v>심각한 검증 오류</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Unknown validation status</v>
+        <v>Close</v>
       </c>
       <c r="B103" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B104" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Email address</v>
       </c>
       <c r="B105" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Valid</v>
+        <v>you@example.com</v>
       </c>
       <c r="B106" t="str">
-        <v>유효</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Warning</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B107" t="str">
-        <v>경고</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Error</v>
+        <v>(optional)</v>
       </c>
       <c r="B108" t="str">
-        <v>오류</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Unknown</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B109" t="str">
-        <v>알 수 없음</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Pass</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B110" t="str">
-        <v>통과</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Fail</v>
+        <v>Cancel</v>
       </c>
       <c r="B111" t="str">
-        <v>실패</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>View in context</v>
+        <v>Subscribe</v>
       </c>
       <c r="B112" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Validation detail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B113" t="str">
-        <v>검증 세부 정보</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Triggered by</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B114" t="str">
-        <v>트리거 항목</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Field</v>
+        <v>Close</v>
       </c>
       <c r="B115" t="str">
-        <v>항목</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Current value</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B116" t="str">
-        <v>현재 값</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Required: 0</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B117" t="str">
-        <v>필수: 0</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Expected: {value}</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B118" t="str">
-        <v>예상: {value}</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Invalid</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B119" t="str">
-        <v>잘못됨</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B120" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Close</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B121" t="str">
-        <v>닫기</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading XML editor…</v>
+        <v>Error:</v>
       </c>
       <c r="B122" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B123" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B124" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B125" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B126" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B127" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B128" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B129" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>indent</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B130" t="str">
-        <v>들여쓰기</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>sort keys</v>
+        <v>Profile ID</v>
       </c>
       <c r="B131" t="str">
-        <v>키 정렬</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B132" t="str">
+        <v>태그를 찾을 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B133" t="str">
+        <v>태그 이름</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B134" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B135" t="str">
+        <v>오프셋</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B136" t="str">
+        <v>크기</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B137" t="str">
+        <v>패딩</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B138" t="str">
+        <v>로드 이후 바이트가 변경됨</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B139" t="str">
+        <v>유형</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B140" t="str">
+        <v>{type} 배열</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B141" t="str">
+        <v>(내용 없음)</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B142" t="str">
+        <v>바이트</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B143" t="str">
+        <v>전체 설명을 로드하는 중…</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B144" t="str">
+        <v>전체 설명을 로드할 수 없습니다:</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B145" t="str">
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B146" t="str">
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B147" t="str">
+        <v>검증 출력 없음</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B148" t="str">
+        <v>프로파일이 유효합니다</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B149" t="str">
+        <v>프로파일에 경고가 있습니다</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B150" t="str">
+        <v>프로파일이 규격을 준수하지 않습니다</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B151" t="str">
+        <v>심각한 검증 오류</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B152" t="str">
+        <v>알 수 없는 검증 상태</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B153" t="str">
+        <v>심각 — 검사용으로만 표시</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B154" t="str">
+        <v>경고나 오류를 찾지 못했습니다.</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B155" t="str">
+        <v>유효</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B156" t="str">
+        <v>경고</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B157" t="str">
+        <v>오류</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B158" t="str">
+        <v>알 수 없음</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B159" t="str">
+        <v>통과</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B160" t="str">
+        <v>실패</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B161" t="str">
+        <v>컨텍스트에서 보기</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B162" t="str">
+        <v>검증 세부 정보</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B163" t="str">
+        <v>트리거 항목</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B164" t="str">
+        <v>항목</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B165" t="str">
+        <v>현재 값</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B166" t="str">
+        <v>필수: 0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B167" t="str">
+        <v>예상: {value}</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B168" t="str">
+        <v>잘못됨</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B169" t="str">
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B170" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B171" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B172" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B173" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B174" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B175" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B176" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B177" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B178" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B179" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B180" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B132" t="str">
+      <c r="B181" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B132"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B181"/>
+  <dimension ref="A1:B190"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -517,1343 +517,1415 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ICC Profile Tool</v>
+        <v>User guide</v>
       </c>
       <c r="B15" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>사용자 가이드</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Search guide</v>
       </c>
       <c r="B16" t="str">
-        <v>ICC 프로파일을 업로드하여</v>
+        <v>가이드 검색</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>specification using the</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B17" t="str">
-        <v>사양을</v>
+        <v>사용자 가이드 검색</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>demo implementation.</v>
+        <v>Previous match</v>
       </c>
       <c r="B18" t="str">
-        <v>데모 구현으로 검증합니다.</v>
+        <v>이전 검색 결과</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Based on</v>
+        <v>Next match</v>
       </c>
       <c r="B19" t="str">
-        <v/>
+        <v>다음 검색 결과</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>demo implementation</v>
+        <v>Close user guide</v>
       </c>
       <c r="B20" t="str">
-        <v>데모 구현 기반</v>
+        <v>사용자 가이드 닫기</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Validating…</v>
+        <v>Loading…</v>
       </c>
       <c r="B21" t="str">
-        <v>검증 중…</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Save ICC profile</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B22" t="str">
-        <v>ICC 프로파일 저장</v>
+        <v>사용자 가이드를 불러올 수 없습니다.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>None</v>
       </c>
       <c r="B23" t="str">
-        <v>● 변경됨 — 저장되지 않음</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B24" t="str">
-        <v>ICC 프로파일을 여기에 놓기</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>or</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B25" t="str">
-        <v>또는</v>
+        <v>ICC 프로파일을 업로드하여</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Choose file</v>
+        <v>specification using the</v>
       </c>
       <c r="B26" t="str">
-        <v>파일 선택</v>
+        <v>사양을</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>.icc and .icm files</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B27" t="str">
-        <v>.icc 및 .icm 파일</v>
+        <v>데모 구현으로 검증합니다.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Header</v>
+        <v>Based on</v>
       </c>
       <c r="B28" t="str">
-        <v>헤더</v>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Tags</v>
+        <v>demo implementation</v>
       </c>
       <c r="B29" t="str">
-        <v>태그</v>
+        <v>데모 구현 기반</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validation</v>
+        <v>Validating…</v>
       </c>
       <c r="B30" t="str">
-        <v>검증</v>
+        <v>검증 중…</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Analysis</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B31" t="str">
-        <v>분석</v>
+        <v>ICC 프로파일 저장</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B32" t="str">
-        <v>중립축 잉킹</v>
+        <v>● 변경됨 — 저장되지 않음</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B33" t="str">
-        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
+        <v>ICC 프로파일을 여기에 놓기</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>or</v>
       </c>
       <c r="B34" t="str">
-        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>또는</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Choose file</v>
       </c>
       <c r="B35" t="str">
-        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
+        <v>파일 선택</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Rendering intent</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B36" t="str">
-        <v>렌더링 의도</v>
+        <v>.icc 및 .icm 파일</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>% ink</v>
+        <v>Header</v>
       </c>
       <c r="B37" t="str">
-        <v>% 잉크</v>
+        <v>헤더</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Perceptual</v>
+        <v>Tags</v>
       </c>
       <c r="B38" t="str">
-        <v>지각적</v>
+        <v>태그</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Relative colorimetric</v>
+        <v>Validation</v>
       </c>
       <c r="B39" t="str">
-        <v>상대 색도</v>
+        <v>검증</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Saturation</v>
+        <v>Analysis</v>
       </c>
       <c r="B40" t="str">
-        <v>채도</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B41" t="str">
-        <v>반전이 많은 채널은 ΔL* 기준 상위 {shown}개만 표시합니다.</v>
+        <v>중립축 잉킹</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Show more ({n})</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B42" t="str">
-        <v>더 보기({n})</v>
+        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>All</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B43" t="str">
-        <v>전체</v>
+        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Analysing…</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B44" t="str">
-        <v>분석 중…</v>
+        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B45" t="str">
-        <v>분석</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>% ink</v>
       </c>
       <c r="B46" t="str">
-        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
+        <v>% 잉크</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Perceptual</v>
       </c>
       <c r="B47" t="str">
-        <v>L* 톤 반전</v>
+        <v>지각적</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B48" t="str">
-        <v>잉크를 더해도 색이 밝아져서는 안 됩니다. 각 장치 채널을 훑으면서 나머지는 고정하고, L*가 올라가는 구간을 표시합니다. 알고리즘은 원래 Harold Boll이 고안했습니다.</v>
+        <v>상대 색도</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B49" t="str">
-        <v>이 프로파일에는 장치→PCS CLUT가 없으므로 L* 반전 검사가 적용되지 않습니다(예: 매트릭스/TRC 디스플레이 프로파일).</v>
+        <v>채도</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>LUT table</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B50" t="str">
-        <v>LUT 테이블</v>
+        <v>반전이 많은 채널은 ΔL* 기준 상위 {shown}개만 표시합니다.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B51" t="str">
-        <v>ΔL* 임계값 (ε)</v>
+        <v>더 보기({n})</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B52" t="str">
-        <v>ε = {eps} 초과 반전: {n}</v>
+        <v>전체</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Analysing…</v>
       </c>
       <c r="B53" t="str">
-        <v>ε = {eps}을 초과하는 L* 반전 없음</v>
+        <v>분석 중…</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Channel</v>
+        <v>Analysis</v>
       </c>
       <c r="B54" t="str">
-        <v>채널</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ink (low → high)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B55" t="str">
-        <v>잉크(낮음 → 높음)</v>
+        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Plot</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B56" t="str">
-        <v>플롯</v>
+        <v>L* 톤 반전</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Raw Output</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B57" t="str">
-        <v>원시 출력</v>
+        <v>잉크를 더해도 색이 밝아져서는 안 됩니다. 각 장치 채널을 훑으면서 나머지는 고정하고, L*가 올라가는 구간을 표시합니다. 알고리즘은 원래 Harold Boll이 고안했습니다.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>XML</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B58" t="str">
-        <v>XML</v>
+        <v>이 프로파일에는 장치→PCS CLUT가 없으므로 L* 반전 검사가 적용되지 않습니다(예: 매트릭스/TRC 디스플레이 프로파일).</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>JSON</v>
+        <v>LUT table</v>
       </c>
       <c r="B59" t="str">
-        <v>JSON</v>
+        <v>LUT 테이블</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B60" t="str">
-        <v>곡선</v>
+        <v>ΔL* 임계값 (ε)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Input curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B61" t="str">
-        <v>입력 곡선</v>
+        <v>ε = {eps} 초과 반전: {n}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Output curves</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B62" t="str">
-        <v>출력 곡선</v>
+        <v>ε = {eps}을 초과하는 L* 반전 없음</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>CLUT image</v>
+        <v>Channel</v>
       </c>
       <c r="B63" t="str">
-        <v>CLUT 이미지</v>
+        <v>채널</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Gamut image</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B64" t="str">
-        <v>색역 이미지</v>
+        <v>잉크(낮음 → 높음)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Chromaticity</v>
+        <v>Plot</v>
       </c>
       <c r="B65" t="str">
-        <v>색도</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Scatter plot</v>
+        <v>Raw Output</v>
       </c>
       <c r="B66" t="str">
-        <v>산점도</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tone response curve</v>
+        <v>XML</v>
       </c>
       <c r="B67" t="str">
-        <v>톤 응답 곡선</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curve table</v>
+        <v>JSON</v>
       </c>
       <c r="B68" t="str">
-        <v>곡선 표</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tables</v>
+        <v>Curves</v>
       </c>
       <c r="B69" t="str">
-        <v>표</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Data</v>
+        <v>Input curves</v>
       </c>
       <c r="B70" t="str">
-        <v>데이터</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Evaluate</v>
+        <v>Output curves</v>
       </c>
       <c r="B71" t="str">
-        <v>평가</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B72" t="str">
-        <v>불러오는 중…</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Input</v>
+        <v>Gamut image</v>
       </c>
       <c r="B73" t="str">
-        <v>입력</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Output</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B74" t="str">
-        <v>출력</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Floating point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B75" t="str">
-        <v>부동 소수점</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Grid point</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B76" t="str">
-        <v>격자점</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Normalized</v>
+        <v>Curve table</v>
       </c>
       <c r="B77" t="str">
-        <v>정규화</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Human</v>
+        <v>Tables</v>
       </c>
       <c r="B78" t="str">
-        <v>사람용</v>
+        <v>표</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Device → PCS</v>
+        <v>Data</v>
       </c>
       <c r="B79" t="str">
-        <v>장치 → PCS</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PCS → Device</v>
+        <v>Evaluate</v>
       </c>
       <c r="B80" t="str">
-        <v>PCS → 장치</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>No CLUT grid</v>
+        <v>Loading…</v>
       </c>
       <c r="B81" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Loading…</v>
+        <v>Input</v>
       </c>
       <c r="B82" t="str">
-        <v>불러오는 중…</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Output</v>
       </c>
       <c r="B83" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Floating point</v>
       </c>
       <c r="B84" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Grid point</v>
       </c>
       <c r="B85" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Normalized</v>
       </c>
       <c r="B86" t="str">
-        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Human</v>
       </c>
       <c r="B87" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B88" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B89" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Security</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B90" t="str">
-        <v>보안</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Conformance</v>
+        <v>Loading…</v>
       </c>
       <c r="B91" t="str">
-        <v>적합성</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Quality</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B92" t="str">
-        <v>품질</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>REPORT</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B93" t="str">
-        <v>보고서</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>FAIL</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B94" t="str">
-        <v>실패</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>checks</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B95" t="str">
-        <v>개 검사</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B96" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B97" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B98" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Powered by {lib}</v>
+        <v>Security</v>
       </c>
       <c r="B99" t="str">
-        <v>{lib} 기반</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Subscribe</v>
+        <v>Conformance</v>
       </c>
       <c r="B100" t="str">
-        <v>구독</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Quality</v>
       </c>
       <c r="B101" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Get notified about new releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B102" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Close</v>
+        <v>FAIL</v>
       </c>
       <c r="B103" t="str">
-        <v>닫기</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>checks</v>
       </c>
       <c r="B104" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Email address</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B105" t="str">
-        <v>이메일 주소</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B106" t="str">
-        <v>you@example.com</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B107" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>(optional)</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B108" t="str">
-        <v>(선택)</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B109" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B110" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B111" t="str">
-        <v>취소</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B112" t="str">
-        <v>구독</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B113" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Email address</v>
       </c>
       <c r="B114" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B115" t="str">
-        <v>닫기</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Privacy notice</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B116" t="str">
-        <v>개인정보 처리방침</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>(optional)</v>
       </c>
       <c r="B117" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B118" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Please check the form and try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B119" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B120" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B121" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Error:</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B122" t="str">
-        <v>오류:</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Convert to XML</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B123" t="str">
-        <v>XML로 변환</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Convert to JSON</v>
+        <v>Close</v>
       </c>
       <c r="B124" t="str">
-        <v>JSON으로 변환</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Convert to ICC</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B125" t="str">
-        <v>ICC로 변환</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Converting to XML…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B126" t="str">
-        <v>XML로 변환 중…</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Converting to JSON…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B127" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Load ICC profile</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B130" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Profile ID</v>
+        <v>Error:</v>
       </c>
       <c r="B131" t="str">
-        <v>프로파일 ID</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>No tags found.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B132" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Tag Name</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B133" t="str">
-        <v>태그 이름</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ID</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B134" t="str">
-        <v>ID</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Offset</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B135" t="str">
-        <v>오프셋</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Size</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B136" t="str">
-        <v>크기</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Pad</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B137" t="str">
-        <v>패딩</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Bytes changed since load</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B138" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Type</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B139" t="str">
-        <v>유형</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Array of {type}</v>
+        <v>Profile ID</v>
       </c>
       <c r="B140" t="str">
-        <v>{type} 배열</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>(No content)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B141" t="str">
-        <v>(내용 없음)</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>bytes</v>
+        <v>Tag Name</v>
       </c>
       <c r="B142" t="str">
-        <v>바이트</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Loading full description…</v>
+        <v>ID</v>
       </c>
       <c r="B143" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Could not load full description:</v>
+        <v>Offset</v>
       </c>
       <c r="B144" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Size</v>
       </c>
       <c r="B145" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Pad</v>
       </c>
       <c r="B146" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>No validation output</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B147" t="str">
-        <v>검증 출력 없음</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Profile is valid</v>
+        <v>Type</v>
       </c>
       <c r="B148" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B149" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile is non-compliant</v>
+        <v>(No content)</v>
       </c>
       <c r="B150" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Critical validation error</v>
+        <v>bytes</v>
       </c>
       <c r="B151" t="str">
-        <v>심각한 검증 오류</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Unknown validation status</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B152" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B153" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No warnings or errors found.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B154" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B155" t="str">
-        <v>유효</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Warning</v>
+        <v>No validation output</v>
       </c>
       <c r="B156" t="str">
-        <v>경고</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B157" t="str">
-        <v>오류</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Unknown</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B158" t="str">
-        <v>알 수 없음</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Pass</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B159" t="str">
-        <v>통과</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Fail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B160" t="str">
-        <v>실패</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>View in context</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B161" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Validation detail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B162" t="str">
-        <v>검증 세부 정보</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Triggered by</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B163" t="str">
-        <v>트리거 항목</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Field</v>
+        <v>Valid</v>
       </c>
       <c r="B164" t="str">
-        <v>항목</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Current value</v>
+        <v>Warning</v>
       </c>
       <c r="B165" t="str">
-        <v>현재 값</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Required: 0</v>
+        <v>Error</v>
       </c>
       <c r="B166" t="str">
-        <v>필수: 0</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Expected: {value}</v>
+        <v>Unknown</v>
       </c>
       <c r="B167" t="str">
-        <v>예상: {value}</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Invalid</v>
+        <v>Pass</v>
       </c>
       <c r="B168" t="str">
-        <v>잘못됨</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Fail</v>
       </c>
       <c r="B169" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>View in context</v>
       </c>
       <c r="B170" t="str">
-        <v>닫기</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Loading XML editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B171" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B172" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B173" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B174" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B175" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B176" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B177" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B178" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>indent</v>
+        <v>Close</v>
       </c>
       <c r="B179" t="str">
-        <v>들여쓰기</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>sort keys</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>키 정렬</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B181" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B182" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B183" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B184" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B185" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B186" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B187" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B188" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B189" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B181" t="str">
+      <c r="B190" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B190"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B200"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -797,330 +797,330 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B50" t="str">
-        <v>반전이 많은 채널은 ΔL* 기준 상위 {shown}개만 표시합니다.</v>
+        <v>절대 색도</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Show more ({n})</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B51" t="str">
-        <v>더 보기({n})</v>
+        <v>프로파일 통계</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>All</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B52" t="str">
-        <v>전체</v>
+        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Analysing…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B53" t="str">
-        <v>분석 중…</v>
+        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B54" t="str">
-        <v>분석</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B55" t="str">
-        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
+        <v>색역 부피 (ΔE³)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B56" t="str">
-        <v>L* 톤 반전</v>
+        <v>왕복 ΔE</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>mean</v>
       </c>
       <c r="B57" t="str">
-        <v>잉크를 더해도 색이 밝아져서는 안 됩니다. 각 장치 채널을 훑으면서 나머지는 고정하고, L*가 올라가는 구간을 표시합니다. 알고리즘은 원래 Harold Boll이 고안했습니다.</v>
+        <v>평균</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>P90</v>
       </c>
       <c r="B58" t="str">
-        <v>이 프로파일에는 장치→PCS CLUT가 없으므로 L* 반전 검사가 적용되지 않습니다(예: 매트릭스/TRC 디스플레이 프로파일).</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>LUT table</v>
+        <v>max</v>
       </c>
       <c r="B59" t="str">
-        <v>LUT 테이블</v>
+        <v>최대</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B60" t="str">
-        <v>ΔL* 임계값 (ε)</v>
+        <v>반전이 많은 채널은 ΔL* 기준 상위 {shown}개만 표시합니다.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B61" t="str">
-        <v>ε = {eps} 초과 반전: {n}</v>
+        <v>더 보기({n})</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B62" t="str">
-        <v>ε = {eps}을 초과하는 L* 반전 없음</v>
+        <v>전체</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Channel</v>
+        <v>Analysing…</v>
       </c>
       <c r="B63" t="str">
-        <v>채널</v>
+        <v>분석 중…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ink (low → high)</v>
+        <v>Analysis</v>
       </c>
       <c r="B64" t="str">
-        <v>잉크(낮음 → 높음)</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B65" t="str">
-        <v>플롯</v>
+        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Raw Output</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B66" t="str">
-        <v>원시 출력</v>
+        <v>L* 톤 반전</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>XML</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B67" t="str">
-        <v>XML</v>
+        <v>잉크를 더해도 색이 밝아져서는 안 됩니다. 각 장치 채널을 훑으면서 나머지는 고정하고, L*가 올라가는 구간을 표시합니다. 알고리즘은 원래 Harold Boll이 고안했습니다.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>JSON</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B68" t="str">
-        <v>JSON</v>
+        <v>이 프로파일에는 장치→PCS CLUT가 없으므로 L* 반전 검사가 적용되지 않습니다(예: 매트릭스/TRC 디스플레이 프로파일).</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Curves</v>
+        <v>LUT table</v>
       </c>
       <c r="B69" t="str">
-        <v>곡선</v>
+        <v>LUT 테이블</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Input curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B70" t="str">
-        <v>입력 곡선</v>
+        <v>ΔL* 임계값 (ε)</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Output curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B71" t="str">
-        <v>출력 곡선</v>
+        <v>ε = {eps} 초과 반전: {n}</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CLUT image</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B72" t="str">
-        <v>CLUT 이미지</v>
+        <v>ε = {eps}을 초과하는 L* 반전 없음</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut image</v>
+        <v>Channel</v>
       </c>
       <c r="B73" t="str">
-        <v>색역 이미지</v>
+        <v>채널</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Chromaticity</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B74" t="str">
-        <v>색도</v>
+        <v>잉크(낮음 → 높음)</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Scatter plot</v>
+        <v>Plot</v>
       </c>
       <c r="B75" t="str">
-        <v>산점도</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tone response curve</v>
+        <v>Raw Output</v>
       </c>
       <c r="B76" t="str">
-        <v>톤 응답 곡선</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Curve table</v>
+        <v>XML</v>
       </c>
       <c r="B77" t="str">
-        <v>곡선 표</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tables</v>
+        <v>JSON</v>
       </c>
       <c r="B78" t="str">
-        <v>표</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Data</v>
+        <v>Curves</v>
       </c>
       <c r="B79" t="str">
-        <v>데이터</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Evaluate</v>
+        <v>Input curves</v>
       </c>
       <c r="B80" t="str">
-        <v>평가</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Loading…</v>
+        <v>Output curves</v>
       </c>
       <c r="B81" t="str">
-        <v>불러오는 중…</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Input</v>
+        <v>CLUT image</v>
       </c>
       <c r="B82" t="str">
-        <v>입력</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B83" t="str">
-        <v>출력</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Floating point</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B84" t="str">
-        <v>부동 소수점</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Grid point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B85" t="str">
-        <v>격자점</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Normalized</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B86" t="str">
-        <v>정규화</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Human</v>
+        <v>Curve table</v>
       </c>
       <c r="B87" t="str">
-        <v>사람용</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Device → PCS</v>
+        <v>Tables</v>
       </c>
       <c r="B88" t="str">
-        <v>장치 → PCS</v>
+        <v>표</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PCS → Device</v>
+        <v>Data</v>
       </c>
       <c r="B89" t="str">
-        <v>PCS → 장치</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>No CLUT grid</v>
+        <v>Evaluate</v>
       </c>
       <c r="B90" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="91">
@@ -1133,799 +1133,879 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Input</v>
       </c>
       <c r="B92" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Output</v>
       </c>
       <c r="B93" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Floating point</v>
       </c>
       <c r="B94" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Grid point</v>
       </c>
       <c r="B95" t="str">
-        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Normalized</v>
       </c>
       <c r="B96" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Human</v>
       </c>
       <c r="B97" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B98" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Security</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B99" t="str">
-        <v>보안</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Conformance</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B100" t="str">
-        <v>적합성</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Quality</v>
+        <v>Loading…</v>
       </c>
       <c r="B101" t="str">
-        <v>품질</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>REPORT</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B102" t="str">
-        <v>보고서</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>FAIL</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B103" t="str">
-        <v>실패</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>checks</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B104" t="str">
-        <v>개 검사</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B105" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B106" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B107" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Powered by {lib}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B108" t="str">
-        <v>{lib} 기반</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Subscribe</v>
+        <v>Security</v>
       </c>
       <c r="B109" t="str">
-        <v>구독</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Conformance</v>
       </c>
       <c r="B110" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Get notified about new releases</v>
+        <v>Quality</v>
       </c>
       <c r="B111" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B112" t="str">
-        <v>닫기</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B113" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B114" t="str">
-        <v>이메일 주소</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B115" t="str">
-        <v>you@example.com</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B116" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B117" t="str">
-        <v>(선택)</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B118" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B119" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B120" t="str">
-        <v>취소</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B121" t="str">
-        <v>구독</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B122" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B123" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B124" t="str">
-        <v>닫기</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B125" t="str">
-        <v>개인정보 처리방침</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B126" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B127" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B128" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B129" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B130" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B131" t="str">
-        <v>오류:</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B132" t="str">
-        <v>XML로 변환</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B133" t="str">
-        <v>JSON으로 변환</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B134" t="str">
-        <v>ICC로 변환</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B135" t="str">
-        <v>XML로 변환 중…</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B136" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B137" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B138" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B139" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B140" t="str">
-        <v>프로파일 ID</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B141" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B142" t="str">
-        <v>태그 이름</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B143" t="str">
-        <v>ID</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B144" t="str">
-        <v>오프셋</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B145" t="str">
-        <v>크기</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B146" t="str">
-        <v>패딩</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B147" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B148" t="str">
-        <v>유형</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B149" t="str">
-        <v>{type} 배열</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B150" t="str">
-        <v>(내용 없음)</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B151" t="str">
-        <v>바이트</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B152" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B153" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B154" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B155" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B156" t="str">
-        <v>검증 출력 없음</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B157" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B158" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B159" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B160" t="str">
-        <v>심각한 검증 오류</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B161" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B162" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B163" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B164" t="str">
-        <v>유효</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B165" t="str">
-        <v>경고</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B166" t="str">
-        <v>오류</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B167" t="str">
-        <v>알 수 없음</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B168" t="str">
-        <v>통과</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B169" t="str">
-        <v>실패</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B170" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B171" t="str">
-        <v>검증 세부 정보</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B172" t="str">
-        <v>트리거 항목</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B173" t="str">
-        <v>항목</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B174" t="str">
-        <v>현재 값</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B175" t="str">
-        <v>필수: 0</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B176" t="str">
-        <v>예상: {value}</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B177" t="str">
-        <v>잘못됨</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B178" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B179" t="str">
-        <v>닫기</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B180" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B181" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B182" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B183" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B184" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B185" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B186" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B187" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B188" t="str">
-        <v>들여쓰기</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B189" t="str">
-        <v>키 정렬</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B190" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B191" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B192" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B193" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B194" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B195" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B196" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B197" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B198" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B199" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B190" t="str">
+      <c r="B200" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B190"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B200"/>
+  <dimension ref="A1:B188"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -877,474 +877,474 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Analysing…</v>
       </c>
       <c r="B60" t="str">
-        <v>반전이 많은 채널은 ΔL* 기준 상위 {shown}개만 표시합니다.</v>
+        <v>분석 중…</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Show more ({n})</v>
+        <v>Analysis</v>
       </c>
       <c r="B61" t="str">
-        <v>더 보기({n})</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>All</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B62" t="str">
-        <v>전체</v>
+        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B63" t="str">
-        <v>분석 중…</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B64" t="str">
-        <v>분석</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B65" t="str">
-        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>L* Tone Reversal</v>
+        <v>JSON</v>
       </c>
       <c r="B66" t="str">
-        <v>L* 톤 반전</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Curves</v>
       </c>
       <c r="B67" t="str">
-        <v>잉크를 더해도 색이 밝아져서는 안 됩니다. 각 장치 채널을 훑으면서 나머지는 고정하고, L*가 올라가는 구간을 표시합니다. 알고리즘은 원래 Harold Boll이 고안했습니다.</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Input curves</v>
       </c>
       <c r="B68" t="str">
-        <v>이 프로파일에는 장치→PCS CLUT가 없으므로 L* 반전 검사가 적용되지 않습니다(예: 매트릭스/TRC 디스플레이 프로파일).</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>LUT table</v>
+        <v>Output curves</v>
       </c>
       <c r="B69" t="str">
-        <v>LUT 테이블</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>CLUT image</v>
       </c>
       <c r="B70" t="str">
-        <v>ΔL* 임계값 (ε)</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Gamut image</v>
       </c>
       <c r="B71" t="str">
-        <v>ε = {eps} 초과 반전: {n}</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B72" t="str">
-        <v>ε = {eps}을 초과하는 L* 반전 없음</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Channel</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B73" t="str">
-        <v>채널</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ink (low → high)</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B74" t="str">
-        <v>잉크(낮음 → 높음)</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Plot</v>
+        <v>Curve table</v>
       </c>
       <c r="B75" t="str">
-        <v>플롯</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Raw Output</v>
+        <v>Tables</v>
       </c>
       <c r="B76" t="str">
-        <v>원시 출력</v>
+        <v>표</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>XML</v>
+        <v>Data</v>
       </c>
       <c r="B77" t="str">
-        <v>XML</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>JSON</v>
+        <v>Evaluate</v>
       </c>
       <c r="B78" t="str">
-        <v>JSON</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Curves</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>곡선</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input curves</v>
+        <v>Input</v>
       </c>
       <c r="B80" t="str">
-        <v>입력 곡선</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output curves</v>
+        <v>Output</v>
       </c>
       <c r="B81" t="str">
-        <v>출력 곡선</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CLUT image</v>
+        <v>Floating point</v>
       </c>
       <c r="B82" t="str">
-        <v>CLUT 이미지</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Gamut image</v>
+        <v>Grid point</v>
       </c>
       <c r="B83" t="str">
-        <v>색역 이미지</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Chromaticity</v>
+        <v>Normalized</v>
       </c>
       <c r="B84" t="str">
-        <v>색도</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Scatter plot</v>
+        <v>Human</v>
       </c>
       <c r="B85" t="str">
-        <v>산점도</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Tone response curve</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B86" t="str">
-        <v>톤 응답 곡선</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Curve table</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B87" t="str">
-        <v>곡선 표</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Tables</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B88" t="str">
-        <v>표</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Data</v>
+        <v>Loading…</v>
       </c>
       <c r="B89" t="str">
-        <v>데이터</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Evaluate</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B90" t="str">
-        <v>평가</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B91" t="str">
-        <v>불러오는 중…</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Input</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B92" t="str">
-        <v>입력</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Output</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B93" t="str">
-        <v>출력</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Floating point</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B94" t="str">
-        <v>부동 소수점</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Grid point</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B95" t="str">
-        <v>격자점</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Normalized</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B96" t="str">
-        <v>정규화</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Human</v>
+        <v>Security</v>
       </c>
       <c r="B97" t="str">
-        <v>사람용</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Device → PCS</v>
+        <v>Conformance</v>
       </c>
       <c r="B98" t="str">
-        <v>장치 → PCS</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>PCS → Device</v>
+        <v>Quality</v>
       </c>
       <c r="B99" t="str">
-        <v>PCS → 장치</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No CLUT grid</v>
+        <v>REPORT</v>
       </c>
       <c r="B100" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Loading…</v>
+        <v>FAIL</v>
       </c>
       <c r="B101" t="str">
-        <v>불러오는 중…</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>checks</v>
       </c>
       <c r="B102" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B103" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B104" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B105" t="str">
-        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B106" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Subscribe</v>
       </c>
       <c r="B107" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B108" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Security</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B109" t="str">
-        <v>보안</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Conformance</v>
+        <v>Close</v>
       </c>
       <c r="B110" t="str">
-        <v>적합성</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Quality</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B111" t="str">
-        <v>품질</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>REPORT</v>
+        <v>Email address</v>
       </c>
       <c r="B112" t="str">
-        <v>보고서</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>FAIL</v>
+        <v>you@example.com</v>
       </c>
       <c r="B113" t="str">
-        <v>실패</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>checks</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B114" t="str">
-        <v>개 검사</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>(optional)</v>
       </c>
       <c r="B115" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B116" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ICC Profile Tool</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B117" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Powered by {lib}</v>
+        <v>Cancel</v>
       </c>
       <c r="B118" t="str">
-        <v>{lib} 기반</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="119">
@@ -1357,18 +1357,18 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B120" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Get notified about new releases</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B121" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="122">
@@ -1381,631 +1381,535 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B123" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Email address</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B124" t="str">
-        <v>이메일 주소</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>you@example.com</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B125" t="str">
-        <v>you@example.com</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B126" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>(optional)</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>(선택)</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Error:</v>
       </c>
       <c r="B129" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Cancel</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B130" t="str">
-        <v>취소</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Subscribe</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B131" t="str">
-        <v>구독</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B132" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B133" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Close</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B134" t="str">
-        <v>닫기</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Privacy notice</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B135" t="str">
-        <v>개인정보 처리방침</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B136" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B137" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B138" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B139" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B140" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Error:</v>
+        <v>ID</v>
       </c>
       <c r="B141" t="str">
-        <v>오류:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Convert to XML</v>
+        <v>Offset</v>
       </c>
       <c r="B142" t="str">
-        <v>XML로 변환</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Convert to JSON</v>
+        <v>Size</v>
       </c>
       <c r="B143" t="str">
-        <v>JSON으로 변환</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Convert to ICC</v>
+        <v>Pad</v>
       </c>
       <c r="B144" t="str">
-        <v>ICC로 변환</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Converting to XML…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B145" t="str">
-        <v>XML로 변환 중…</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Converting to JSON…</v>
+        <v>Type</v>
       </c>
       <c r="B146" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Converting to ICC…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B147" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Load ICC profile</v>
+        <v>(No content)</v>
       </c>
       <c r="B148" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>bytes</v>
       </c>
       <c r="B149" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile ID</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B150" t="str">
-        <v>프로파일 ID</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>No tags found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B151" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Tag Name</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B152" t="str">
-        <v>태그 이름</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ID</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B153" t="str">
-        <v>ID</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Offset</v>
+        <v>No validation output</v>
       </c>
       <c r="B154" t="str">
-        <v>오프셋</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Size</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B155" t="str">
-        <v>크기</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Pad</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B156" t="str">
-        <v>패딩</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B157" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Type</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B158" t="str">
-        <v>유형</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Array of {type}</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B159" t="str">
-        <v>{type} 배열</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>(No content)</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B160" t="str">
-        <v>(내용 없음)</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>bytes</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B161" t="str">
-        <v>바이트</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Loading full description…</v>
+        <v>Valid</v>
       </c>
       <c r="B162" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Could not load full description:</v>
+        <v>Warning</v>
       </c>
       <c r="B163" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error</v>
       </c>
       <c r="B164" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Unknown</v>
       </c>
       <c r="B165" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>No validation output</v>
+        <v>Pass</v>
       </c>
       <c r="B166" t="str">
-        <v>검증 출력 없음</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Profile is valid</v>
+        <v>Fail</v>
       </c>
       <c r="B167" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Profile has warning(s)</v>
+        <v>View in context</v>
       </c>
       <c r="B168" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Validation detail</v>
       </c>
       <c r="B169" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Critical validation error</v>
+        <v>Triggered by</v>
       </c>
       <c r="B170" t="str">
-        <v>심각한 검증 오류</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Unknown validation status</v>
+        <v>Field</v>
       </c>
       <c r="B171" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Current value</v>
       </c>
       <c r="B172" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B173" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Valid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B174" t="str">
-        <v>유효</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Warning</v>
+        <v>Invalid</v>
       </c>
       <c r="B175" t="str">
-        <v>경고</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Error</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B176" t="str">
-        <v>오류</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Unknown</v>
+        <v>Close</v>
       </c>
       <c r="B177" t="str">
-        <v>알 수 없음</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Pass</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B178" t="str">
-        <v>통과</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Fail</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>실패</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>View in context</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B180" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Validation detail</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>검증 세부 정보</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Triggered by</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B182" t="str">
-        <v>트리거 항목</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Field</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B183" t="str">
-        <v>항목</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Current value</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B184" t="str">
-        <v>현재 값</v>
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Required: 0</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>필수: 0</v>
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Expected: {value}</v>
+        <v>indent</v>
       </c>
       <c r="B186" t="str">
-        <v>예상: {value}</v>
+        <v>들여쓰기</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Invalid</v>
+        <v>sort keys</v>
       </c>
       <c r="B187" t="str">
-        <v>잘못됨</v>
+        <v>키 정렬</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B188" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v>Close</v>
-      </c>
-      <c r="B189" t="str">
-        <v>닫기</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>Loading XML editor…</v>
-      </c>
-      <c r="B190" t="str">
-        <v>XML 편집기 로드 중…</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>Loading JSON editor…</v>
-      </c>
-      <c r="B191" t="str">
-        <v>JSON 편집기 로드 중…</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B192" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B193" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>● unsaved XML edits</v>
-      </c>
-      <c r="B194" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>● unsaved JSON edits</v>
-      </c>
-      <c r="B195" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B196" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B197" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B198" t="str">
-        <v>들여쓰기</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B199" t="str">
-        <v>키 정렬</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B200" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B188"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B188"/>
+  <dimension ref="A1:B189"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -853,1063 +853,1071 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B57" t="str">
-        <v>평균</v>
+        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B58" t="str">
-        <v>P90</v>
+        <v>평균</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B59" t="str">
-        <v>최대</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B60" t="str">
-        <v>분석 중…</v>
+        <v>최대</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B61" t="str">
-        <v>분석</v>
+        <v>분석 중…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B62" t="str">
-        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B63" t="str">
-        <v>플롯</v>
+        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B64" t="str">
-        <v>원시 출력</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B65" t="str">
-        <v>XML</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B67" t="str">
-        <v>곡선</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B68" t="str">
-        <v>입력 곡선</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B69" t="str">
-        <v>출력 곡선</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B70" t="str">
-        <v>CLUT 이미지</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B71" t="str">
-        <v>색역 이미지</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B72" t="str">
-        <v>색도</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B73" t="str">
-        <v>산점도</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B74" t="str">
-        <v>톤 응답 곡선</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B75" t="str">
-        <v>곡선 표</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B76" t="str">
-        <v>표</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B77" t="str">
-        <v>데이터</v>
+        <v>표</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B78" t="str">
-        <v>평가</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B79" t="str">
-        <v>불러오는 중…</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B80" t="str">
-        <v>입력</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B81" t="str">
-        <v>출력</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B82" t="str">
-        <v>부동 소수점</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B83" t="str">
-        <v>격자점</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B84" t="str">
-        <v>정규화</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B85" t="str">
-        <v>사람용</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B86" t="str">
-        <v>장치 → PCS</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B87" t="str">
-        <v>PCS → 장치</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B88" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B89" t="str">
-        <v>불러오는 중…</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B90" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B91" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B92" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B93" t="str">
-        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B94" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B95" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B96" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B97" t="str">
-        <v>보안</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B98" t="str">
-        <v>적합성</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B99" t="str">
-        <v>품질</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B100" t="str">
-        <v>보고서</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B101" t="str">
-        <v>실패</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B102" t="str">
-        <v>개 검사</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B103" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B104" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B105" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B106" t="str">
-        <v>{lib} 기반</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B107" t="str">
-        <v>구독</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B108" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B109" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B110" t="str">
-        <v>닫기</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B111" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B112" t="str">
-        <v>이메일 주소</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B113" t="str">
-        <v>you@example.com</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B114" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B115" t="str">
-        <v>(선택)</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B116" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B117" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B118" t="str">
-        <v>취소</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B119" t="str">
-        <v>구독</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B120" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B121" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B122" t="str">
-        <v>닫기</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B123" t="str">
-        <v>개인정보 처리방침</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B124" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B125" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B126" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>오류:</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B130" t="str">
-        <v>XML로 변환</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B131" t="str">
-        <v>JSON으로 변환</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B132" t="str">
-        <v>ICC로 변환</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B133" t="str">
-        <v>XML로 변환 중…</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B134" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B135" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B136" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B137" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B138" t="str">
-        <v>프로파일 ID</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B139" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B140" t="str">
-        <v>태그 이름</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B141" t="str">
-        <v>ID</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B142" t="str">
-        <v>오프셋</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B143" t="str">
-        <v>크기</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B144" t="str">
-        <v>패딩</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B145" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B146" t="str">
-        <v>유형</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B147" t="str">
-        <v>{type} 배열</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B148" t="str">
-        <v>(내용 없음)</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B149" t="str">
-        <v>바이트</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B150" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B151" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B152" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B153" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B154" t="str">
-        <v>검증 출력 없음</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B155" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B156" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B157" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B158" t="str">
-        <v>심각한 검증 오류</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B159" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B160" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B161" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B162" t="str">
-        <v>유효</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B163" t="str">
-        <v>경고</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B164" t="str">
-        <v>오류</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B165" t="str">
-        <v>알 수 없음</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B166" t="str">
-        <v>통과</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B167" t="str">
-        <v>실패</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B168" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B169" t="str">
-        <v>검증 세부 정보</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B170" t="str">
-        <v>트리거 항목</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B171" t="str">
-        <v>항목</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B172" t="str">
-        <v>현재 값</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B173" t="str">
-        <v>필수: 0</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B174" t="str">
-        <v>예상: {value}</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B175" t="str">
-        <v>잘못됨</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B176" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B177" t="str">
-        <v>닫기</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B178" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B182" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B183" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B184" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B186" t="str">
-        <v>들여쓰기</v>
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B187" t="str">
-        <v>키 정렬</v>
+        <v>들여쓰기</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B188" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B188" t="str">
+      <c r="B189" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B188"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B189"/>
+  <dimension ref="A1:B236"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -413,1511 +413,1887 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Settings</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B2" t="str">
-        <v>설정</v>
+        <v>왕복 (PRMG)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Display</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B3" t="str">
-        <v>표시</v>
+        <v>참조 도구 iccRoundTrip과 동일하게 프로파일의 장치 큐브에 대해 왕복을 계산합니다. 왕복 1은 장치→PCS→장치 오차(ΔE*ab)이고, 왕복 2는 PCS 왕복 안정성을 측정합니다. PRMG 히스토그램은 Perceptual Reference Medium Gamut에 대한 상호 운용성을 나타냅니다.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Background</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B4" t="str">
-        <v>배경</v>
+        <v>MPE(색상) 태그 사용</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Language</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B5" t="str">
-        <v>언어</v>
+        <v>이 프로파일은 왕복할 수 없습니다. 이 지표에 필요한 장치↔PCS 변환이 없습니다(예: 단방향 또는 추상 프로파일).</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>System</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B6" t="str">
-        <v>시스템</v>
+        <v>왕복을 건너뜀: 장치 색 공간이 너무 넓어 평가할 수 없습니다(샘플이 너무 많음).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Light</v>
+        <v>Metric</v>
       </c>
       <c r="B7" t="str">
-        <v>밝게</v>
+        <v>지표</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dark</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B8" t="str">
-        <v>어둡게</v>
+        <v>왕복 1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>System default</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B9" t="str">
-        <v>시스템 기본값</v>
+        <v>왕복 2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Number format</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B10" t="str">
-        <v>숫자 형식</v>
+        <v>장치 → PCS → 장치</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Hexadecimal</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B11" t="str">
-        <v>16진수</v>
+        <v>PCS 왕복 안정성</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Decimal</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B12" t="str">
-        <v>10진수</v>
+        <v>최소 ΔE</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Help</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>도움말</v>
+        <v>평균 ΔE</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Contact</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>문의</v>
+        <v>최대 ΔE</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>User guide</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B15" t="str">
-        <v>사용자 가이드</v>
+        <v>최악 L, a, b</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Search guide</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B16" t="str">
-        <v>가이드 검색</v>
+        <v>지정된 색역</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Search the user guide</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>사용자 가이드 검색</v>
+        <v>지각 참조 매체 색역</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Previous match</v>
+        <v>Not specified</v>
       </c>
       <c r="B18" t="str">
-        <v>이전 검색 결과</v>
+        <v>지정 안 됨</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Next match</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B19" t="str">
-        <v>다음 검색 결과</v>
+        <v>평가 안 됨</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Close user guide</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B20" t="str">
-        <v>사용자 가이드 닫기</v>
+        <v>PRMG 상호 운용성</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B21" t="str">
-        <v>불러오는 중…</v>
+        <v>왕복 ΔE</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Count</v>
       </c>
       <c r="B22" t="str">
-        <v>사용자 가이드를 불러올 수 없습니다.</v>
+        <v>개수</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>None</v>
+        <v>Share</v>
       </c>
       <c r="B23" t="str">
-        <v>없음</v>
+        <v>비율</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Total</v>
       </c>
       <c r="B24" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>합계</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B25" t="str">
-        <v>ICC 프로파일을 업로드하여</v>
+        <v>PRMG 평가 안 됨</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>specification using the</v>
+        <v>Settings</v>
       </c>
       <c r="B26" t="str">
-        <v>사양을</v>
+        <v>설정</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>demo implementation.</v>
+        <v>Display</v>
       </c>
       <c r="B27" t="str">
-        <v>데모 구현으로 검증합니다.</v>
+        <v>표시</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Based on</v>
+        <v>Background</v>
       </c>
       <c r="B28" t="str">
-        <v/>
+        <v>배경</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>demo implementation</v>
+        <v>Language</v>
       </c>
       <c r="B29" t="str">
-        <v>데모 구현 기반</v>
+        <v>언어</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validating…</v>
+        <v>System</v>
       </c>
       <c r="B30" t="str">
-        <v>검증 중…</v>
+        <v>시스템</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Save ICC profile</v>
+        <v>Light</v>
       </c>
       <c r="B31" t="str">
-        <v>ICC 프로파일 저장</v>
+        <v>밝게</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Dark</v>
       </c>
       <c r="B32" t="str">
-        <v>● 변경됨 — 저장되지 않음</v>
+        <v>어둡게</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>System default</v>
       </c>
       <c r="B33" t="str">
-        <v>ICC 프로파일을 여기에 놓기</v>
+        <v>시스템 기본값</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>or</v>
+        <v>Number format</v>
       </c>
       <c r="B34" t="str">
-        <v>또는</v>
+        <v>숫자 형식</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Choose file</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B35" t="str">
-        <v>파일 선택</v>
+        <v>16진수</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>.icc and .icm files</v>
+        <v>Decimal</v>
       </c>
       <c r="B36" t="str">
-        <v>.icc 및 .icm 파일</v>
+        <v>10진수</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Header</v>
+        <v>Help</v>
       </c>
       <c r="B37" t="str">
-        <v>헤더</v>
+        <v>도움말</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Tags</v>
+        <v>Contact</v>
       </c>
       <c r="B38" t="str">
-        <v>태그</v>
+        <v>문의</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Validation</v>
+        <v>User guide</v>
       </c>
       <c r="B39" t="str">
-        <v>검증</v>
+        <v>사용자 가이드</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Analysis</v>
+        <v>Search guide</v>
       </c>
       <c r="B40" t="str">
-        <v>분석</v>
+        <v>가이드 검색</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B41" t="str">
-        <v>중립축 잉킹</v>
+        <v>사용자 가이드 검색</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Previous match</v>
       </c>
       <c r="B42" t="str">
-        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
+        <v>이전 검색 결과</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Next match</v>
       </c>
       <c r="B43" t="str">
-        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>다음 검색 결과</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Close user guide</v>
       </c>
       <c r="B44" t="str">
-        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
+        <v>사용자 가이드 닫기</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Rendering intent</v>
+        <v>Loading…</v>
       </c>
       <c r="B45" t="str">
-        <v>렌더링 의도</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>% ink</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B46" t="str">
-        <v>% 잉크</v>
+        <v>사용자 가이드를 불러올 수 없습니다.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Perceptual</v>
+        <v>None</v>
       </c>
       <c r="B47" t="str">
-        <v>지각적</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Relative Colorimetric</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B48" t="str">
-        <v>상대 색도</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Saturation</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B49" t="str">
-        <v>채도</v>
+        <v>ICC 프로파일을 업로드하여</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>specification using the</v>
       </c>
       <c r="B50" t="str">
-        <v>절대 색도</v>
+        <v>사양을</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Profile Statistics</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B51" t="str">
-        <v>프로파일 통계</v>
+        <v>데모 구현으로 검증합니다.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Based on</v>
       </c>
       <c r="B52" t="str">
-        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>demo implementation</v>
       </c>
       <c r="B53" t="str">
-        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
+        <v>데모 구현 기반</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Rendering intent</v>
+        <v>Validating…</v>
       </c>
       <c r="B54" t="str">
-        <v>렌더링 의도</v>
+        <v>검증 중…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B55" t="str">
-        <v>색역 부피 (ΔE³)</v>
+        <v>ICC 프로파일 저장</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Round-trip ΔE</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B56" t="str">
-        <v>왕복 ΔE</v>
+        <v>● 변경됨 — 저장되지 않음</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Profiles</v>
       </c>
       <c r="B57" t="str">
-        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>mean</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B58" t="str">
-        <v>평균</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>P90</v>
+        <v>Collapse</v>
       </c>
       <c r="B59" t="str">
-        <v>P90</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>max</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B60" t="str">
-        <v>최대</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysing…</v>
+        <v>Remove</v>
       </c>
       <c r="B61" t="str">
-        <v>분석 중…</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Analysis</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B62" t="str">
-        <v>분석</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>or use “Load Profiles” — files stay on your device.</v>
       </c>
       <c r="B63" t="str">
-        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Plot</v>
+        <v>Profile</v>
       </c>
       <c r="B64" t="str">
-        <v>플롯</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Raw Output</v>
+        <v>Compare</v>
       </c>
       <c r="B65" t="str">
-        <v>원시 출력</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>XML</v>
+        <v>Link</v>
       </c>
       <c r="B66" t="str">
-        <v>XML</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>JSON</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B67" t="str">
-        <v>JSON</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curves</v>
+        <v>Remove</v>
       </c>
       <c r="B68" t="str">
-        <v>곡선</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Input curves</v>
+        <v>No profile selected</v>
       </c>
       <c r="B69" t="str">
-        <v>입력 곡선</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Output curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B70" t="str">
-        <v>출력 곡선</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>CLUT image</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B71" t="str">
-        <v>CLUT 이미지</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Gamut image</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B72" t="str">
-        <v>색역 이미지</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B73" t="str">
-        <v>색도</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Scatter plot</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B74" t="str">
-        <v>산점도</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Tone response curve</v>
+        <v>Linking</v>
       </c>
       <c r="B75" t="str">
-        <v>톤 응답 곡선</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Curve table</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B76" t="str">
-        <v>곡선 표</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Tables</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B77" t="str">
-        <v>표</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Data</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B78" t="str">
-        <v>데이터</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Evaluate</v>
+        <v>OK</v>
       </c>
       <c r="B79" t="str">
-        <v>평가</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Loading…</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B80" t="str">
-        <v>불러오는 중…</v>
+        <v>ICC 프로파일을 여기에 놓기</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Input</v>
+        <v>or</v>
       </c>
       <c r="B81" t="str">
-        <v>입력</v>
+        <v>또는</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Output</v>
+        <v>Choose file</v>
       </c>
       <c r="B82" t="str">
-        <v>출력</v>
+        <v>파일 선택</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Floating point</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B83" t="str">
-        <v>부동 소수점</v>
+        <v>.icc 및 .icm 파일</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Grid point</v>
+        <v>Header</v>
       </c>
       <c r="B84" t="str">
-        <v>격자점</v>
+        <v>헤더</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Normalized</v>
+        <v>Tags</v>
       </c>
       <c r="B85" t="str">
-        <v>정규화</v>
+        <v>태그</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Human</v>
+        <v>Validation</v>
       </c>
       <c r="B86" t="str">
-        <v>사람용</v>
+        <v>검증</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Device → PCS</v>
+        <v>Analysis</v>
       </c>
       <c r="B87" t="str">
-        <v>장치 → PCS</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B88" t="str">
-        <v>PCS → 장치</v>
+        <v>중립축 잉킹</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>No CLUT grid</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B89" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading…</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B90" t="str">
-        <v>불러오는 중…</v>
+        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B91" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B92" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>% ink</v>
       </c>
       <c r="B93" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>% 잉크</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Perceptual</v>
       </c>
       <c r="B94" t="str">
-        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
+        <v>지각적</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B95" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>상대 색도</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Saturation</v>
       </c>
       <c r="B96" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>채도</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B97" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>절대 색도</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Security</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B98" t="str">
-        <v>보안</v>
+        <v>프로파일 통계</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Conformance</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B99" t="str">
-        <v>적합성</v>
+        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Quality</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B100" t="str">
-        <v>품질</v>
+        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>REPORT</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B101" t="str">
-        <v>보고서</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>FAIL</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B102" t="str">
-        <v>실패</v>
+        <v>색역 부피 (ΔE³)</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>checks</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B103" t="str">
-        <v>개 검사</v>
+        <v>왕복 ΔE</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B104" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>mean</v>
       </c>
       <c r="B105" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>평균</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool</v>
+        <v>P90</v>
       </c>
       <c r="B106" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Powered by {lib}</v>
+        <v>max</v>
       </c>
       <c r="B107" t="str">
-        <v>{lib} 기반</v>
+        <v>최대</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Subscribe</v>
+        <v>Analysing…</v>
       </c>
       <c r="B108" t="str">
-        <v>구독</v>
+        <v>분석 중…</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Analysis</v>
       </c>
       <c r="B109" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new releases</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B110" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Close</v>
+        <v>Plot</v>
       </c>
       <c r="B111" t="str">
-        <v>닫기</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Raw Output</v>
       </c>
       <c r="B112" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Email address</v>
+        <v>XML</v>
       </c>
       <c r="B113" t="str">
-        <v>이메일 주소</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>you@example.com</v>
+        <v>JSON</v>
       </c>
       <c r="B114" t="str">
-        <v>you@example.com</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Curves</v>
       </c>
       <c r="B115" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>(optional)</v>
+        <v>Input curves</v>
       </c>
       <c r="B116" t="str">
-        <v>(선택)</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Output curves</v>
       </c>
       <c r="B117" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B118" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Cancel</v>
+        <v>Gamut image</v>
       </c>
       <c r="B119" t="str">
-        <v>취소</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Subscribe</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B120" t="str">
-        <v>구독</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B121" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B122" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Close</v>
+        <v>Curve table</v>
       </c>
       <c r="B123" t="str">
-        <v>닫기</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Privacy notice</v>
+        <v>Tables</v>
       </c>
       <c r="B124" t="str">
-        <v>개인정보 처리방침</v>
+        <v>표</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Data</v>
       </c>
       <c r="B125" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B126" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Loading…</v>
       </c>
       <c r="B127" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Input</v>
       </c>
       <c r="B128" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Output</v>
       </c>
       <c r="B129" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Error:</v>
+        <v>Floating point</v>
       </c>
       <c r="B130" t="str">
-        <v>오류:</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to XML</v>
+        <v>Grid point</v>
       </c>
       <c r="B131" t="str">
-        <v>XML로 변환</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to JSON</v>
+        <v>Normalized</v>
       </c>
       <c r="B132" t="str">
-        <v>JSON으로 변환</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to ICC</v>
+        <v>Human</v>
       </c>
       <c r="B133" t="str">
-        <v>ICC로 변환</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to XML…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B134" t="str">
-        <v>XML로 변환 중…</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to JSON…</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B135" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to ICC…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B136" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Load ICC profile</v>
+        <v>Loading…</v>
       </c>
       <c r="B137" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B138" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Profile ID</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B139" t="str">
-        <v>프로파일 ID</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>No tags found.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B140" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Tag Name</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B141" t="str">
-        <v>태그 이름</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>ID</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B142" t="str">
-        <v>ID</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Offset</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B143" t="str">
-        <v>오프셋</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Size</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B144" t="str">
-        <v>크기</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Pad</v>
+        <v>Security</v>
       </c>
       <c r="B145" t="str">
-        <v>패딩</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Bytes changed since load</v>
+        <v>Conformance</v>
       </c>
       <c r="B146" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Type</v>
+        <v>Quality</v>
       </c>
       <c r="B147" t="str">
-        <v>유형</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Array of {type}</v>
+        <v>REPORT</v>
       </c>
       <c r="B148" t="str">
-        <v>{type} 배열</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>(No content)</v>
+        <v>FAIL</v>
       </c>
       <c r="B149" t="str">
-        <v>(내용 없음)</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>bytes</v>
+        <v>checks</v>
       </c>
       <c r="B150" t="str">
-        <v>바이트</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Loading full description…</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B151" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Could not load full description:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B152" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B153" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B154" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>No validation output</v>
+        <v>Subscribe</v>
       </c>
       <c r="B155" t="str">
-        <v>검증 출력 없음</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile is valid</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B156" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B157" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Close</v>
       </c>
       <c r="B158" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Critical validation error</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B159" t="str">
-        <v>심각한 검증 오류</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Unknown validation status</v>
+        <v>Email address</v>
       </c>
       <c r="B160" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>you@example.com</v>
       </c>
       <c r="B161" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>No warnings or errors found.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B162" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Valid</v>
+        <v>(optional)</v>
       </c>
       <c r="B163" t="str">
-        <v>유효</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Warning</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B164" t="str">
-        <v>경고</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Error</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B165" t="str">
-        <v>오류</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Unknown</v>
+        <v>Cancel</v>
       </c>
       <c r="B166" t="str">
-        <v>알 수 없음</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Pass</v>
+        <v>Subscribe</v>
       </c>
       <c r="B167" t="str">
-        <v>통과</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Fail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B168" t="str">
-        <v>실패</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>View in context</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B169" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Validation detail</v>
+        <v>Close</v>
       </c>
       <c r="B170" t="str">
-        <v>검증 세부 정보</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Triggered by</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B171" t="str">
-        <v>트리거 항목</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Field</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B172" t="str">
-        <v>항목</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Current value</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B173" t="str">
-        <v>현재 값</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Required: 0</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B174" t="str">
-        <v>필수: 0</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B175" t="str">
-        <v>예상: {value}</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Invalid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B176" t="str">
-        <v>잘못됨</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error:</v>
       </c>
       <c r="B177" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Close</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B178" t="str">
-        <v>닫기</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading XML editor…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B179" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B180" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B181" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B182" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B183" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B184" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B185" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B186" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>indent</v>
+        <v>No tags found.</v>
       </c>
       <c r="B187" t="str">
-        <v>들여쓰기</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>sort keys</v>
+        <v>Tag Name</v>
       </c>
       <c r="B188" t="str">
-        <v>키 정렬</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B189" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B190" t="str">
+        <v>오프셋</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B191" t="str">
+        <v>크기</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B192" t="str">
+        <v>패딩</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B193" t="str">
+        <v>로드 이후 바이트가 변경됨</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B194" t="str">
+        <v>유형</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B195" t="str">
+        <v>{type} 배열</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B196" t="str">
+        <v>(내용 없음)</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B197" t="str">
+        <v>바이트</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B198" t="str">
+        <v>전체 설명을 로드하는 중…</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B199" t="str">
+        <v>전체 설명을 로드할 수 없습니다:</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B200" t="str">
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B201" t="str">
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B202" t="str">
+        <v>검증 출력 없음</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B203" t="str">
+        <v>프로파일이 유효합니다</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B204" t="str">
+        <v>프로파일에 경고가 있습니다</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B205" t="str">
+        <v>프로파일이 규격을 준수하지 않습니다</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B206" t="str">
+        <v>심각한 검증 오류</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B207" t="str">
+        <v>알 수 없는 검증 상태</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B208" t="str">
+        <v>심각 — 검사용으로만 표시</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B209" t="str">
+        <v>경고나 오류를 찾지 못했습니다.</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B210" t="str">
+        <v>유효</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B211" t="str">
+        <v>경고</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B212" t="str">
+        <v>오류</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B213" t="str">
+        <v>알 수 없음</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B214" t="str">
+        <v>통과</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B215" t="str">
+        <v>실패</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B216" t="str">
+        <v>컨텍스트에서 보기</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B217" t="str">
+        <v>검증 세부 정보</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B218" t="str">
+        <v>트리거 항목</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B219" t="str">
+        <v>항목</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B220" t="str">
+        <v>현재 값</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B221" t="str">
+        <v>필수: 0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B222" t="str">
+        <v>예상: {value}</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B223" t="str">
+        <v>잘못됨</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B224" t="str">
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B225" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B226" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B227" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B228" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B229" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B230" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B231" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B232" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B233" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B234" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B235" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B189" t="str">
+      <c r="B236" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B236"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B236"/>
+  <dimension ref="A1:B319"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -605,1695 +605,2365 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Settings</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B26" t="str">
-        <v>설정</v>
+        <v>하나의 렌더링 의도에 대한 전체 프로파일 지표: 장치→PCS 변환이 둘러싸는 색역 부피 (ΔE*ab³)와 왕복 정확도 지표입니다. 렌더링 의도와 왕복 유형을 선택하면 표와 히스토그램이 그에 맞게 업데이트됩니다.</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Display</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B27" t="str">
-        <v>표시</v>
+        <v>왕복 유형</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Background</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>배경</v>
+        <v>이 왕복 유형에는 영향을 주지 않습니다</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Language</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B29" t="str">
-        <v>언어</v>
+        <v>이 왕복 유형은 이 프로파일에서 사용할 수 없습니다.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>System</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B30" t="str">
-        <v>시스템</v>
+        <v>왕복 ΔE 분포</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Light</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B31" t="str">
-        <v>밝게</v>
+        <v>평가 영역 안에 들어온 왕복 샘플이 없습니다.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dark</v>
+        <v>Std Dev</v>
       </c>
       <c r="B32" t="str">
-        <v>어둡게</v>
+        <v>표준편차</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>System default</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B33" t="str">
-        <v>시스템 기본값</v>
+        <v>상대 빈도</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Number format</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>숫자 형식</v>
+        <v>누적 빈도</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Hexadecimal</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B35" t="str">
-        <v>16진수</v>
+        <v>가로 배율</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Decimal</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B36" t="str">
-        <v>10진수</v>
+        <v>정수 ΔE</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Help</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B37" t="str">
-        <v>도움말</v>
+        <v>자동 배율</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Contact</v>
+        <v>Bins</v>
       </c>
       <c r="B38" t="str">
-        <v>문의</v>
+        <v>구간</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>User guide</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B39" t="str">
-        <v>사용자 가이드</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Search guide</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B40" t="str">
-        <v>가이드 검색</v>
+        <v>장치↔PCS 변환의 색상 조회 테이블(CLUT)을 하나의 이미지로 타일 형태로 배열한 것입니다. 볼 렌더링 의도 테이블을 선택하세요.</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Search the user guide</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B41" t="str">
-        <v>사용자 가이드 검색</v>
+        <v>이 프로파일에는 시각화할 CLUT 기반 장치↔PCS 테이블이 없습니다.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Previous match</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B42" t="str">
-        <v>이전 검색 결과</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Next match</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B43" t="str">
-        <v>다음 검색 결과</v>
+        <v>색역 태그의 색역 내/외 맵: PCS 색상이 재현 가능한 곳은 중립, 장치 색역을 벗어나는 곳은 빨강으로 표시됩니다.</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Close user guide</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B44" t="str">
-        <v>사용자 가이드 닫기</v>
+        <v>이 프로파일에는 시각화할 색역 태그가 없습니다.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Loading…</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B45" t="str">
-        <v>불러오는 중…</v>
+        <v>세로 배율</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Could not load the user guide.</v>
+        <v>X–Y</v>
       </c>
       <c r="B46" t="str">
-        <v>사용자 가이드를 불러올 수 없습니다.</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>None</v>
+        <v>Tone increase</v>
       </c>
       <c r="B47" t="str">
-        <v>없음</v>
+        <v>톤 증가</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B48" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>톤 증가(출력 − 입력)</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Show full dump</v>
       </c>
       <c r="B49" t="str">
-        <v>ICC 프로파일을 업로드하여</v>
+        <v>전체 덤프 표시</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>specification using the</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B50" t="str">
-        <v>사양을</v>
+        <v>성능을 위해 출력이 잘렸습니다.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>demo implementation.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B51" t="str">
-        <v>데모 구현으로 검증합니다.</v>
+        <v>색역 내 개요 (RT0)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Based on</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B52" t="str">
-        <v/>
+        <v>역변환 + 색역 (RT1)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>demo implementation</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B53" t="str">
-        <v>데모 구현 기반</v>
+        <v>재현성 (RT2)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Validating…</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B54" t="str">
-        <v>검증 중…</v>
+        <v>PRMG 상호운용성</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Save ICC profile</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B55" t="str">
-        <v>ICC 프로파일 저장</v>
+        <v>iccviz 개요: 장치 값 격자를 PCS로, 다시 장치로, 그리고 다시 PCS로 변환하여 두 PCS 결과 사이의 ΔE*ab를 측정합니다. 색역 내 안정성을 빠르게 확인합니다.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B56" t="str">
-        <v>● 변경됨 — 저장되지 않음</v>
+        <v>iccRoundTrip 왕복 1: 각 장치 색상의 PCS와 Lab → 장치 → Lab 왕복을 한 번 거친 후의 PCS 사이의 ΔE*ab. 역변환 정확도와 색역 매핑을 반영합니다.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profiles</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>iccRoundTrip 왕복 2: 첫 번째와 두 번째 왕복 사이의 ΔE*ab — 반복되는 PCS 왕복이 얼마나 안정적인지(재현성, 첫 왕복의 색역 클리핑과 무관)를 나타냅니다.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Show profile pool</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>iccRoundTrip PRMG: Perceptual Reference Medium Gamut 내의 PCS 색상을 한 번 왕복(Lab → 장치 → Lab)합니다. ΔE*ab 분포는 프로파일 간 상호운용성을 나타냅니다.</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Collapse</v>
+        <v>Settings</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>설정</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Load Profiles</v>
+        <v>Display</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>표시</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Remove</v>
+        <v>Background</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>배경</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Language</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>언어</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>or use “Load Profiles” — files stay on your device.</v>
+        <v>System</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>시스템</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile</v>
+        <v>Light</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>밝게</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Compare</v>
+        <v>Dark</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>어둡게</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Link</v>
+        <v>System default</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>시스템 기본값</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Number format</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>숫자 형식</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Remove</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>16진수</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>No profile selected</v>
+        <v>Decimal</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>10진수</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Help</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>도움말</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Contact</v>
       </c>
       <c r="B71" t="str">
-        <v/>
+        <v>문의</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>User guide</v>
       </c>
       <c r="B72" t="str">
-        <v/>
+        <v>사용자 가이드</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut comparison</v>
+        <v>Search guide</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>가이드 검색</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>사용자 가이드 검색</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Linking</v>
+        <v>Previous match</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>이전 검색 결과</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Next match</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>다음 검색 결과</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Close user guide</v>
       </c>
       <c r="B77" t="str">
-        <v/>
+        <v>사용자 가이드 닫기</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Loading…</v>
       </c>
       <c r="B78" t="str">
-        <v/>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>OK</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B79" t="str">
-        <v/>
+        <v>사용자 가이드를 불러올 수 없습니다.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>None</v>
       </c>
       <c r="B80" t="str">
-        <v>ICC 프로파일을 여기에 놓기</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>or</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B81" t="str">
-        <v>또는</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Choose file</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B82" t="str">
-        <v>파일 선택</v>
+        <v>ICC 프로파일을 업로드하여</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>.icc and .icm files</v>
+        <v>specification using the</v>
       </c>
       <c r="B83" t="str">
-        <v>.icc 및 .icm 파일</v>
+        <v>사양을</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Header</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B84" t="str">
-        <v>헤더</v>
+        <v>데모 구현으로 검증합니다.</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Tags</v>
+        <v>Based on</v>
       </c>
       <c r="B85" t="str">
-        <v>태그</v>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Validation</v>
+        <v>demo implementation</v>
       </c>
       <c r="B86" t="str">
-        <v>검증</v>
+        <v>데모 구현 기반</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Analysis</v>
+        <v>Validating…</v>
       </c>
       <c r="B87" t="str">
-        <v>분석</v>
+        <v>검증 중…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B88" t="str">
-        <v>중립축 잉킹</v>
+        <v>ICC 프로파일 저장</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B89" t="str">
-        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
+        <v>● 변경됨 — 저장되지 않음</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>프로파일</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B91" t="str">
-        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
+        <v>프로파일 풀 표시</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Rendering intent</v>
+        <v>Collapse</v>
       </c>
       <c r="B92" t="str">
-        <v>렌더링 의도</v>
+        <v>접기</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>% ink</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B93" t="str">
-        <v>% 잉크</v>
+        <v>프로파일 불러오기</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Perceptual</v>
+        <v>Remove</v>
       </c>
       <c r="B94" t="str">
-        <v>지각적</v>
+        <v>제거</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B95" t="str">
-        <v>상대 색도</v>
+        <v>여기에 ICC 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Saturation</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B96" t="str">
-        <v>채도</v>
+        <v>또는 이미지(TIFF/PNG/JPEG)를 놓아 내장된 프로파일을 추출하세요 — 파일은 사용자 장치에 그대로 남습니다.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>New from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>절대 색도</v>
+        <v>.cube에서 새로 만들기</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Statistics</v>
+        <v>Sort by name</v>
       </c>
       <c r="B98" t="str">
-        <v>프로파일 통계</v>
+        <v>이름순 정렬</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>A–Z</v>
       </c>
       <c r="B99" t="str">
-        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B100" t="str">
-        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
+        <v>.cube에서 새 프로파일</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Rendering intent</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B101" t="str">
-        <v>렌더링 의도</v>
+        <v>Adobe/Resolve의 .cube 3D LUT에서 ICC DeviceLink를 만듭니다. 결과는 풀에 추가되고 다운로드됩니다.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B102" t="str">
-        <v>색역 부피 (ΔE³)</v>
+        <v>.cube 파일 선택</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Round-trip ΔE</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B103" t="str">
-        <v>왕복 ΔE</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
-      </c>
-      <c r="B104" t="str">
-        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
+        <v>또는 여기에 놓거나 아래에 붙여넣으세요</v>
+      </c>
+    </row>
+    <row r="104" xml:space="preserve">
+      <c r="A104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
+      </c>
+      <c r="B104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>mean</v>
+        <v>Cancel</v>
       </c>
       <c r="B105" t="str">
-        <v>평균</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>P90</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B106" t="str">
-        <v>P90</v>
+        <v>DeviceLink 만들기</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>max</v>
+        <v>Creating…</v>
       </c>
       <c r="B107" t="str">
-        <v>최대</v>
+        <v>만드는 중…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Analysing…</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B108" t="str">
-        <v>분석 중…</v>
+        <v>해당 파일을 읽을 수 없습니다.</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Analysis</v>
+        <v>Profile</v>
       </c>
       <c r="B109" t="str">
-        <v>분석</v>
+        <v>프로파일</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Compare</v>
       </c>
       <c r="B110" t="str">
-        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
+        <v>비교</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Plot</v>
+        <v>Link</v>
       </c>
       <c r="B111" t="str">
-        <v>플롯</v>
+        <v>링크</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Raw Output</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B112" t="str">
-        <v>원시 출력</v>
+        <v>풀에서 이 탭으로 프로파일을 끌어다 놓으세요</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>XML</v>
+        <v>Remove</v>
       </c>
       <c r="B113" t="str">
-        <v>XML</v>
+        <v>제거</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>JSON</v>
+        <v>No profile selected</v>
       </c>
       <c r="B114" t="str">
-        <v>JSON</v>
+        <v>선택된 프로파일 없음</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B115" t="str">
-        <v>곡선</v>
+        <v>풀에서 프로파일을 '프로파일' 탭으로 끌어다 놓아 검사하세요.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Input curves</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B116" t="str">
-        <v>입력 곡선</v>
+        <v>아직 비교할 항목이 없습니다</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Output curves</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B117" t="str">
-        <v>출력 곡선</v>
+        <v>하나 이상의 프로파일을 '비교' 탭으로 끌어다 놓으세요.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>CLUT image</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B118" t="str">
-        <v>CLUT 이미지</v>
+        <v>색역 비교</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut image</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B119" t="str">
-        <v>색역 이미지</v>
+        <v>3D 색역 및 2D 슬라이스 보기가 여기에 추가됩니다. 누적:</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Chromaticity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B120" t="str">
-        <v>색도</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Scatter plot</v>
+        <v>Shell</v>
       </c>
       <c r="B121" t="str">
-        <v>산점도</v>
+        <v>셸</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Tone response curve</v>
+        <v>Wireframe</v>
       </c>
       <c r="B122" t="str">
-        <v>톤 응답 곡선</v>
+        <v>와이어프레임</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Curve table</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>곡선 표</v>
+        <v>불투명도</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tables</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>표</v>
+        <v>색상</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Data</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>데이터</v>
+        <v>단색</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Evaluate</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>평가</v>
+        <v>값 기준</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Loading…</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>불러오는 중…</v>
+        <v>색상(Hue) 기준</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Input</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>입력</v>
+        <v>회전</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Output</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>출력</v>
+        <v>턴테이블</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Floating point</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>부동 소수점</v>
+        <v>궤도</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Grid point</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>격자점</v>
+        <v>드래그 속도</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Normalized</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>정규화</v>
+        <v>롤</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Human</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>사람용</v>
+        <v>롤 속도</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Device → PCS</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>장치 → PCS</v>
+        <v>색역 생성 중…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>PCS → Device</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>PCS → 장치</v>
+        <v>색역 없음</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>No CLUT grid</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>표시/숨기기</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Loading…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>불러오는 중…</v>
+        <v>3D 색역 셸</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>2D 색역 슬라이스</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>평면</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>선택한 프로파일 중 색역을 도출할 장치→PCS 변환을 가진 것이 없습니다.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>링크</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Security</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>보안</v>
+        <v>DeviceLink 생성과 다중 프로파일 변환은 이후 단계에서 제공됩니다.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Conformance</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>적합성</v>
+        <v>더 많은 링크 메이커(DeviceLink, …)가 여기에 추가됩니다.</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Quality</v>
+        <v>V4 Display Maker</v>
       </c>
       <c r="B147" t="str">
-        <v>품질</v>
+        <v>V4 디스플레이 메이커</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>REPORT</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>보고서</v>
+        <v>V5 RGB 디스플레이와 V5 관찰자 프로파일을 여기에 끌어다 놓아 V4 디스플레이 프로파일을 만드세요.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>FAIL</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>실패</v>
+        <v>V5 RGB 디스플레이</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>checks</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>개 검사</v>
+        <v>디스플레이 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>V5 관찰자 (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>관찰자 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>V5 RGB 디스플레이도 관찰자도 아닌 프로파일은 무시되었습니다.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Powered by {lib}</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>{lib} 기반</v>
+        <v>V4 디스플레이 프로파일 만들기</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Subscribe</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>구독</v>
+        <v>프로파일 이름</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>만들기</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Get notified about new releases</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>만드는 중…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Close</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>닫기</v>
+        <v>'{name}'을(를) 만들었습니다 — 풀과 이 탭에 추가되었습니다.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Cancel</v>
       </c>
       <c r="B159" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Email address</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B160" t="str">
-        <v>이메일 주소</v>
+        <v>{n}개 파일을 불러오지 못했습니다</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>you@example.com</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B161" t="str">
-        <v>you@example.com</v>
+        <v>이 파일들은 ICC 프로파일이 아니므로 풀에 추가되지 않았습니다:</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>How will you use profiletool?</v>
+        <v>OK</v>
       </c>
       <c r="B162" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>확인</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>(optional)</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B163" t="str">
-        <v>(선택)</v>
+        <v>ICC 프로파일을 여기에 놓기</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>or</v>
       </c>
       <c r="B164" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>또는</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Choose file</v>
       </c>
       <c r="B165" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>파일 선택</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cancel</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B166" t="str">
-        <v>취소</v>
+        <v>.icc 및 .icm 파일</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Subscribe</v>
+        <v>Header</v>
       </c>
       <c r="B167" t="str">
-        <v>구독</v>
+        <v>헤더</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Tags</v>
       </c>
       <c r="B168" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>태그</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Validation</v>
       </c>
       <c r="B169" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>검증</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>Analysis</v>
       </c>
       <c r="B170" t="str">
-        <v>닫기</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Privacy notice</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B171" t="str">
-        <v>개인정보 처리방침</v>
+        <v>중립축 잉킹</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B172" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B173" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Please check the form and try again.</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B174" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B175" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Network error. Please try again.</v>
+        <v>% ink</v>
       </c>
       <c r="B176" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>% 잉크</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Error:</v>
+        <v>Perceptual</v>
       </c>
       <c r="B177" t="str">
-        <v>오류:</v>
+        <v>지각적</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Convert to XML</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B178" t="str">
-        <v>XML로 변환</v>
+        <v>상대 색도</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Convert to JSON</v>
+        <v>Saturation</v>
       </c>
       <c r="B179" t="str">
-        <v>JSON으로 변환</v>
+        <v>채도</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Convert to ICC</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B180" t="str">
-        <v>ICC로 변환</v>
+        <v>절대 색도</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Converting to XML…</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B181" t="str">
-        <v>XML로 변환 중…</v>
+        <v>프로파일 통계</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Converting to JSON…</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B182" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Converting to ICC…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B183" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Load ICC profile</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B184" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B185" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>색역 부피 (ΔE³)</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Profile ID</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B186" t="str">
-        <v>프로파일 ID</v>
+        <v>왕복 ΔE</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>No tags found.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B187" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Tag Name</v>
+        <v>mean</v>
       </c>
       <c r="B188" t="str">
-        <v>태그 이름</v>
+        <v>평균</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
       <c r="B189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Offset</v>
+        <v>max</v>
       </c>
       <c r="B190" t="str">
-        <v>오프셋</v>
+        <v>최대</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Size</v>
+        <v>Analysing…</v>
       </c>
       <c r="B191" t="str">
-        <v>크기</v>
+        <v>분석 중…</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Pad</v>
+        <v>Analysis</v>
       </c>
       <c r="B192" t="str">
-        <v>패딩</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B193" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Type</v>
+        <v>Plot</v>
       </c>
       <c r="B194" t="str">
-        <v>유형</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Array of {type}</v>
+        <v>Raw Output</v>
       </c>
       <c r="B195" t="str">
-        <v>{type} 배열</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>(No content)</v>
+        <v>XML</v>
       </c>
       <c r="B196" t="str">
-        <v>(내용 없음)</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>bytes</v>
+        <v>JSON</v>
       </c>
       <c r="B197" t="str">
-        <v>바이트</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Loading full description…</v>
+        <v>Curves</v>
       </c>
       <c r="B198" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not load full description:</v>
+        <v>Input curves</v>
       </c>
       <c r="B199" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Output curves</v>
       </c>
       <c r="B200" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B201" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>No validation output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B202" t="str">
-        <v>검증 출력 없음</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Profile is valid</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B203" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B204" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B205" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Critical validation error</v>
+        <v>Curve table</v>
       </c>
       <c r="B206" t="str">
-        <v>심각한 검증 오류</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Unknown validation status</v>
+        <v>Tables</v>
       </c>
       <c r="B207" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>표</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Data</v>
       </c>
       <c r="B208" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B209" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Valid</v>
+        <v>Loading…</v>
       </c>
       <c r="B210" t="str">
-        <v>유효</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Warning</v>
+        <v>Input</v>
       </c>
       <c r="B211" t="str">
-        <v>경고</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Error</v>
+        <v>Output</v>
       </c>
       <c r="B212" t="str">
-        <v>오류</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Unknown</v>
+        <v>Floating point</v>
       </c>
       <c r="B213" t="str">
-        <v>알 수 없음</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Pass</v>
+        <v>Grid point</v>
       </c>
       <c r="B214" t="str">
-        <v>통과</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Fail</v>
+        <v>Normalized</v>
       </c>
       <c r="B215" t="str">
-        <v>실패</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>View in context</v>
+        <v>Human</v>
       </c>
       <c r="B216" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Validation detail</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B217" t="str">
-        <v>검증 세부 정보</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Triggered by</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B218" t="str">
-        <v>트리거 항목</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Field</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B219" t="str">
-        <v>항목</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Current value</v>
+        <v>Loading…</v>
       </c>
       <c r="B220" t="str">
-        <v>현재 값</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Required: 0</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B221" t="str">
-        <v>필수: 0</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B222" t="str">
-        <v>예상: {value}</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invalid</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B223" t="str">
-        <v>잘못됨</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B224" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Close</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B225" t="str">
-        <v>닫기</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Loading XML editor…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B226" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B227" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Security</v>
       </c>
       <c r="B228" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Conformance</v>
       </c>
       <c r="B229" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Quality</v>
       </c>
       <c r="B230" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>REPORT</v>
       </c>
       <c r="B231" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>FAIL</v>
       </c>
       <c r="B232" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>checks</v>
       </c>
       <c r="B233" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>indent</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B234" t="str">
-        <v>들여쓰기</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>sort keys</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B235" t="str">
-        <v>키 정렬</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B236" t="str">
+        <v>ICC 프로파일 도구</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B237" t="str">
+        <v>{lib} 기반</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B238" t="str">
+        <v>구독</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B239" t="str">
+        <v>profiletool 새 릴리스 알림 받기</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B240" t="str">
+        <v>새 릴리스 알림 받기</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B241" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B242" t="str">
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B243" t="str">
+        <v>이메일 주소</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B244" t="str">
+        <v>you@example.com</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B245" t="str">
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B246" t="str">
+        <v>(선택)</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B247" t="str">
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B248" t="str">
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B249" t="str">
+        <v>취소</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B250" t="str">
+        <v>구독</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B251" t="str">
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B252" t="str">
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B253" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B254" t="str">
+        <v>개인정보 처리방침</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B255" t="str">
+        <v>유효한 이메일 주소를 입력하세요.</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B256" t="str">
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B257" t="str">
+        <v>양식을 확인하고 다시 시도하세요.</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B258" t="str">
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B259" t="str">
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B260" t="str">
+        <v>오류:</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B261" t="str">
+        <v>XML로 변환</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B262" t="str">
+        <v>JSON으로 변환</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B263" t="str">
+        <v>ICC로 변환</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B264" t="str">
+        <v>XML로 변환 중…</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B265" t="str">
+        <v>JSON으로 변환 중…</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B266" t="str">
+        <v>ICC로 변환 중…</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B267" t="str">
+        <v>ICC 프로파일 로드</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B268" t="str">
+        <v>ICC 프로파일 파일용 드롭 영역</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B269" t="str">
+        <v>프로파일 ID</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B270" t="str">
+        <v>태그를 찾을 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B271" t="str">
+        <v>태그 이름</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B272" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B273" t="str">
+        <v>오프셋</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B274" t="str">
+        <v>크기</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B275" t="str">
+        <v>패딩</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B276" t="str">
+        <v>로드 이후 바이트가 변경됨</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B277" t="str">
+        <v>유형</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B278" t="str">
+        <v>{type} 배열</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B279" t="str">
+        <v>(내용 없음)</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B280" t="str">
+        <v>바이트</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B281" t="str">
+        <v>전체 설명을 로드하는 중…</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B282" t="str">
+        <v>전체 설명을 로드할 수 없습니다:</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B283" t="str">
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B284" t="str">
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B285" t="str">
+        <v>검증 출력 없음</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B286" t="str">
+        <v>프로파일이 유효합니다</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B287" t="str">
+        <v>프로파일에 경고가 있습니다</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B288" t="str">
+        <v>프로파일이 규격을 준수하지 않습니다</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B289" t="str">
+        <v>심각한 검증 오류</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B290" t="str">
+        <v>알 수 없는 검증 상태</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B291" t="str">
+        <v>심각 — 검사용으로만 표시</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B292" t="str">
+        <v>경고나 오류를 찾지 못했습니다.</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B293" t="str">
+        <v>유효</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B294" t="str">
+        <v>경고</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B295" t="str">
+        <v>오류</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B296" t="str">
+        <v>알 수 없음</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B297" t="str">
+        <v>통과</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B298" t="str">
+        <v>실패</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B299" t="str">
+        <v>컨텍스트에서 보기</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B300" t="str">
+        <v>검증 세부 정보</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B301" t="str">
+        <v>트리거 항목</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B302" t="str">
+        <v>항목</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B303" t="str">
+        <v>현재 값</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B304" t="str">
+        <v>필수: 0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B305" t="str">
+        <v>예상: {value}</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B306" t="str">
+        <v>잘못됨</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B307" t="str">
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B308" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B309" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B310" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B311" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B312" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B313" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B314" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B315" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B316" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B317" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B318" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B236" t="str">
+      <c r="B319" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B236"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B319"/>
+  <dimension ref="A1:B413"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Link</v>
+        <v>Combine</v>
       </c>
       <c r="B111" t="str">
         <v>링크</v>
@@ -1299,1671 +1299,2423 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B112" t="str">
-        <v>풀에서 이 탭으로 프로파일을 끌어다 놓으세요</v>
+        <v>스펙트럴</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B113" t="str">
-        <v>제거</v>
+        <v>풀에서 이 탭으로 프로파일을 끌어다 놓으세요</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B114" t="str">
-        <v>선택된 프로파일 없음</v>
+        <v>제거</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B115" t="str">
-        <v>풀에서 프로파일을 '프로파일' 탭으로 끌어다 놓아 검사하세요.</v>
+        <v>선택된 프로파일 없음</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B116" t="str">
-        <v>아직 비교할 항목이 없습니다</v>
+        <v>풀에서 프로파일을 '프로파일' 탭으로 끌어다 놓아 검사하세요.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B117" t="str">
-        <v>하나 이상의 프로파일을 '비교' 탭으로 끌어다 놓으세요.</v>
+        <v>아직 비교할 항목이 없습니다</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B118" t="str">
-        <v>색역 비교</v>
+        <v>하나 이상의 프로파일을 '비교' 탭으로 끌어다 놓으세요.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B119" t="str">
-        <v>3D 색역 및 2D 슬라이스 보기가 여기에 추가됩니다. 누적:</v>
+        <v>색역 비교</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B120" t="str">
-        <v>렌더링 의도</v>
+        <v>3D 색역 및 2D 슬라이스 보기가 여기에 추가됩니다. 누적:</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B121" t="str">
-        <v>셸</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B122" t="str">
-        <v>와이어프레임</v>
+        <v>셸</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Wireframe</v>
       </c>
       <c r="B123" t="str">
-        <v>불투명도</v>
+        <v>와이어프레임</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B124" t="str">
-        <v>색상</v>
+        <v>축 번호</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Opacity</v>
       </c>
       <c r="B125" t="str">
-        <v>단색</v>
+        <v>불투명도</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Colour</v>
       </c>
       <c r="B126" t="str">
-        <v>값 기준</v>
+        <v>색상</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Solid</v>
       </c>
       <c r="B127" t="str">
-        <v>색상(Hue) 기준</v>
+        <v>단색</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>By value</v>
       </c>
       <c r="B128" t="str">
-        <v>회전</v>
+        <v>값 기준</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>By hue</v>
       </c>
       <c r="B129" t="str">
-        <v>턴테이블</v>
+        <v>색상(Hue) 기준</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>Rotation</v>
       </c>
       <c r="B130" t="str">
-        <v>궤도</v>
+        <v>회전</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B131" t="str">
-        <v>드래그 속도</v>
+        <v>턴테이블</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Orbit</v>
       </c>
       <c r="B132" t="str">
-        <v>롤</v>
+        <v>궤도</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Drag speed</v>
       </c>
       <c r="B133" t="str">
-        <v>롤 속도</v>
+        <v>드래그 속도</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Roll</v>
       </c>
       <c r="B134" t="str">
-        <v>색역 생성 중…</v>
+        <v>롤</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Roll speed</v>
       </c>
       <c r="B135" t="str">
-        <v>색역 없음</v>
+        <v>롤 속도</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B136" t="str">
-        <v>표시/숨기기</v>
+        <v>색역 생성 중…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>no gamut</v>
       </c>
       <c r="B137" t="str">
-        <v>3D 색역 셸</v>
+        <v>색역 없음</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Show / hide</v>
       </c>
       <c r="B138" t="str">
-        <v>2D 색역 슬라이스</v>
+        <v>표시/숨기기</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B139" t="str">
-        <v>평면</v>
+        <v>3D 색역 셸</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>2D 색역 슬라이스</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>Plane</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>평면</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>a*</v>
       </c>
       <c r="B143" t="str">
-        <v>선택한 프로파일 중 색역을 도출할 장치→PCS 변환을 가진 것이 없습니다.</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>b*</v>
       </c>
       <c r="B144" t="str">
-        <v>링크</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B145" t="str">
-        <v>DeviceLink 생성과 다중 프로파일 변환은 이후 단계에서 제공됩니다.</v>
+        <v>선택한 프로파일 중 색역을 도출할 장치→PCS 변환을 가진 것이 없습니다.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>Linking</v>
       </c>
       <c r="B146" t="str">
-        <v>더 많은 링크 메이커(DeviceLink, …)가 여기에 추가됩니다.</v>
+        <v>링크</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>V4 Display Maker</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B147" t="str">
-        <v>V4 디스플레이 메이커</v>
+        <v>DeviceLink 생성과 다중 프로파일 변환은 이후 단계에서 제공됩니다.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B148" t="str">
-        <v>V5 RGB 디스플레이와 V5 관찰자 프로파일을 여기에 끌어다 놓아 V4 디스플레이 프로파일을 만드세요.</v>
+        <v>더 많은 링크 메이커(DeviceLink, …)가 여기에 추가됩니다.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>Observer Change</v>
       </c>
       <c r="B149" t="str">
-        <v>V5 RGB 디스플레이</v>
+        <v>V4 디스플레이 메이커</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B150" t="str">
-        <v>디스플레이 프로파일을 놓으세요</v>
+        <v>V5 RGB 디스플레이와 V5 관찰자 프로파일을 여기에 끌어다 놓아 V4 디스플레이 프로파일을 만드세요.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B151" t="str">
-        <v>V5 관찰자 (PCC)</v>
+        <v>V5 RGB 디스플레이</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B152" t="str">
-        <v>관찰자 프로파일을 놓으세요</v>
+        <v>디스플레이 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B153" t="str">
-        <v>V5 RGB 디스플레이도 관찰자도 아닌 프로파일은 무시되었습니다.</v>
+        <v>V5 관찰자 (PCC)</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B154" t="str">
-        <v>V4 디스플레이 프로파일 만들기</v>
+        <v>관찰자 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B155" t="str">
-        <v>프로파일 이름</v>
+        <v>V5 RGB 디스플레이도 관찰자도 아닌 프로파일은 무시되었습니다.</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B156" t="str">
-        <v>만들기</v>
+        <v>V4 디스플레이 프로파일 만들기</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Profile name</v>
       </c>
       <c r="B157" t="str">
-        <v>만드는 중…</v>
+        <v>프로파일 이름</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Create</v>
       </c>
       <c r="B158" t="str">
-        <v>'{name}'을(를) 만들었습니다 — 풀과 이 탭에 추가되었습니다.</v>
+        <v>만들기</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Cancel</v>
+        <v>Making…</v>
       </c>
       <c r="B159" t="str">
-        <v>취소</v>
+        <v>만드는 중…</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B160" t="str">
-        <v>{n}개 파일을 불러오지 못했습니다</v>
+        <v>'{name}'을(를) 만들었습니다 — 풀과 이 탭에 추가되었습니다.</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B161" t="str">
-        <v>이 파일들은 ICC 프로파일이 아니므로 풀에 추가되지 않았습니다:</v>
+        <v>링크 파이프라인</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>OK</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B162" t="str">
-        <v>확인</v>
+        <v>프로파일 체인을 구성한 다음 DeviceLink를 만들거나, 이미지를 변환하거나, 색상 데이터셋을 변환하세요.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Done</v>
       </c>
       <c r="B163" t="str">
-        <v>ICC 프로파일을 여기에 놓기</v>
+        <v>완료</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>or</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B164" t="str">
-        <v>또는</v>
+        <v>변환할 이미지를 드롭하세요 (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Choose file</v>
+        <v>Checking image…</v>
       </c>
       <c r="B165" t="str">
-        <v>파일 선택</v>
+        <v>이미지 확인 중…</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>.icc and .icm files</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B166" t="str">
-        <v>.icc 및 .icm 파일</v>
+        <v>지원되지 않는 이미지입니다 (TIFF, PNG 또는 JPEG).</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Header</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B167" t="str">
-        <v>헤더</v>
+        <v>이미지가 너무 큽니다 ({mp} MP, 제한 {max} MP).</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Tags</v>
+        <v>Transform Image</v>
       </c>
       <c r="B168" t="str">
-        <v>태그</v>
+        <v>이미지 변환</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation</v>
+        <v>Transforming…</v>
       </c>
       <c r="B169" t="str">
-        <v>검증</v>
+        <v>변환 중…</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Analysis</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B170" t="str">
-        <v>분석</v>
+        <v>체인을 시작하려면 프로파일을 드롭하세요</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>removed</v>
       </c>
       <c r="B171" t="str">
-        <v>중립축 잉킹</v>
+        <v>제거됨</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Move earlier</v>
       </c>
       <c r="B172" t="str">
-        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
+        <v>앞으로 이동</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Move later</v>
       </c>
       <c r="B173" t="str">
-        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>뒤로 이동</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Move up</v>
       </c>
       <c r="B174" t="str">
-        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
+        <v>위로 이동</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent</v>
+        <v>Move down</v>
       </c>
       <c r="B175" t="str">
-        <v>렌더링 의도</v>
+        <v>아래로 이동</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>% ink</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B176" t="str">
-        <v>% 잉크</v>
+        <v>렌더링 인텐트 (전체)</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Perceptual</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B177" t="str">
-        <v>지각적</v>
+        <v>이 변환의 렌더링 인텐트</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B178" t="str">
-        <v>상대 색도</v>
+        <v>변환마다 렌더링 인텐트가 다릅니다</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Saturation</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B179" t="str">
-        <v>채도</v>
+        <v>체인 방향 전환 (첫 변환을 반전시키고 체인 전체에 반영됩니다)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B180" t="str">
-        <v>절대 색도</v>
+        <v>체인에 포함된 프로파일이 풀에서 제거되었습니다 — 계속하려면 제거하세요.</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Profile Statistics</v>
+        <v>Chain</v>
       </c>
       <c r="B181" t="str">
-        <v>프로파일 통계</v>
+        <v>체인</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B182" t="str">
-        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
+        <v>체인을 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B183" t="str">
-        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
+        <v>체인 확인 중…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Rendering intent</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B184" t="str">
-        <v>렌더링 의도</v>
+        <v>체인이 연결되지 않습니다 ({detail}).</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B185" t="str">
-        <v>색역 부피 (ΔE³)</v>
+        <v>프로파일 {n}이(가) 이전 단계와 연결되지 않습니다 ({detail}).</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B186" t="str">
-        <v>왕복 ΔE</v>
+        <v>이미지를 처리하기 전에 체인을 수정하세요</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Clear</v>
       </c>
       <c r="B187" t="str">
-        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
+        <v>지우기</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>mean</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B188" t="str">
-        <v>평균</v>
+        <v>DeviceLink 만들기</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>P90</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B189" t="str">
-        <v>P90</v>
+        <v>DeviceLink 이름</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>max</v>
+        <v>Making…</v>
       </c>
       <c r="B190" t="str">
-        <v>최대</v>
+        <v>생성 중…</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Analysing…</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B191" t="str">
-        <v>분석 중…</v>
+        <v>"{name}" 생성됨 — 풀과 이 탭에 추가되었습니다.</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Analysis</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B192" t="str">
-        <v>분석</v>
+        <v>{src} 이미지를 드롭하면 {dst}(으)로 변환됩니다 — 결과는 다운로드되며 저장되지 않습니다.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B193" t="str">
-        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
+        <v>이미지를 처리하려면 체인을 구성하세요</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Plot</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B194" t="str">
-        <v>플롯</v>
+        <v>이 체인은 이미지 색공간에서 시작하고 끝나지 않습니다</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Raw Output</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B195" t="str">
-        <v>원시 출력</v>
+        <v>변환된 이미지를 저장했습니다.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>XML</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B196" t="str">
-        <v>XML</v>
+        <v>색상 데이터셋을 드롭하세요 (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>JSON</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B197" t="str">
-        <v>JSON</v>
+        <v>해당 파일을 읽을 수 없습니다.</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Curves</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B198" t="str">
-        <v>곡선</v>
+        <v>데이터 파일이 너무 큽니다.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Input curves</v>
+        <v>Transform Data</v>
       </c>
       <c r="B199" t="str">
-        <v>입력 곡선</v>
+        <v>데이터 변환</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Output curves</v>
+        <v>Transforming…</v>
       </c>
       <c r="B200" t="str">
-        <v>출력 곡선</v>
+        <v>변환 중…</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>CLUT image</v>
+        <v>Prefer</v>
       </c>
       <c r="B201" t="str">
-        <v>CLUT 이미지</v>
+        <v>선호</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Gamut image</v>
+        <v>Observer</v>
       </c>
       <c r="B202" t="str">
-        <v>색역 이미지</v>
+        <v>관측자</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Chromaticity</v>
+        <v>Illuminant</v>
       </c>
       <c r="B203" t="str">
-        <v>색도</v>
+        <v>광원</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Scatter plot</v>
+        <v>Condition</v>
       </c>
       <c r="B204" t="str">
-        <v>산점도</v>
+        <v>조건</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Tone response curve</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B205" t="str">
-        <v>톤 응답 곡선</v>
+        <v>중복 {n}건 필터링</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Curve table</v>
+        <v>median</v>
       </c>
       <c r="B206" t="str">
-        <v>곡선 표</v>
+        <v>중앙값</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Tables</v>
+        <v>mean</v>
       </c>
       <c r="B207" t="str">
-        <v>표</v>
+        <v>평균값</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Data</v>
+        <v>patches</v>
       </c>
       <c r="B208" t="str">
-        <v>데이터</v>
+        <v>패치</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Evaluate</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B209" t="str">
-        <v>평가</v>
+        <v>중복 {n}건</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Loading…</v>
+        <v>Transform result</v>
       </c>
       <c r="B210" t="str">
-        <v>불러오는 중…</v>
+        <v>변환 결과</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Input</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B211" t="str">
-        <v>입력</v>
+        <v>{src} → {dst} · 패치 {n}개</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Output</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B212" t="str">
-        <v>출력</v>
+        <v>전체 {total}건 중 처음 {shown}건 표시 중 — 저장하면 전체가 기록됩니다.</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Floating point</v>
+        <v>Save as</v>
       </c>
       <c r="B213" t="str">
-        <v>부동 소수점</v>
+        <v>다른 이름으로 저장</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Grid point</v>
+        <v>Save</v>
       </c>
       <c r="B214" t="str">
-        <v>격자점</v>
+        <v>저장</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Normalized</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B215" t="str">
-        <v>정규화</v>
+        <v>변환 반전</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Human</v>
+        <v>Inverting…</v>
       </c>
       <c r="B216" t="str">
-        <v>사람용</v>
+        <v>반전 중…</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Device → PCS</v>
+        <v>Invert</v>
       </c>
       <c r="B217" t="str">
-        <v>장치 → PCS</v>
+        <v>반전</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>PCS → Device</v>
+        <v>last stage</v>
       </c>
       <c r="B218" t="str">
-        <v>PCS → 장치</v>
+        <v>마지막 단계</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>No CLUT grid</v>
+        <v>first stage</v>
       </c>
       <c r="B219" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>첫 단계</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Loading…</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B220" t="str">
-        <v>불러오는 중…</v>
+        <v>{in} 데이터 → {out} 검색</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B221" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>반전에는 2–3개 프로파일로 이루어진 체인이 필요합니다</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Invalid profile URL:</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B222" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>데이터셋은 {in}이어야 합니다. 역검색은 {out}과 패치별 역변환 가능성 비용을 산출합니다.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B223" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>ΔE 비용</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B224" t="str">
-        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
+        <v>이 이미지에는 내장된 ICC 프로파일이 있습니다.</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B225" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>추출 후 체인에 추가</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Extracting…</v>
       </c>
       <c r="B226" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>추출 중…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Dismiss</v>
       </c>
       <c r="B227" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Security</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B228" t="str">
-        <v>보안</v>
+        <v>내장된 프로파일을 추출했습니다 — 풀에 추가되고 체인의 첫 번째 자리에 배치되었습니다.</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Conformance</v>
+        <v>Image output options</v>
       </c>
       <c r="B229" t="str">
-        <v>적합성</v>
+        <v>이미지 출력 옵션</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Quality</v>
+        <v>Encoding</v>
       </c>
       <c r="B230" t="str">
-        <v>품질</v>
+        <v>인코딩</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>REPORT</v>
+        <v>Same as source</v>
       </c>
       <c r="B231" t="str">
-        <v>보고서</v>
+        <v>원본과 동일</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>FAIL</v>
+        <v>8-bit</v>
       </c>
       <c r="B232" t="str">
-        <v>실패</v>
+        <v>8비트</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>checks</v>
+        <v>16-bit</v>
       </c>
       <c r="B233" t="str">
-        <v>개 검사</v>
+        <v>16비트</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B234" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>부동소수점 (32비트)</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Compression</v>
       </c>
       <c r="B235" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>압축</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B236" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Powered by {lib}</v>
+        <v>Planar</v>
       </c>
       <c r="B237" t="str">
-        <v>{lib} 기반</v>
+        <v>플레이너</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Subscribe</v>
+        <v>Composite</v>
       </c>
       <c r="B238" t="str">
-        <v>구독</v>
+        <v>컴포지트</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Separated</v>
       </c>
       <c r="B239" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>분리</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Get notified about new releases</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B240" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>CMM 보간</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Close</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B241" t="str">
-        <v>닫기</v>
+        <v>사면체</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Linear</v>
       </c>
       <c r="B242" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>선형</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Email address</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B243" t="str">
-        <v>이메일 주소</v>
+        <v>ICC 포함</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>you@example.com</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B244" t="str">
-        <v>you@example.com</v>
+        <v>인코딩, 압축, 플레이너 방식은 저장되는 TIFF에 반영됩니다. TIFF 전용 옵션(부동소수점, LZW/ZIP, 분리)을 설정하지 않으면 RGB/Gray 출력은 PNG로 유지됩니다.</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B245" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>스펙트럴 TIFF 조합</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>(optional)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B246" t="str">
-        <v>(선택)</v>
+        <v>단일 채널 스펙트럴 이미지를 채널 순서대로 드롭하면 하나의 다중 채널 TIFF로 조합됩니다.</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B247" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>스펙트럴 이미지를 여기에 드롭하세요 (또는 클릭하여 선택)</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ch</v>
       </c>
       <c r="B248" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B249" t="str">
-        <v>취소</v>
+        <v>조합 후 저장</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Subscribe</v>
+        <v>Assembling…</v>
       </c>
       <c r="B250" t="str">
-        <v>구독</v>
+        <v>조합 중…</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B251" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>{n}개 채널을 조합했습니다.</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B252" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>이미지로 인식되는 파일이 없습니다 (TIFF, PNG 또는 JPEG).</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B253" t="str">
-        <v>닫기</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Privacy notice</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B254" t="str">
-        <v>개인정보 처리방침</v>
+        <v>{n}개 파일을 불러오지 못했습니다</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B255" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>이 파일들은 ICC 프로파일이 아니므로 풀에 추가되지 않았습니다:</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>OK</v>
       </c>
       <c r="B256" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>확인</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B257" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>ICC 프로파일을 여기에 놓기</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>or</v>
       </c>
       <c r="B258" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>또는</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Choose file</v>
       </c>
       <c r="B259" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>파일 선택</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Error:</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B260" t="str">
-        <v>오류:</v>
+        <v>.icc 및 .icm 파일</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Convert to XML</v>
+        <v>Header</v>
       </c>
       <c r="B261" t="str">
-        <v>XML로 변환</v>
+        <v>헤더</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Convert to JSON</v>
+        <v>Tags</v>
       </c>
       <c r="B262" t="str">
-        <v>JSON으로 변환</v>
+        <v>태그</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Convert to ICC</v>
+        <v>Validation</v>
       </c>
       <c r="B263" t="str">
-        <v>ICC로 변환</v>
+        <v>검증</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Converting to XML…</v>
+        <v>Analysis</v>
       </c>
       <c r="B264" t="str">
-        <v>XML로 변환 중…</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Converting to JSON…</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B265" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>중립축 잉킹</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B266" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Load ICC profile</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B267" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B268" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Profile ID</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B269" t="str">
-        <v>프로파일 ID</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>No tags found.</v>
+        <v>% ink</v>
       </c>
       <c r="B270" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>% 잉크</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Tag Name</v>
+        <v>Perceptual</v>
       </c>
       <c r="B271" t="str">
-        <v>태그 이름</v>
+        <v>지각적</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>ID</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>ID</v>
+        <v>상대 색도</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Offset</v>
+        <v>Saturation</v>
       </c>
       <c r="B273" t="str">
-        <v>오프셋</v>
+        <v>채도</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Size</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B274" t="str">
-        <v>크기</v>
+        <v>절대 색도</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Pad</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B275" t="str">
-        <v>패딩</v>
+        <v>프로파일 통계</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Bytes changed since load</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B276" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Type</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B277" t="str">
-        <v>유형</v>
+        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Array of {type}</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B278" t="str">
-        <v>{type} 배열</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>(No content)</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B279" t="str">
-        <v>(내용 없음)</v>
+        <v>색역 부피 (ΔE³)</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>bytes</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B280" t="str">
-        <v>바이트</v>
+        <v>왕복 ΔE</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Loading full description…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B281" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Could not load full description:</v>
+        <v>mean</v>
       </c>
       <c r="B282" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>평균</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>P90</v>
       </c>
       <c r="B283" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>max</v>
       </c>
       <c r="B284" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>최대</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>No validation output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B285" t="str">
-        <v>검증 출력 없음</v>
+        <v>분석 중…</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Profile is valid</v>
+        <v>Analysis</v>
       </c>
       <c r="B286" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B287" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Plot</v>
       </c>
       <c r="B288" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Critical validation error</v>
+        <v>Raw Output</v>
       </c>
       <c r="B289" t="str">
-        <v>심각한 검증 오류</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Unknown validation status</v>
+        <v>XML</v>
       </c>
       <c r="B290" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>JSON</v>
       </c>
       <c r="B291" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Curves</v>
       </c>
       <c r="B292" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Valid</v>
+        <v>Input curves</v>
       </c>
       <c r="B293" t="str">
-        <v>유효</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Warning</v>
+        <v>Output curves</v>
       </c>
       <c r="B294" t="str">
-        <v>경고</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Error</v>
+        <v>CLUT image</v>
       </c>
       <c r="B295" t="str">
-        <v>오류</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Unknown</v>
+        <v>Gamut image</v>
       </c>
       <c r="B296" t="str">
-        <v>알 수 없음</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Pass</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B297" t="str">
-        <v>통과</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Fail</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B298" t="str">
-        <v>실패</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>View in context</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B299" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Validation detail</v>
+        <v>Curve table</v>
       </c>
       <c r="B300" t="str">
-        <v>검증 세부 정보</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Triggered by</v>
+        <v>Tables</v>
       </c>
       <c r="B301" t="str">
-        <v>트리거 항목</v>
+        <v>표</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Field</v>
+        <v>Data</v>
       </c>
       <c r="B302" t="str">
-        <v>항목</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Current value</v>
+        <v>Evaluate</v>
       </c>
       <c r="B303" t="str">
-        <v>현재 값</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Required: 0</v>
+        <v>Loading…</v>
       </c>
       <c r="B304" t="str">
-        <v>필수: 0</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Expected: {value}</v>
+        <v>Input</v>
       </c>
       <c r="B305" t="str">
-        <v>예상: {value}</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Invalid</v>
+        <v>Output</v>
       </c>
       <c r="B306" t="str">
-        <v>잘못됨</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Floating point</v>
       </c>
       <c r="B307" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Close</v>
+        <v>Grid point</v>
       </c>
       <c r="B308" t="str">
-        <v>닫기</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Loading XML editor…</v>
+        <v>Normalized</v>
       </c>
       <c r="B309" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Human</v>
       </c>
       <c r="B310" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B311" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B312" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>● unsaved XML edits</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B313" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading…</v>
       </c>
       <c r="B314" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B315" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B316" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>indent</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B317" t="str">
-        <v>들여쓰기</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>sort keys</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B318" t="str">
-        <v>키 정렬</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
+        <v>Loading Profile Assessment WG report…</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>Running Profile Assessment WG checks…</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>Profile Assessment WG Report</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Profile Assessment WG 보고서</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>Security</v>
+      </c>
+      <c r="B322" t="str">
+        <v>보안</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Conformance</v>
+      </c>
+      <c r="B323" t="str">
+        <v>적합성</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Quality</v>
+      </c>
+      <c r="B324" t="str">
+        <v>품질</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>REPORT</v>
+      </c>
+      <c r="B325" t="str">
+        <v>보고서</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="B326" t="str">
+        <v>실패</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>checks</v>
+      </c>
+      <c r="B327" t="str">
+        <v>개 검사</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+      </c>
+      <c r="B328" t="str">
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>ICC Profile Tool · powered by IccProfLib</v>
+      </c>
+      <c r="B329" t="str">
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B330" t="str">
+        <v>ICC 프로파일 도구</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B331" t="str">
+        <v>{lib} 기반</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B332" t="str">
+        <v>구독</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B333" t="str">
+        <v>profiletool 새 릴리스 알림 받기</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B334" t="str">
+        <v>새 릴리스 알림 받기</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B335" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B336" t="str">
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B337" t="str">
+        <v>이메일 주소</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B338" t="str">
+        <v>you@example.com</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B339" t="str">
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B340" t="str">
+        <v>(선택)</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B341" t="str">
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B342" t="str">
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B343" t="str">
+        <v>취소</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B344" t="str">
+        <v>구독</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B345" t="str">
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B346" t="str">
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B347" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B348" t="str">
+        <v>개인정보 처리방침</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B349" t="str">
+        <v>유효한 이메일 주소를 입력하세요.</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B350" t="str">
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B351" t="str">
+        <v>양식을 확인하고 다시 시도하세요.</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B352" t="str">
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B353" t="str">
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B354" t="str">
+        <v>오류:</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B355" t="str">
+        <v>XML로 변환</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B356" t="str">
+        <v>JSON으로 변환</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B357" t="str">
+        <v>ICC로 변환</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B358" t="str">
+        <v>XML로 변환 중…</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B359" t="str">
+        <v>JSON으로 변환 중…</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B360" t="str">
+        <v>ICC로 변환 중…</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B361" t="str">
+        <v>ICC 프로파일 로드</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B362" t="str">
+        <v>ICC 프로파일 파일용 드롭 영역</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B363" t="str">
+        <v>프로파일 ID</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B364" t="str">
+        <v>태그를 찾을 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B365" t="str">
+        <v>태그 이름</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B366" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B367" t="str">
+        <v>오프셋</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B368" t="str">
+        <v>크기</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B369" t="str">
+        <v>패딩</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B370" t="str">
+        <v>로드 이후 바이트가 변경됨</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B371" t="str">
+        <v>유형</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B372" t="str">
+        <v>{type} 배열</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B373" t="str">
+        <v>(내용 없음)</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B374" t="str">
+        <v>바이트</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B375" t="str">
+        <v>전체 설명을 로드하는 중…</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B376" t="str">
+        <v>전체 설명을 로드할 수 없습니다:</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B377" t="str">
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B378" t="str">
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B379" t="str">
+        <v>검증 출력 없음</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B380" t="str">
+        <v>프로파일이 유효합니다</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B381" t="str">
+        <v>프로파일에 경고가 있습니다</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B382" t="str">
+        <v>프로파일이 규격을 준수하지 않습니다</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B383" t="str">
+        <v>심각한 검증 오류</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B384" t="str">
+        <v>알 수 없는 검증 상태</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B385" t="str">
+        <v>심각 — 검사용으로만 표시</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B386" t="str">
+        <v>경고나 오류를 찾지 못했습니다.</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B387" t="str">
+        <v>유효</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B388" t="str">
+        <v>경고</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B389" t="str">
+        <v>오류</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B390" t="str">
+        <v>알 수 없음</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B391" t="str">
+        <v>통과</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B392" t="str">
+        <v>실패</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B393" t="str">
+        <v>컨텍스트에서 보기</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B394" t="str">
+        <v>검증 세부 정보</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B395" t="str">
+        <v>트리거 항목</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B396" t="str">
+        <v>항목</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B397" t="str">
+        <v>현재 값</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B398" t="str">
+        <v>필수: 0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B399" t="str">
+        <v>예상: {value}</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B400" t="str">
+        <v>잘못됨</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B401" t="str">
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B402" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B403" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B404" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B405" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B406" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B407" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B408" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B409" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B410" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B411" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B412" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B319" t="str">
+      <c r="B413" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B413"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B413"/>
+  <dimension ref="A1:B410"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1053,2669 +1053,2645 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Based on</v>
       </c>
       <c r="B82" t="str">
-        <v>ICC 프로파일을 업로드하여</v>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>specification using the</v>
+        <v>demo implementation</v>
       </c>
       <c r="B83" t="str">
-        <v>사양을</v>
+        <v>데모 구현 기반</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation.</v>
+        <v>Validating…</v>
       </c>
       <c r="B84" t="str">
-        <v>데모 구현으로 검증합니다.</v>
+        <v>검증 중…</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Based on</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B85" t="str">
-        <v/>
+        <v>ICC 프로파일 저장</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>demo implementation</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B86" t="str">
-        <v>데모 구현 기반</v>
+        <v>● 변경됨 — 저장되지 않음</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Validating…</v>
+        <v>Profiles</v>
       </c>
       <c r="B87" t="str">
-        <v>검증 중…</v>
+        <v>프로파일</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Save ICC profile</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B88" t="str">
-        <v>ICC 프로파일 저장</v>
+        <v>프로파일 풀 표시</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Collapse</v>
       </c>
       <c r="B89" t="str">
-        <v>● 변경됨 — 저장되지 않음</v>
+        <v>접기</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Profiles</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>프로파일</v>
+        <v>프로파일 불러오기</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Show profile pool</v>
+        <v>Remove</v>
       </c>
       <c r="B91" t="str">
-        <v>프로파일 풀 표시</v>
+        <v>제거</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Collapse</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B92" t="str">
-        <v>접기</v>
+        <v>여기에 ICC 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load Profiles</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B93" t="str">
-        <v>프로파일 불러오기</v>
+        <v>또는 이미지(TIFF/PNG/JPEG)를 놓아 내장된 프로파일을 추출하세요 — 파일은 사용자 장치에 그대로 남습니다.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Remove</v>
+        <v>New from .cube</v>
       </c>
       <c r="B94" t="str">
-        <v>제거</v>
+        <v>.cube에서 새로 만들기</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Sort by name</v>
       </c>
       <c r="B95" t="str">
-        <v>여기에 ICC 프로파일을 놓으세요</v>
+        <v>이름순 정렬</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>A–Z</v>
       </c>
       <c r="B96" t="str">
-        <v>또는 이미지(TIFF/PNG/JPEG)를 놓아 내장된 프로파일을 추출하세요 — 파일은 사용자 장치에 그대로 남습니다.</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New from .cube</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>.cube에서 새로 만들기</v>
+        <v>.cube에서 새 프로파일</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Sort by name</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B98" t="str">
-        <v>이름순 정렬</v>
+        <v>Adobe/Resolve의 .cube 3D LUT에서 ICC DeviceLink를 만듭니다. 결과는 풀에 추가되고 다운로드됩니다.</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>A–Z</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B99" t="str">
-        <v>A–Z</v>
+        <v>.cube 파일 선택</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>New profile from .cube</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B100" t="str">
-        <v>.cube에서 새 프로파일</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Adobe/Resolve의 .cube 3D LUT에서 ICC DeviceLink를 만듭니다. 결과는 풀에 추가되고 다운로드됩니다.</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Choose .cube file</v>
-      </c>
-      <c r="B102" t="str">
-        <v>.cube 파일 선택</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>or drop it here, or paste below</v>
-      </c>
-      <c r="B103" t="str">
         <v>또는 여기에 놓거나 아래에 붙여넣으세요</v>
       </c>
     </row>
-    <row r="104" xml:space="preserve">
-      <c r="A104" t="str" xml:space="preserve">
+    <row r="101" xml:space="preserve">
+      <c r="A101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B104" t="str" xml:space="preserve">
+      <c r="B101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B102" t="str">
+        <v>취소</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Create DeviceLink</v>
+      </c>
+      <c r="B103" t="str">
+        <v>DeviceLink 만들기</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Creating…</v>
+      </c>
+      <c r="B104" t="str">
+        <v>만드는 중…</v>
+      </c>
+    </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Cancel</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B105" t="str">
-        <v>취소</v>
+        <v>해당 파일을 읽을 수 없습니다.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Create DeviceLink</v>
+        <v>Profile</v>
       </c>
       <c r="B106" t="str">
-        <v>DeviceLink 만들기</v>
+        <v>프로파일</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Creating…</v>
+        <v>Compare</v>
       </c>
       <c r="B107" t="str">
-        <v>만드는 중…</v>
+        <v>비교</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Could not read that file.</v>
+        <v>Combine</v>
       </c>
       <c r="B108" t="str">
-        <v>해당 파일을 읽을 수 없습니다.</v>
+        <v>링크</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Profile</v>
+        <v>Spectral</v>
       </c>
       <c r="B109" t="str">
-        <v>프로파일</v>
+        <v>스펙트럴</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Compare</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B110" t="str">
-        <v>비교</v>
+        <v>풀에서 이 탭으로 프로파일을 끌어다 놓으세요</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Combine</v>
+        <v>Remove</v>
       </c>
       <c r="B111" t="str">
-        <v>링크</v>
+        <v>제거</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Spectral</v>
+        <v>No profile selected</v>
       </c>
       <c r="B112" t="str">
-        <v>스펙트럴</v>
+        <v>선택된 프로파일 없음</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B113" t="str">
-        <v>풀에서 이 탭으로 프로파일을 끌어다 놓으세요</v>
+        <v>풀에서 프로파일을 '프로파일' 탭으로 끌어다 놓아 검사하세요.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Remove</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B114" t="str">
-        <v>제거</v>
+        <v>아직 비교할 항목이 없습니다</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>No profile selected</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B115" t="str">
-        <v>선택된 프로파일 없음</v>
+        <v>하나 이상의 프로파일을 '비교' 탭으로 끌어다 놓으세요.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B116" t="str">
-        <v>풀에서 프로파일을 '프로파일' 탭으로 끌어다 놓아 검사하세요.</v>
+        <v>색역 비교</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Nothing to compare yet</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B117" t="str">
-        <v>아직 비교할 항목이 없습니다</v>
+        <v>3D 색역 및 2D 슬라이스 보기가 여기에 추가됩니다. 누적:</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B118" t="str">
-        <v>하나 이상의 프로파일을 '비교' 탭으로 끌어다 놓으세요.</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut comparison</v>
+        <v>Shell</v>
       </c>
       <c r="B119" t="str">
-        <v>색역 비교</v>
+        <v>셸</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Wireframe</v>
       </c>
       <c r="B120" t="str">
-        <v>3D 색역 및 2D 슬라이스 보기가 여기에 추가됩니다. 누적:</v>
+        <v>와이어프레임</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Rendering intent</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B121" t="str">
-        <v>렌더링 의도</v>
+        <v>축 번호</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Shell</v>
+        <v>Opacity</v>
       </c>
       <c r="B122" t="str">
-        <v>셸</v>
+        <v>불투명도</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Wireframe</v>
+        <v>Colour</v>
       </c>
       <c r="B123" t="str">
-        <v>와이어프레임</v>
+        <v>색상</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Axis numbers</v>
+        <v>Solid</v>
       </c>
       <c r="B124" t="str">
-        <v>축 번호</v>
+        <v>단색</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Opacity</v>
+        <v>By value</v>
       </c>
       <c r="B125" t="str">
-        <v>불투명도</v>
+        <v>값 기준</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Colour</v>
+        <v>By hue</v>
       </c>
       <c r="B126" t="str">
-        <v>색상</v>
+        <v>색상(Hue) 기준</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Solid</v>
+        <v>Rotation</v>
       </c>
       <c r="B127" t="str">
-        <v>단색</v>
+        <v>회전</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>By value</v>
+        <v>Turntable</v>
       </c>
       <c r="B128" t="str">
-        <v>값 기준</v>
+        <v>턴테이블</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>By hue</v>
+        <v>Orbit</v>
       </c>
       <c r="B129" t="str">
-        <v>색상(Hue) 기준</v>
+        <v>궤도</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Rotation</v>
+        <v>Drag speed</v>
       </c>
       <c r="B130" t="str">
-        <v>회전</v>
+        <v>드래그 속도</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Turntable</v>
+        <v>Roll</v>
       </c>
       <c r="B131" t="str">
-        <v>턴테이블</v>
+        <v>롤</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Orbit</v>
+        <v>Roll speed</v>
       </c>
       <c r="B132" t="str">
-        <v>궤도</v>
+        <v>롤 속도</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Drag speed</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B133" t="str">
-        <v>드래그 속도</v>
+        <v>색역 생성 중…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Roll</v>
+        <v>no gamut</v>
       </c>
       <c r="B134" t="str">
-        <v>롤</v>
+        <v>색역 없음</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Roll speed</v>
+        <v>Show / hide</v>
       </c>
       <c r="B135" t="str">
-        <v>롤 속도</v>
+        <v>표시/숨기기</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Building gamut…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B136" t="str">
-        <v>색역 생성 중…</v>
+        <v>3D 색역 셸</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>no gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B137" t="str">
-        <v>색역 없음</v>
+        <v>2D 색역 슬라이스</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Show / hide</v>
+        <v>Plane</v>
       </c>
       <c r="B138" t="str">
-        <v>표시/숨기기</v>
+        <v>평면</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>3-D gamut shell</v>
+        <v>L*</v>
       </c>
       <c r="B139" t="str">
-        <v>3D 색역 셸</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>2-D gamut slice</v>
+        <v>a*</v>
       </c>
       <c r="B140" t="str">
-        <v>2D 색역 슬라이스</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Plane</v>
+        <v>b*</v>
       </c>
       <c r="B141" t="str">
-        <v>평면</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>L*</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B142" t="str">
-        <v>L*</v>
+        <v>선택한 프로파일 중 색역을 도출할 장치→PCS 변환을 가진 것이 없습니다.</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>a*</v>
+        <v>Linking</v>
       </c>
       <c r="B143" t="str">
-        <v>a*</v>
+        <v>링크</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>b*</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B144" t="str">
-        <v>b*</v>
+        <v>DeviceLink 생성과 다중 프로파일 변환은 이후 단계에서 제공됩니다.</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B145" t="str">
-        <v>선택한 프로파일 중 색역을 도출할 장치→PCS 변환을 가진 것이 없습니다.</v>
+        <v>더 많은 링크 메이커(DeviceLink, …)가 여기에 추가됩니다.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Linking</v>
+        <v>Observer Change</v>
       </c>
       <c r="B146" t="str">
-        <v>링크</v>
+        <v>V4 디스플레이 메이커</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B147" t="str">
-        <v>DeviceLink 생성과 다중 프로파일 변환은 이후 단계에서 제공됩니다.</v>
+        <v>V5 RGB 디스플레이와 V5 관찰자 프로파일을 여기에 끌어다 놓아 V4 디스플레이 프로파일을 만드세요.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B148" t="str">
-        <v>더 많은 링크 메이커(DeviceLink, …)가 여기에 추가됩니다.</v>
+        <v>V5 RGB 디스플레이</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Observer Change</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B149" t="str">
-        <v>V4 디스플레이 메이커</v>
+        <v>디스플레이 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B150" t="str">
-        <v>V5 RGB 디스플레이와 V5 관찰자 프로파일을 여기에 끌어다 놓아 V4 디스플레이 프로파일을 만드세요.</v>
+        <v>V5 관찰자 (PCC)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 RGB display</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B151" t="str">
-        <v>V5 RGB 디스플레이</v>
+        <v>관찰자 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop a display profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B152" t="str">
-        <v>디스플레이 프로파일을 놓으세요</v>
+        <v>V5 RGB 디스플레이도 관찰자도 아닌 프로파일은 무시되었습니다.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B153" t="str">
-        <v>V5 관찰자 (PCC)</v>
+        <v>V4 디스플레이 프로파일 만들기</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop an observer profile</v>
+        <v>Profile name</v>
       </c>
       <c r="B154" t="str">
-        <v>관찰자 프로파일을 놓으세요</v>
+        <v>프로파일 이름</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>Create</v>
       </c>
       <c r="B155" t="str">
-        <v>V5 RGB 디스플레이도 관찰자도 아닌 프로파일은 무시되었습니다.</v>
+        <v>만들기</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Making…</v>
       </c>
       <c r="B156" t="str">
-        <v>V4 디스플레이 프로파일 만들기</v>
+        <v>만드는 중…</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile name</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B157" t="str">
-        <v>프로파일 이름</v>
+        <v>'{name}'을(를) 만들었습니다 — 풀과 이 탭에 추가되었습니다.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Create</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B158" t="str">
-        <v>만들기</v>
+        <v>링크 파이프라인</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Making…</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B159" t="str">
-        <v>만드는 중…</v>
+        <v>프로파일 체인을 구성한 다음 DeviceLink를 만들거나, 이미지를 변환하거나, 색상 데이터셋을 변환하세요.</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Done</v>
       </c>
       <c r="B160" t="str">
-        <v>'{name}'을(를) 만들었습니다 — 풀과 이 탭에 추가되었습니다.</v>
+        <v>완료</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Link Pipeline</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B161" t="str">
-        <v>링크 파이프라인</v>
+        <v>변환할 이미지를 드롭하세요 (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Checking image…</v>
       </c>
       <c r="B162" t="str">
-        <v>프로파일 체인을 구성한 다음 DeviceLink를 만들거나, 이미지를 변환하거나, 색상 데이터셋을 변환하세요.</v>
+        <v>이미지 확인 중…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Done</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B163" t="str">
-        <v>완료</v>
+        <v>지원되지 않는 이미지입니다 (TIFF, PNG 또는 JPEG).</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B164" t="str">
-        <v>변환할 이미지를 드롭하세요 (TIFF/PNG/JPEG)</v>
+        <v>이미지가 너무 큽니다 ({mp} MP, 제한 {max} MP).</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Checking image…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B165" t="str">
-        <v>이미지 확인 중…</v>
+        <v>이미지 변환</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Transforming…</v>
       </c>
       <c r="B166" t="str">
-        <v>지원되지 않는 이미지입니다 (TIFF, PNG 또는 JPEG).</v>
+        <v>변환 중…</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B167" t="str">
-        <v>이미지가 너무 큽니다 ({mp} MP, 제한 {max} MP).</v>
+        <v>체인을 시작하려면 프로파일을 드롭하세요</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Transform Image</v>
+        <v>removed</v>
       </c>
       <c r="B168" t="str">
-        <v>이미지 변환</v>
+        <v>제거됨</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Transforming…</v>
+        <v>Move earlier</v>
       </c>
       <c r="B169" t="str">
-        <v>변환 중…</v>
+        <v>앞으로 이동</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Move later</v>
       </c>
       <c r="B170" t="str">
-        <v>체인을 시작하려면 프로파일을 드롭하세요</v>
+        <v>뒤로 이동</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>removed</v>
+        <v>Move up</v>
       </c>
       <c r="B171" t="str">
-        <v>제거됨</v>
+        <v>위로 이동</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move earlier</v>
+        <v>Move down</v>
       </c>
       <c r="B172" t="str">
-        <v>앞으로 이동</v>
+        <v>아래로 이동</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move later</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B173" t="str">
-        <v>뒤로 이동</v>
+        <v>렌더링 인텐트 (전체)</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move up</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B174" t="str">
-        <v>위로 이동</v>
+        <v>이 변환의 렌더링 인텐트</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move down</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B175" t="str">
-        <v>아래로 이동</v>
+        <v>변환마다 렌더링 인텐트가 다릅니다</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B176" t="str">
-        <v>렌더링 인텐트 (전체)</v>
+        <v>체인 방향 전환 (첫 변환을 반전시키고 체인 전체에 반영됩니다)</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B177" t="str">
-        <v>이 변환의 렌더링 인텐트</v>
+        <v>체인에 포함된 프로파일이 풀에서 제거되었습니다 — 계속하려면 제거하세요.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Chain</v>
       </c>
       <c r="B178" t="str">
-        <v>변환마다 렌더링 인텐트가 다릅니다</v>
+        <v>체인</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B179" t="str">
-        <v>체인 방향 전환 (첫 변환을 반전시키고 체인 전체에 반영됩니다)</v>
+        <v>체인을 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B180" t="str">
-        <v>체인에 포함된 프로파일이 풀에서 제거되었습니다 — 계속하려면 제거하세요.</v>
+        <v>체인 확인 중…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Chain</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B181" t="str">
-        <v>체인</v>
+        <v>체인이 연결되지 않습니다 ({detail}).</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>체인을 분석할 수 없습니다.</v>
+        <v>프로파일 {n}이(가) 이전 단계와 연결되지 않습니다 ({detail}).</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Checking chain…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B183" t="str">
-        <v>체인 확인 중…</v>
+        <v>이미지를 처리하기 전에 체인을 수정하세요</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Clear</v>
       </c>
       <c r="B184" t="str">
-        <v>체인이 연결되지 않습니다 ({detail}).</v>
+        <v>지우기</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B185" t="str">
-        <v>프로파일 {n}이(가) 이전 단계와 연결되지 않습니다 ({detail}).</v>
+        <v>DeviceLink 만들기</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B186" t="str">
-        <v>이미지를 처리하기 전에 체인을 수정하세요</v>
+        <v>DeviceLink 이름</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Clear</v>
+        <v>Making…</v>
       </c>
       <c r="B187" t="str">
-        <v>지우기</v>
+        <v>생성 중…</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Make DeviceLink</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B188" t="str">
-        <v>DeviceLink 만들기</v>
+        <v>"{name}" 생성됨 — 풀과 이 탭에 추가되었습니다.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>DeviceLink name</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B189" t="str">
-        <v>DeviceLink 이름</v>
+        <v>{src} 이미지를 드롭하면 {dst}(으)로 변환됩니다 — 결과는 다운로드되며 저장되지 않습니다.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Making…</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B190" t="str">
-        <v>생성 중…</v>
+        <v>이미지를 처리하려면 체인을 구성하세요</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B191" t="str">
-        <v>"{name}" 생성됨 — 풀과 이 탭에 추가되었습니다.</v>
+        <v>이 체인은 이미지 색공간에서 시작하고 끝나지 않습니다</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B192" t="str">
-        <v>{src} 이미지를 드롭하면 {dst}(으)로 변환됩니다 — 결과는 다운로드되며 저장되지 않습니다.</v>
+        <v>변환된 이미지를 저장했습니다.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B193" t="str">
-        <v>이미지를 처리하려면 체인을 구성하세요</v>
+        <v>색상 데이터셋을 드롭하세요 (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B194" t="str">
-        <v>이 체인은 이미지 색공간에서 시작하고 끝나지 않습니다</v>
+        <v>해당 파일을 읽을 수 없습니다.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B195" t="str">
-        <v>변환된 이미지를 저장했습니다.</v>
+        <v>데이터 파일이 너무 큽니다.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Transform Data</v>
       </c>
       <c r="B196" t="str">
-        <v>색상 데이터셋을 드롭하세요 (CGATS/CSV/CxF/JSON)</v>
+        <v>데이터 변환</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Could not read that file.</v>
+        <v>Transforming…</v>
       </c>
       <c r="B197" t="str">
-        <v>해당 파일을 읽을 수 없습니다.</v>
+        <v>변환 중…</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Data file too large.</v>
+        <v>Prefer</v>
       </c>
       <c r="B198" t="str">
-        <v>데이터 파일이 너무 큽니다.</v>
+        <v>선호</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Transform Data</v>
+        <v>Observer</v>
       </c>
       <c r="B199" t="str">
-        <v>데이터 변환</v>
+        <v>관측자</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Transforming…</v>
+        <v>Illuminant</v>
       </c>
       <c r="B200" t="str">
-        <v>변환 중…</v>
+        <v>광원</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Prefer</v>
+        <v>Condition</v>
       </c>
       <c r="B201" t="str">
-        <v>선호</v>
+        <v>조건</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Observer</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B202" t="str">
-        <v>관측자</v>
+        <v>중복 {n}건 필터링</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Illuminant</v>
+        <v>median</v>
       </c>
       <c r="B203" t="str">
-        <v>광원</v>
+        <v>중앙값</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Condition</v>
+        <v>mean</v>
       </c>
       <c r="B204" t="str">
-        <v>조건</v>
+        <v>평균값</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>patches</v>
       </c>
       <c r="B205" t="str">
-        <v>중복 {n}건 필터링</v>
+        <v>패치</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>median</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B206" t="str">
-        <v>중앙값</v>
+        <v>중복 {n}건</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>mean</v>
+        <v>Transform result</v>
       </c>
       <c r="B207" t="str">
-        <v>평균값</v>
+        <v>변환 결과</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>patches</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B208" t="str">
-        <v>패치</v>
+        <v>{src} → {dst} · 패치 {n}개</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{n} duplicates</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B209" t="str">
-        <v>중복 {n}건</v>
+        <v>전체 {total}건 중 처음 {shown}건 표시 중 — 저장하면 전체가 기록됩니다.</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Transform result</v>
+        <v>Save as</v>
       </c>
       <c r="B210" t="str">
-        <v>변환 결과</v>
+        <v>다른 이름으로 저장</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Save</v>
       </c>
       <c r="B211" t="str">
-        <v>{src} → {dst} · 패치 {n}개</v>
+        <v>저장</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B212" t="str">
-        <v>전체 {total}건 중 처음 {shown}건 표시 중 — 저장하면 전체가 기록됩니다.</v>
+        <v>변환 반전</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Save as</v>
+        <v>Inverting…</v>
       </c>
       <c r="B213" t="str">
-        <v>다른 이름으로 저장</v>
+        <v>반전 중…</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Save</v>
+        <v>Invert</v>
       </c>
       <c r="B214" t="str">
-        <v>저장</v>
+        <v>반전</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert Transform</v>
+        <v>last stage</v>
       </c>
       <c r="B215" t="str">
-        <v>변환 반전</v>
+        <v>마지막 단계</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Inverting…</v>
+        <v>first stage</v>
       </c>
       <c r="B216" t="str">
-        <v>반전 중…</v>
+        <v>첫 단계</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B217" t="str">
-        <v>반전</v>
+        <v>{in} 데이터 → {out} 검색</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>last stage</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B218" t="str">
-        <v>마지막 단계</v>
+        <v>반전에는 2–3개 프로파일로 이루어진 체인이 필요합니다</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>first stage</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B219" t="str">
-        <v>첫 단계</v>
+        <v>데이터셋은 {in}이어야 합니다. 역검색은 {out}과 패치별 역변환 가능성 비용을 산출합니다.</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B220" t="str">
-        <v>{in} 데이터 → {out} 검색</v>
+        <v>ΔE 비용</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B221" t="str">
-        <v>반전에는 2–3개 프로파일로 이루어진 체인이 필요합니다</v>
+        <v>이 이미지에는 내장된 ICC 프로파일이 있습니다.</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B222" t="str">
-        <v>데이터셋은 {in}이어야 합니다. 역검색은 {out}과 패치별 역변환 가능성 비용을 산출합니다.</v>
+        <v>추출 후 체인에 추가</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>ΔE cost</v>
+        <v>Extracting…</v>
       </c>
       <c r="B223" t="str">
-        <v>ΔE 비용</v>
+        <v>추출 중…</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B224" t="str">
-        <v>이 이미지에는 내장된 ICC 프로파일이 있습니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B225" t="str">
-        <v>추출 후 체인에 추가</v>
+        <v>내장된 프로파일을 추출했습니다 — 풀에 추가되고 체인의 첫 번째 자리에 배치되었습니다.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracting…</v>
+        <v>Image output options</v>
       </c>
       <c r="B226" t="str">
-        <v>추출 중…</v>
+        <v>이미지 출력 옵션</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Dismiss</v>
+        <v>Encoding</v>
       </c>
       <c r="B227" t="str">
-        <v>닫기</v>
+        <v>인코딩</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Same as source</v>
       </c>
       <c r="B228" t="str">
-        <v>내장된 프로파일을 추출했습니다 — 풀에 추가되고 체인의 첫 번째 자리에 배치되었습니다.</v>
+        <v>원본과 동일</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Image output options</v>
+        <v>8-bit</v>
       </c>
       <c r="B229" t="str">
-        <v>이미지 출력 옵션</v>
+        <v>8비트</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Encoding</v>
+        <v>16-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>인코딩</v>
+        <v>16비트</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Same as source</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B231" t="str">
-        <v>원본과 동일</v>
+        <v>부동소수점 (32비트)</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>8-bit</v>
+        <v>Compression</v>
       </c>
       <c r="B232" t="str">
-        <v>8비트</v>
+        <v>압축</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>16-bit</v>
+        <v>None</v>
       </c>
       <c r="B233" t="str">
-        <v>16비트</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Float (32-bit)</v>
+        <v>Planar</v>
       </c>
       <c r="B234" t="str">
-        <v>부동소수점 (32비트)</v>
+        <v>플레이너</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Compression</v>
+        <v>Composite</v>
       </c>
       <c r="B235" t="str">
-        <v>압축</v>
+        <v>컴포지트</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>None</v>
+        <v>Separated</v>
       </c>
       <c r="B236" t="str">
-        <v>없음</v>
+        <v>분리</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Planar</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B237" t="str">
-        <v>플레이너</v>
+        <v>CMM 보간</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Composite</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B238" t="str">
-        <v>컴포지트</v>
+        <v>사면체</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Separated</v>
+        <v>Linear</v>
       </c>
       <c r="B239" t="str">
-        <v>분리</v>
+        <v>선형</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>CMM interpolation</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B240" t="str">
-        <v>CMM 보간</v>
+        <v>ICC 포함</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Tetrahedral</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B241" t="str">
-        <v>사면체</v>
+        <v>인코딩, 압축, 플레이너 방식은 저장되는 TIFF에 반영됩니다. TIFF 전용 옵션(부동소수점, LZW/ZIP, 분리)을 설정하지 않으면 RGB/Gray 출력은 PNG로 유지됩니다.</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Linear</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B242" t="str">
-        <v>선형</v>
+        <v>스펙트럴 TIFF 조합</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Embed ICC</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B243" t="str">
-        <v>ICC 포함</v>
+        <v>단일 채널 스펙트럴 이미지를 채널 순서대로 드롭하면 하나의 다중 채널 TIFF로 조합됩니다.</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B244" t="str">
-        <v>인코딩, 압축, 플레이너 방식은 저장되는 TIFF에 반영됩니다. TIFF 전용 옵션(부동소수점, LZW/ZIP, 분리)을 설정하지 않으면 RGB/Gray 출력은 PNG로 유지됩니다.</v>
+        <v>스펙트럴 이미지를 여기에 드롭하세요 (또는 클릭하여 선택)</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>ch</v>
       </c>
       <c r="B245" t="str">
-        <v>스펙트럴 TIFF 조합</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B246" t="str">
-        <v>단일 채널 스펙트럴 이미지를 채널 순서대로 드롭하면 하나의 다중 채널 TIFF로 조합됩니다.</v>
+        <v>조합 후 저장</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Assembling…</v>
       </c>
       <c r="B247" t="str">
-        <v>스펙트럴 이미지를 여기에 드롭하세요 (또는 클릭하여 선택)</v>
+        <v>조합 중…</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>ch</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B248" t="str">
-        <v>ch</v>
+        <v>{n}개 채널을 조합했습니다.</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B249" t="str">
-        <v>조합 후 저장</v>
+        <v>이미지로 인식되는 파일이 없습니다 (TIFF, PNG 또는 JPEG).</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Assembling…</v>
+        <v>Cancel</v>
       </c>
       <c r="B250" t="str">
-        <v>조합 중…</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B251" t="str">
-        <v>{n}개 채널을 조합했습니다.</v>
+        <v>{n}개 파일을 불러오지 못했습니다</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B252" t="str">
-        <v>이미지로 인식되는 파일이 없습니다 (TIFF, PNG 또는 JPEG).</v>
+        <v>이 파일들은 ICC 프로파일이 아니므로 풀에 추가되지 않았습니다:</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Cancel</v>
+        <v>OK</v>
       </c>
       <c r="B253" t="str">
-        <v>취소</v>
+        <v>확인</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B254" t="str">
-        <v>{n}개 파일을 불러오지 못했습니다</v>
+        <v>ICC 프로파일을 여기에 놓기</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>or</v>
       </c>
       <c r="B255" t="str">
-        <v>이 파일들은 ICC 프로파일이 아니므로 풀에 추가되지 않았습니다:</v>
+        <v>또는</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>OK</v>
+        <v>Choose file</v>
       </c>
       <c r="B256" t="str">
-        <v>확인</v>
+        <v>파일 선택</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B257" t="str">
-        <v>ICC 프로파일을 여기에 놓기</v>
+        <v>.icc 및 .icm 파일</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>or</v>
+        <v>Header</v>
       </c>
       <c r="B258" t="str">
-        <v>또는</v>
+        <v>헤더</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Choose file</v>
+        <v>Tags</v>
       </c>
       <c r="B259" t="str">
-        <v>파일 선택</v>
+        <v>태그</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>.icc and .icm files</v>
+        <v>Validation</v>
       </c>
       <c r="B260" t="str">
-        <v>.icc 및 .icm 파일</v>
+        <v>검증</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Header</v>
+        <v>Analysis</v>
       </c>
       <c r="B261" t="str">
-        <v>헤더</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Tags</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B262" t="str">
-        <v>태그</v>
+        <v>중립축 잉킹</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Validation</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B263" t="str">
-        <v>검증</v>
+        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Analysis</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B264" t="str">
-        <v>분석</v>
+        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B265" t="str">
-        <v>중립축 잉킹</v>
+        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B266" t="str">
-        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>% ink</v>
       </c>
       <c r="B267" t="str">
-        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>% 잉크</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Perceptual</v>
       </c>
       <c r="B268" t="str">
-        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
+        <v>지각적</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Rendering intent</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B269" t="str">
-        <v>렌더링 의도</v>
+        <v>상대 색도</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>% ink</v>
+        <v>Saturation</v>
       </c>
       <c r="B270" t="str">
-        <v>% 잉크</v>
+        <v>채도</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Perceptual</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B271" t="str">
-        <v>지각적</v>
+        <v>절대 색도</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B272" t="str">
-        <v>상대 색도</v>
+        <v>프로파일 통계</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Saturation</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B273" t="str">
-        <v>채도</v>
+        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B274" t="str">
-        <v>절대 색도</v>
+        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Profile Statistics</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B275" t="str">
-        <v>프로파일 통계</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B276" t="str">
-        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
+        <v>색역 부피 (ΔE³)</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B277" t="str">
-        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
+        <v>왕복 ΔE</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Rendering intent</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B278" t="str">
-        <v>렌더링 의도</v>
+        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>mean</v>
       </c>
       <c r="B279" t="str">
-        <v>색역 부피 (ΔE³)</v>
+        <v>평균</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Round-trip ΔE</v>
+        <v>P90</v>
       </c>
       <c r="B280" t="str">
-        <v>왕복 ΔE</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>max</v>
       </c>
       <c r="B281" t="str">
-        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
+        <v>최대</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>mean</v>
+        <v>Analysing…</v>
       </c>
       <c r="B282" t="str">
-        <v>평균</v>
+        <v>분석 중…</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>P90</v>
+        <v>Analysis</v>
       </c>
       <c r="B283" t="str">
-        <v>P90</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>max</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B284" t="str">
-        <v>최대</v>
+        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B285" t="str">
-        <v>분석 중…</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B286" t="str">
-        <v>분석</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B287" t="str">
-        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Plot</v>
+        <v>JSON</v>
       </c>
       <c r="B288" t="str">
-        <v>플롯</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Raw Output</v>
+        <v>Curves</v>
       </c>
       <c r="B289" t="str">
-        <v>원시 출력</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>XML</v>
+        <v>Input curves</v>
       </c>
       <c r="B290" t="str">
-        <v>XML</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>JSON</v>
+        <v>Output curves</v>
       </c>
       <c r="B291" t="str">
-        <v>JSON</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Curves</v>
+        <v>CLUT image</v>
       </c>
       <c r="B292" t="str">
-        <v>곡선</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Input curves</v>
+        <v>Gamut image</v>
       </c>
       <c r="B293" t="str">
-        <v>입력 곡선</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Output curves</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B294" t="str">
-        <v>출력 곡선</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>CLUT image</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B295" t="str">
-        <v>CLUT 이미지</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Gamut image</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B296" t="str">
-        <v>색역 이미지</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Chromaticity</v>
+        <v>Curve table</v>
       </c>
       <c r="B297" t="str">
-        <v>색도</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Scatter plot</v>
+        <v>Tables</v>
       </c>
       <c r="B298" t="str">
-        <v>산점도</v>
+        <v>표</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tone response curve</v>
+        <v>Data</v>
       </c>
       <c r="B299" t="str">
-        <v>톤 응답 곡선</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Curve table</v>
+        <v>Evaluate</v>
       </c>
       <c r="B300" t="str">
-        <v>곡선 표</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Tables</v>
+        <v>Loading…</v>
       </c>
       <c r="B301" t="str">
-        <v>표</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Data</v>
+        <v>Input</v>
       </c>
       <c r="B302" t="str">
-        <v>데이터</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Evaluate</v>
+        <v>Output</v>
       </c>
       <c r="B303" t="str">
-        <v>평가</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Loading…</v>
+        <v>Floating point</v>
       </c>
       <c r="B304" t="str">
-        <v>불러오는 중…</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Input</v>
+        <v>Grid point</v>
       </c>
       <c r="B305" t="str">
-        <v>입력</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Output</v>
+        <v>Normalized</v>
       </c>
       <c r="B306" t="str">
-        <v>출력</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Floating point</v>
+        <v>Human</v>
       </c>
       <c r="B307" t="str">
-        <v>부동 소수점</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Grid point</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B308" t="str">
-        <v>격자점</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Normalized</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B309" t="str">
-        <v>정규화</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Human</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B310" t="str">
-        <v>사람용</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Device → PCS</v>
+        <v>Loading…</v>
       </c>
       <c r="B311" t="str">
-        <v>장치 → PCS</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B312" t="str">
-        <v>PCS → 장치</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No CLUT grid</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B313" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Loading…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B314" t="str">
-        <v>불러오는 중…</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B315" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B316" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B317" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B318" t="str">
-        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Security</v>
       </c>
       <c r="B319" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Conformance</v>
       </c>
       <c r="B320" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Quality</v>
       </c>
       <c r="B321" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Security</v>
+        <v>REPORT</v>
       </c>
       <c r="B322" t="str">
-        <v>보안</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Conformance</v>
+        <v>FAIL</v>
       </c>
       <c r="B323" t="str">
-        <v>적합성</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Quality</v>
+        <v>checks</v>
       </c>
       <c r="B324" t="str">
-        <v>품질</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>REPORT</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B325" t="str">
-        <v>보고서</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>FAIL</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B326" t="str">
-        <v>실패</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>checks</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B327" t="str">
-        <v>개 검사</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B328" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Subscribe</v>
       </c>
       <c r="B329" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B330" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Powered by {lib}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B331" t="str">
-        <v>{lib} 기반</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B332" t="str">
-        <v>구독</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B333" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Get notified about new releases</v>
+        <v>Email address</v>
       </c>
       <c r="B334" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B335" t="str">
-        <v>닫기</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B336" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Email address</v>
+        <v>(optional)</v>
       </c>
       <c r="B337" t="str">
-        <v>이메일 주소</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>you@example.com</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B338" t="str">
-        <v>you@example.com</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>How will you use profiletool?</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B339" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>(optional)</v>
+        <v>Cancel</v>
       </c>
       <c r="B340" t="str">
-        <v>(선택)</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B341" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B342" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Cancel</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B343" t="str">
-        <v>취소</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B344" t="str">
-        <v>구독</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B345" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B346" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Close</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B347" t="str">
-        <v>닫기</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Privacy notice</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B348" t="str">
-        <v>개인정보 처리방침</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Error:</v>
       </c>
       <c r="B351" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B352" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B353" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Error:</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B354" t="str">
-        <v>오류:</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to XML</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B355" t="str">
-        <v>XML로 변환</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Convert to JSON</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B356" t="str">
-        <v>JSON으로 변환</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B357" t="str">
-        <v>ICC로 변환</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to XML…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B358" t="str">
-        <v>XML로 변환 중…</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Converting to JSON…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B359" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Converting to ICC…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B360" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Load ICC profile</v>
+        <v>No tags found.</v>
       </c>
       <c r="B361" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Tag Name</v>
       </c>
       <c r="B362" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Profile ID</v>
+        <v>ID</v>
       </c>
       <c r="B363" t="str">
-        <v>프로파일 ID</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>No tags found.</v>
+        <v>Offset</v>
       </c>
       <c r="B364" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Tag Name</v>
+        <v>Size</v>
       </c>
       <c r="B365" t="str">
-        <v>태그 이름</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ID</v>
+        <v>Pad</v>
       </c>
       <c r="B366" t="str">
-        <v>ID</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Offset</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B367" t="str">
-        <v>오프셋</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Size</v>
+        <v>Type</v>
       </c>
       <c r="B368" t="str">
-        <v>크기</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Pad</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B369" t="str">
-        <v>패딩</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Bytes changed since load</v>
+        <v>(No content)</v>
       </c>
       <c r="B370" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Type</v>
+        <v>bytes</v>
       </c>
       <c r="B371" t="str">
-        <v>유형</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Array of {type}</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B372" t="str">
-        <v>{type} 배열</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>(No content)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B373" t="str">
-        <v>(내용 없음)</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>bytes</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B374" t="str">
-        <v>바이트</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Loading full description…</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B375" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Could not load full description:</v>
+        <v>No validation output</v>
       </c>
       <c r="B376" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B377" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B378" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>No validation output</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B379" t="str">
-        <v>검증 출력 없음</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B380" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B381" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B382" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical validation error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B383" t="str">
-        <v>심각한 검증 오류</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Unknown validation status</v>
+        <v>Valid</v>
       </c>
       <c r="B384" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Warning</v>
       </c>
       <c r="B385" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Error</v>
       </c>
       <c r="B386" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Valid</v>
+        <v>Unknown</v>
       </c>
       <c r="B387" t="str">
-        <v>유효</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Warning</v>
+        <v>Pass</v>
       </c>
       <c r="B388" t="str">
-        <v>경고</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Error</v>
+        <v>Fail</v>
       </c>
       <c r="B389" t="str">
-        <v>오류</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Unknown</v>
+        <v>View in context</v>
       </c>
       <c r="B390" t="str">
-        <v>알 수 없음</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Pass</v>
+        <v>Validation detail</v>
       </c>
       <c r="B391" t="str">
-        <v>통과</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Fail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B392" t="str">
-        <v>실패</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>View in context</v>
+        <v>Field</v>
       </c>
       <c r="B393" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Validation detail</v>
+        <v>Current value</v>
       </c>
       <c r="B394" t="str">
-        <v>검증 세부 정보</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Triggered by</v>
+        <v>Required: 0</v>
       </c>
       <c r="B395" t="str">
-        <v>트리거 항목</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Field</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B396" t="str">
-        <v>항목</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Current value</v>
+        <v>Invalid</v>
       </c>
       <c r="B397" t="str">
-        <v>현재 값</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Required: 0</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B398" t="str">
-        <v>필수: 0</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Expected: {value}</v>
+        <v>Close</v>
       </c>
       <c r="B399" t="str">
-        <v>예상: {value}</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Invalid</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B400" t="str">
-        <v>잘못됨</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Close</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B402" t="str">
-        <v>닫기</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Loading XML editor…</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Loading JSON editor…</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B404" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B405" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B406" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>indent</v>
       </c>
       <c r="B408" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>들여쓰기</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>sort keys</v>
       </c>
       <c r="B409" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>키 정렬</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B410" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B411" t="str">
-        <v>들여쓰기</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B412" t="str">
-        <v>키 정렬</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B413" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B413"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B410"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B410"/>
+  <dimension ref="A1:B411"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -413,3285 +413,3293 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Round-Trip (PRMG)</v>
+        <v>{pct}% of samples were out of range and were clamped.</v>
       </c>
       <c r="B2" t="str">
-        <v>왕복 (PRMG)</v>
+        <v>샘플의 {pct}%가 범위를 벗어나 클램프되었습니다.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B3" t="str">
-        <v>참조 도구 iccRoundTrip과 동일하게 프로파일의 장치 큐브에 대해 왕복을 계산합니다. 왕복 1은 장치→PCS→장치 오차(ΔE*ab)이고, 왕복 2는 PCS 왕복 안정성을 측정합니다. PRMG 히스토그램은 Perceptual Reference Medium Gamut에 대한 상호 운용성을 나타냅니다.</v>
+        <v>왕복 (PRMG)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Use MPE (color) tags</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B4" t="str">
-        <v>MPE(색상) 태그 사용</v>
+        <v>참조 도구 iccRoundTrip과 동일하게 프로파일의 장치 큐브에 대해 왕복을 계산합니다. 왕복 1은 장치→PCS→장치 오차(ΔE*ab)이고, 왕복 2는 PCS 왕복 안정성을 측정합니다. PRMG 히스토그램은 Perceptual Reference Medium Gamut에 대한 상호 운용성을 나타냅니다.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B5" t="str">
-        <v>이 프로파일은 왕복할 수 없습니다. 이 지표에 필요한 장치↔PCS 변환이 없습니다(예: 단방향 또는 추상 프로파일).</v>
+        <v>MPE(색상) 태그 사용</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B6" t="str">
-        <v>왕복을 건너뜀: 장치 색 공간이 너무 넓어 평가할 수 없습니다(샘플이 너무 많음).</v>
+        <v>이 프로파일은 왕복할 수 없습니다. 이 지표에 필요한 장치↔PCS 변환이 없습니다(예: 단방향 또는 추상 프로파일).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Metric</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B7" t="str">
-        <v>지표</v>
+        <v>왕복을 건너뜀: 장치 색 공간이 너무 넓어 평가할 수 없습니다(샘플이 너무 많음).</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Round Trip 1</v>
+        <v>Metric</v>
       </c>
       <c r="B8" t="str">
-        <v>왕복 1</v>
+        <v>지표</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Round Trip 2</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B9" t="str">
-        <v>왕복 2</v>
+        <v>왕복 1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>device → PCS → device</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B10" t="str">
-        <v>장치 → PCS → 장치</v>
+        <v>왕복 2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>PCS round-trip stability</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B11" t="str">
-        <v>PCS 왕복 안정성</v>
+        <v>장치 → PCS → 장치</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Min ΔE</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B12" t="str">
-        <v>최소 ΔE</v>
+        <v>PCS 왕복 안정성</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Mean ΔE</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>평균 ΔE</v>
+        <v>최소 ΔE</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Max ΔE</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>최대 ΔE</v>
+        <v>평균 ΔE</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Worst L, a, b</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B15" t="str">
-        <v>최악 L, a, b</v>
+        <v>최대 ΔE</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Specified gamut</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B16" t="str">
-        <v>지정된 색역</v>
+        <v>최악 L, a, b</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>지각 참조 매체 색역</v>
+        <v>지정된 색역</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Not specified</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B18" t="str">
-        <v>지정 안 됨</v>
+        <v>지각 참조 매체 색역</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not evaluated</v>
+        <v>Not specified</v>
       </c>
       <c r="B19" t="str">
-        <v>평가 안 됨</v>
+        <v>지정 안 됨</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>PRMG interoperability</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B20" t="str">
-        <v>PRMG 상호 운용성</v>
+        <v>평가 안 됨</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Round-trip ΔE</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B21" t="str">
-        <v>왕복 ΔE</v>
+        <v>PRMG 상호 운용성</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Count</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B22" t="str">
-        <v>개수</v>
+        <v>왕복 ΔE</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Share</v>
+        <v>Count</v>
       </c>
       <c r="B23" t="str">
-        <v>비율</v>
+        <v>개수</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Total</v>
+        <v>Share</v>
       </c>
       <c r="B24" t="str">
-        <v>합계</v>
+        <v>비율</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Total</v>
       </c>
       <c r="B25" t="str">
-        <v>PRMG 평가 안 됨</v>
+        <v>합계</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B26" t="str">
-        <v>하나의 렌더링 의도에 대한 전체 프로파일 지표: 장치→PCS 변환이 둘러싸는 색역 부피 (ΔE*ab³)와 왕복 정확도 지표입니다. 렌더링 의도와 왕복 유형을 선택하면 표와 히스토그램이 그에 맞게 업데이트됩니다.</v>
+        <v>PRMG 평가 안 됨</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Round-trip type</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B27" t="str">
-        <v>왕복 유형</v>
+        <v>하나의 렌더링 의도에 대한 전체 프로파일 지표: 장치→PCS 변환이 둘러싸는 색역 부피 (ΔE*ab³)와 왕복 정확도 지표입니다. 렌더링 의도와 왕복 유형을 선택하면 표와 히스토그램이 그에 맞게 업데이트됩니다.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>이 왕복 유형에는 영향을 주지 않습니다</v>
+        <v>왕복 유형</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B29" t="str">
-        <v>이 왕복 유형은 이 프로파일에서 사용할 수 없습니다.</v>
+        <v>이 왕복 유형에는 영향을 주지 않습니다</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B30" t="str">
-        <v>왕복 ΔE 분포</v>
+        <v>이 왕복 유형은 이 프로파일에서 사용할 수 없습니다.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B31" t="str">
-        <v>평가 영역 안에 들어온 왕복 샘플이 없습니다.</v>
+        <v>왕복 ΔE 분포</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Std Dev</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B32" t="str">
-        <v>표준편차</v>
+        <v>평가 영역 안에 들어온 왕복 샘플이 없습니다.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Relative frequency</v>
+        <v>Std Dev</v>
       </c>
       <c r="B33" t="str">
-        <v>상대 빈도</v>
+        <v>표준편차</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Cumulative frequency</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>누적 빈도</v>
+        <v>상대 빈도</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Horizontal scale</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B35" t="str">
-        <v>가로 배율</v>
+        <v>누적 빈도</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Integer ΔE</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B36" t="str">
-        <v>정수 ΔE</v>
+        <v>가로 배율</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Auto-scale</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B37" t="str">
-        <v>자동 배율</v>
+        <v>정수 ΔE</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Bins</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B38" t="str">
-        <v>구간</v>
+        <v>자동 배율</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>CLUT Image</v>
+        <v>Bins</v>
       </c>
       <c r="B39" t="str">
-        <v>CLUT 이미지</v>
+        <v>구간</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B40" t="str">
-        <v>장치↔PCS 변환의 색상 조회 테이블(CLUT)을 하나의 이미지로 타일 형태로 배열한 것입니다. 볼 렌더링 의도 테이블을 선택하세요.</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B41" t="str">
-        <v>이 프로파일에는 시각화할 CLUT 기반 장치↔PCS 테이블이 없습니다.</v>
+        <v>장치↔PCS 변환의 색상 조회 테이블(CLUT)을 하나의 이미지로 타일 형태로 배열한 것입니다. 볼 렌더링 의도 테이블을 선택하세요.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Gamut Image</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B42" t="str">
-        <v>색역 이미지</v>
+        <v>이 프로파일에는 시각화할 CLUT 기반 장치↔PCS 테이블이 없습니다.</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B43" t="str">
-        <v>색역 태그의 색역 내/외 맵: PCS 색상이 재현 가능한 곳은 중립, 장치 색역을 벗어나는 곳은 빨강으로 표시됩니다.</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B44" t="str">
-        <v>이 프로파일에는 시각화할 색역 태그가 없습니다.</v>
+        <v>색역 태그의 색역 내/외 맵: PCS 색상이 재현 가능한 곳은 중립, 장치 색역을 벗어나는 곳은 빨강으로 표시됩니다.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B45" t="str">
-        <v>세로 배율</v>
+        <v>이 프로파일에는 시각화할 색역 태그가 없습니다.</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>X–Y</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B46" t="str">
-        <v>X–Y</v>
+        <v>세로 배율</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Tone increase</v>
+        <v>X–Y</v>
       </c>
       <c r="B47" t="str">
-        <v>톤 증가</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B48" t="str">
-        <v>톤 증가(출력 − 입력)</v>
+        <v>톤 증가</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Show full dump</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B49" t="str">
-        <v>전체 덤프 표시</v>
+        <v>톤 증가(출력 − 입력)</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Output truncated for performance.</v>
+        <v>Show full dump</v>
       </c>
       <c r="B50" t="str">
-        <v>성능을 위해 출력이 잘렸습니다.</v>
+        <v>전체 덤프 표시</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B51" t="str">
-        <v>색역 내 개요 (RT0)</v>
+        <v>성능을 위해 출력이 잘렸습니다.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B52" t="str">
-        <v>역변환 + 색역 (RT1)</v>
+        <v>색역 내 개요 (RT0)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B53" t="str">
-        <v>재현성 (RT2)</v>
+        <v>역변환 + 색역 (RT1)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>PRMG interoperability</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B54" t="str">
-        <v>PRMG 상호운용성</v>
+        <v>재현성 (RT2)</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B55" t="str">
-        <v>iccviz 개요: 장치 값 격자를 PCS로, 다시 장치로, 그리고 다시 PCS로 변환하여 두 PCS 결과 사이의 ΔE*ab를 측정합니다. 색역 내 안정성을 빠르게 확인합니다.</v>
+        <v>PRMG 상호운용성</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B56" t="str">
-        <v>iccRoundTrip 왕복 1: 각 장치 색상의 PCS와 Lab → 장치 → Lab 왕복을 한 번 거친 후의 PCS 사이의 ΔE*ab. 역변환 정확도와 색역 매핑을 반영합니다.</v>
+        <v>iccviz 개요: 장치 값 격자를 PCS로, 다시 장치로, 그리고 다시 PCS로 변환하여 두 PCS 결과 사이의 ΔE*ab를 측정합니다. 색역 내 안정성을 빠르게 확인합니다.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip 왕복 2: 첫 번째와 두 번째 왕복 사이의 ΔE*ab — 반복되는 PCS 왕복이 얼마나 안정적인지(재현성, 첫 왕복의 색역 클리핑과 무관)를 나타냅니다.</v>
+        <v>iccRoundTrip 왕복 1: 각 장치 색상의 PCS와 Lab → 장치 → Lab 왕복을 한 번 거친 후의 PCS 사이의 ΔE*ab. 역변환 정확도와 색역 매핑을 반영합니다.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip PRMG: Perceptual Reference Medium Gamut 내의 PCS 색상을 한 번 왕복(Lab → 장치 → Lab)합니다. ΔE*ab 분포는 프로파일 간 상호운용성을 나타냅니다.</v>
+        <v>iccRoundTrip 왕복 2: 첫 번째와 두 번째 왕복 사이의 ΔE*ab — 반복되는 PCS 왕복이 얼마나 안정적인지(재현성, 첫 왕복의 색역 클리핑과 무관)를 나타냅니다.</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Settings</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B59" t="str">
-        <v>설정</v>
+        <v>iccRoundTrip PRMG: Perceptual Reference Medium Gamut 내의 PCS 색상을 한 번 왕복(Lab → 장치 → Lab)합니다. ΔE*ab 분포는 프로파일 간 상호운용성을 나타냅니다.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Display</v>
+        <v>Settings</v>
       </c>
       <c r="B60" t="str">
-        <v>표시</v>
+        <v>설정</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Background</v>
+        <v>Display</v>
       </c>
       <c r="B61" t="str">
-        <v>배경</v>
+        <v>표시</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Language</v>
+        <v>Background</v>
       </c>
       <c r="B62" t="str">
-        <v>언어</v>
+        <v>배경</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>System</v>
+        <v>Language</v>
       </c>
       <c r="B63" t="str">
-        <v>시스템</v>
+        <v>언어</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Light</v>
+        <v>System</v>
       </c>
       <c r="B64" t="str">
-        <v>밝게</v>
+        <v>시스템</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dark</v>
+        <v>Light</v>
       </c>
       <c r="B65" t="str">
-        <v>어둡게</v>
+        <v>밝게</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>System default</v>
+        <v>Dark</v>
       </c>
       <c r="B66" t="str">
-        <v>시스템 기본값</v>
+        <v>어둡게</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Number format</v>
+        <v>System default</v>
       </c>
       <c r="B67" t="str">
-        <v>숫자 형식</v>
+        <v>시스템 기본값</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Hexadecimal</v>
+        <v>Number format</v>
       </c>
       <c r="B68" t="str">
-        <v>16진수</v>
+        <v>숫자 형식</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Decimal</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B69" t="str">
-        <v>10진수</v>
+        <v>16진수</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Help</v>
+        <v>Decimal</v>
       </c>
       <c r="B70" t="str">
-        <v>도움말</v>
+        <v>10진수</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Contact</v>
+        <v>Help</v>
       </c>
       <c r="B71" t="str">
-        <v>문의</v>
+        <v>도움말</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>User guide</v>
+        <v>Contact</v>
       </c>
       <c r="B72" t="str">
-        <v>사용자 가이드</v>
+        <v>문의</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Search guide</v>
+        <v>User guide</v>
       </c>
       <c r="B73" t="str">
-        <v>가이드 검색</v>
+        <v>사용자 가이드</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search the user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B74" t="str">
-        <v>사용자 가이드 검색</v>
+        <v>가이드 검색</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Previous match</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B75" t="str">
-        <v>이전 검색 결과</v>
+        <v>사용자 가이드 검색</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Next match</v>
+        <v>Previous match</v>
       </c>
       <c r="B76" t="str">
-        <v>다음 검색 결과</v>
+        <v>이전 검색 결과</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Close user guide</v>
+        <v>Next match</v>
       </c>
       <c r="B77" t="str">
-        <v>사용자 가이드 닫기</v>
+        <v>다음 검색 결과</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading…</v>
+        <v>Close user guide</v>
       </c>
       <c r="B78" t="str">
-        <v>불러오는 중…</v>
+        <v>사용자 가이드 닫기</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>사용자 가이드를 불러올 수 없습니다.</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>None</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B80" t="str">
-        <v>없음</v>
+        <v>사용자 가이드를 불러올 수 없습니다.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B81" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Based on</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B82" t="str">
-        <v/>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>demo implementation</v>
+        <v>Based on</v>
       </c>
       <c r="B83" t="str">
-        <v>데모 구현 기반</v>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Validating…</v>
+        <v>demo implementation</v>
       </c>
       <c r="B84" t="str">
-        <v>검증 중…</v>
+        <v>데모 구현 기반</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Save ICC profile</v>
+        <v>Validating…</v>
       </c>
       <c r="B85" t="str">
-        <v>ICC 프로파일 저장</v>
+        <v>검증 중…</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B86" t="str">
-        <v>● 변경됨 — 저장되지 않음</v>
+        <v>ICC 프로파일 저장</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B87" t="str">
-        <v>프로파일</v>
+        <v>● 변경됨 — 저장되지 않음</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Show profile pool</v>
+        <v>Profiles</v>
       </c>
       <c r="B88" t="str">
-        <v>프로파일 풀 표시</v>
+        <v>프로파일</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Collapse</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B89" t="str">
-        <v>접기</v>
+        <v>프로파일 풀 표시</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Load Profiles</v>
+        <v>Collapse</v>
       </c>
       <c r="B90" t="str">
-        <v>프로파일 불러오기</v>
+        <v>접기</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Remove</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B91" t="str">
-        <v>제거</v>
+        <v>프로파일 불러오기</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Remove</v>
       </c>
       <c r="B92" t="str">
-        <v>여기에 ICC 프로파일을 놓으세요</v>
+        <v>제거</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B93" t="str">
-        <v>또는 이미지(TIFF/PNG/JPEG)를 놓아 내장된 프로파일을 추출하세요 — 파일은 사용자 장치에 그대로 남습니다.</v>
+        <v>여기에 ICC 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>New from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B94" t="str">
-        <v>.cube에서 새로 만들기</v>
+        <v>또는 이미지(TIFF/PNG/JPEG)를 놓아 내장된 프로파일을 추출하세요 — 파일은 사용자 장치에 그대로 남습니다.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Sort by name</v>
+        <v>New from .cube</v>
       </c>
       <c r="B95" t="str">
-        <v>이름순 정렬</v>
+        <v>.cube에서 새로 만들기</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B96" t="str">
-        <v>A–Z</v>
+        <v>이름순 정렬</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B97" t="str">
-        <v>.cube에서 새 프로파일</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B98" t="str">
-        <v>Adobe/Resolve의 .cube 3D LUT에서 ICC DeviceLink를 만듭니다. 결과는 풀에 추가되고 다운로드됩니다.</v>
+        <v>.cube에서 새 프로파일</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B99" t="str">
-        <v>.cube 파일 선택</v>
+        <v>Adobe/Resolve의 .cube 3D LUT에서 ICC DeviceLink를 만듭니다. 결과는 풀에 추가되고 다운로드됩니다.</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B100" t="str">
+        <v>.cube 파일 선택</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B101" t="str">
         <v>또는 여기에 놓거나 아래에 붙여넣으세요</v>
       </c>
     </row>
-    <row r="101" xml:space="preserve">
-      <c r="A101" t="str" xml:space="preserve">
+    <row r="102" xml:space="preserve">
+      <c r="A102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B101" t="str" xml:space="preserve">
+      <c r="B102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B102" t="str">
-        <v>취소</v>
-      </c>
-    </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B103" t="str">
-        <v>DeviceLink 만들기</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B104" t="str">
-        <v>만드는 중…</v>
+        <v>DeviceLink 만들기</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B105" t="str">
-        <v>해당 파일을 읽을 수 없습니다.</v>
+        <v>만드는 중…</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B106" t="str">
-        <v>프로파일</v>
+        <v>해당 파일을 읽을 수 없습니다.</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B107" t="str">
-        <v>비교</v>
+        <v>프로파일</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B108" t="str">
-        <v>링크</v>
+        <v>비교</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B109" t="str">
-        <v>스펙트럴</v>
+        <v>링크</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B110" t="str">
-        <v>풀에서 이 탭으로 프로파일을 끌어다 놓으세요</v>
+        <v>스펙트럴</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B111" t="str">
-        <v>제거</v>
+        <v>풀에서 이 탭으로 프로파일을 끌어다 놓으세요</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B112" t="str">
-        <v>선택된 프로파일 없음</v>
+        <v>제거</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B113" t="str">
-        <v>풀에서 프로파일을 '프로파일' 탭으로 끌어다 놓아 검사하세요.</v>
+        <v>선택된 프로파일 없음</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B114" t="str">
-        <v>아직 비교할 항목이 없습니다</v>
+        <v>풀에서 프로파일을 '프로파일' 탭으로 끌어다 놓아 검사하세요.</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B115" t="str">
-        <v>하나 이상의 프로파일을 '비교' 탭으로 끌어다 놓으세요.</v>
+        <v>아직 비교할 항목이 없습니다</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B116" t="str">
-        <v>색역 비교</v>
+        <v>하나 이상의 프로파일을 '비교' 탭으로 끌어다 놓으세요.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B117" t="str">
-        <v>3D 색역 및 2D 슬라이스 보기가 여기에 추가됩니다. 누적:</v>
+        <v>색역 비교</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B118" t="str">
-        <v>렌더링 의도</v>
+        <v>3D 색역 및 2D 슬라이스 보기가 여기에 추가됩니다. 누적:</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B119" t="str">
-        <v>셸</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B120" t="str">
-        <v>와이어프레임</v>
+        <v>셸</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B121" t="str">
-        <v>축 번호</v>
+        <v>와이어프레임</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B122" t="str">
-        <v>불투명도</v>
+        <v>축 번호</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>색상</v>
+        <v>불투명도</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>단색</v>
+        <v>색상</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>값 기준</v>
+        <v>단색</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>색상(Hue) 기준</v>
+        <v>값 기준</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>회전</v>
+        <v>색상(Hue) 기준</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>턴테이블</v>
+        <v>회전</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>궤도</v>
+        <v>턴테이블</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>드래그 속도</v>
+        <v>궤도</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>롤</v>
+        <v>드래그 속도</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>롤 속도</v>
+        <v>롤</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>색역 생성 중…</v>
+        <v>롤 속도</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>색역 없음</v>
+        <v>색역 생성 중…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>표시/숨기기</v>
+        <v>색역 없음</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>3D 색역 셸</v>
+        <v>표시/숨기기</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>2D 색역 슬라이스</v>
+        <v>3D 색역 셸</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>평면</v>
+        <v>2D 색역 슬라이스</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>L*</v>
+        <v>평면</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>선택한 프로파일 중 색역을 도출할 장치→PCS 변환을 가진 것이 없습니다.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>링크</v>
+        <v>선택한 프로파일 중 색역을 도출할 장치→PCS 변환을 가진 것이 없습니다.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>DeviceLink 생성과 다중 프로파일 변환은 이후 단계에서 제공됩니다.</v>
+        <v>링크</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>더 많은 링크 메이커(DeviceLink, …)가 여기에 추가됩니다.</v>
+        <v>DeviceLink 생성과 다중 프로파일 변환은 이후 단계에서 제공됩니다.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>V4 디스플레이 메이커</v>
+        <v>더 많은 링크 메이커(DeviceLink, …)가 여기에 추가됩니다.</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B147" t="str">
-        <v>V5 RGB 디스플레이와 V5 관찰자 프로파일을 여기에 끌어다 놓아 V4 디스플레이 프로파일을 만드세요.</v>
+        <v>V4 디스플레이 메이커</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>V5 RGB 디스플레이</v>
+        <v>V5 RGB 디스플레이와 V5 관찰자 프로파일을 여기에 끌어다 놓아 V4 디스플레이 프로파일을 만드세요.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>디스플레이 프로파일을 놓으세요</v>
+        <v>V5 RGB 디스플레이</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>V5 관찰자 (PCC)</v>
+        <v>디스플레이 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>관찰자 프로파일을 놓으세요</v>
+        <v>V5 관찰자 (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>V5 RGB 디스플레이도 관찰자도 아닌 프로파일은 무시되었습니다.</v>
+        <v>관찰자 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>V4 디스플레이 프로파일 만들기</v>
+        <v>V5 RGB 디스플레이도 관찰자도 아닌 프로파일은 무시되었습니다.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>프로파일 이름</v>
+        <v>V4 디스플레이 프로파일 만들기</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>만들기</v>
+        <v>프로파일 이름</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>만드는 중…</v>
+        <v>만들기</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>'{name}'을(를) 만들었습니다 — 풀과 이 탭에 추가되었습니다.</v>
+        <v>만드는 중…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>링크 파이프라인</v>
+        <v>'{name}'을(를) 만들었습니다 — 풀과 이 탭에 추가되었습니다.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B159" t="str">
-        <v>프로파일 체인을 구성한 다음 DeviceLink를 만들거나, 이미지를 변환하거나, 색상 데이터셋을 변환하세요.</v>
+        <v>링크 파이프라인</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B160" t="str">
-        <v>완료</v>
+        <v>프로파일 체인을 구성한 다음 DeviceLink를 만들거나, 이미지를 변환하거나, 색상 데이터셋을 변환하세요.</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B161" t="str">
-        <v>변환할 이미지를 드롭하세요 (TIFF/PNG/JPEG)</v>
+        <v>완료</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B162" t="str">
-        <v>이미지 확인 중…</v>
+        <v>변환할 이미지를 드롭하세요 (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B163" t="str">
-        <v>지원되지 않는 이미지입니다 (TIFF, PNG 또는 JPEG).</v>
+        <v>이미지 확인 중…</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B164" t="str">
-        <v>이미지가 너무 큽니다 ({mp} MP, 제한 {max} MP).</v>
+        <v>지원되지 않는 이미지입니다 (TIFF, PNG 또는 JPEG).</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B165" t="str">
-        <v>이미지 변환</v>
+        <v>이미지가 너무 큽니다 ({mp} MP, 제한 {max} MP).</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B166" t="str">
-        <v>변환 중…</v>
+        <v>이미지 변환</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B167" t="str">
-        <v>체인을 시작하려면 프로파일을 드롭하세요</v>
+        <v>변환 중…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B168" t="str">
-        <v>제거됨</v>
+        <v>체인을 시작하려면 프로파일을 드롭하세요</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B169" t="str">
-        <v>앞으로 이동</v>
+        <v>제거됨</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B170" t="str">
-        <v>뒤로 이동</v>
+        <v>앞으로 이동</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B171" t="str">
-        <v>위로 이동</v>
+        <v>뒤로 이동</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B172" t="str">
-        <v>아래로 이동</v>
+        <v>위로 이동</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B173" t="str">
-        <v>렌더링 인텐트 (전체)</v>
+        <v>아래로 이동</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B174" t="str">
-        <v>이 변환의 렌더링 인텐트</v>
+        <v>렌더링 인텐트 (전체)</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B175" t="str">
-        <v>변환마다 렌더링 인텐트가 다릅니다</v>
+        <v>이 변환의 렌더링 인텐트</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B176" t="str">
-        <v>체인 방향 전환 (첫 변환을 반전시키고 체인 전체에 반영됩니다)</v>
+        <v>변환마다 렌더링 인텐트가 다릅니다</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B177" t="str">
-        <v>체인에 포함된 프로파일이 풀에서 제거되었습니다 — 계속하려면 제거하세요.</v>
+        <v>체인 방향 전환 (첫 변환을 반전시키고 체인 전체에 반영됩니다)</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B178" t="str">
-        <v>체인</v>
+        <v>체인에 포함된 프로파일이 풀에서 제거되었습니다 — 계속하려면 제거하세요.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B179" t="str">
-        <v>체인을 분석할 수 없습니다.</v>
+        <v>체인</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B180" t="str">
-        <v>체인 확인 중…</v>
+        <v>체인을 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B181" t="str">
-        <v>체인이 연결되지 않습니다 ({detail}).</v>
+        <v>체인 확인 중…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>프로파일 {n}이(가) 이전 단계와 연결되지 않습니다 ({detail}).</v>
+        <v>체인이 연결되지 않습니다 ({detail}).</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B183" t="str">
-        <v>이미지를 처리하기 전에 체인을 수정하세요</v>
+        <v>프로파일 {n}이(가) 이전 단계와 연결되지 않습니다 ({detail}).</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B184" t="str">
-        <v>지우기</v>
+        <v>이미지를 처리하기 전에 체인을 수정하세요</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B185" t="str">
-        <v>DeviceLink 만들기</v>
+        <v>지우기</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B186" t="str">
-        <v>DeviceLink 이름</v>
+        <v>DeviceLink 만들기</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B187" t="str">
-        <v>생성 중…</v>
+        <v>DeviceLink 이름</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B188" t="str">
-        <v>"{name}" 생성됨 — 풀과 이 탭에 추가되었습니다.</v>
+        <v>생성 중…</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B189" t="str">
-        <v>{src} 이미지를 드롭하면 {dst}(으)로 변환됩니다 — 결과는 다운로드되며 저장되지 않습니다.</v>
+        <v>"{name}" 생성됨 — 풀과 이 탭에 추가되었습니다.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B190" t="str">
-        <v>이미지를 처리하려면 체인을 구성하세요</v>
+        <v>{src} 이미지를 드롭하면 {dst}(으)로 변환됩니다 — 결과는 다운로드되며 저장되지 않습니다.</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B191" t="str">
-        <v>이 체인은 이미지 색공간에서 시작하고 끝나지 않습니다</v>
+        <v>이미지를 처리하려면 체인을 구성하세요</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B192" t="str">
-        <v>변환된 이미지를 저장했습니다.</v>
+        <v>이 체인은 이미지 색공간에서 시작하고 끝나지 않습니다</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B193" t="str">
-        <v>색상 데이터셋을 드롭하세요 (CGATS/CSV/CxF/JSON)</v>
+        <v>변환된 이미지를 저장했습니다.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B194" t="str">
-        <v>해당 파일을 읽을 수 없습니다.</v>
+        <v>색상 데이터셋을 드롭하세요 (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B195" t="str">
-        <v>데이터 파일이 너무 큽니다.</v>
+        <v>해당 파일을 읽을 수 없습니다.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B196" t="str">
-        <v>데이터 변환</v>
+        <v>데이터 파일이 너무 큽니다.</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B197" t="str">
-        <v>변환 중…</v>
+        <v>데이터 변환</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B198" t="str">
-        <v>선호</v>
+        <v>변환 중…</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B199" t="str">
-        <v>관측자</v>
+        <v>선호</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B200" t="str">
-        <v>광원</v>
+        <v>관측자</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B201" t="str">
-        <v>조건</v>
+        <v>광원</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B202" t="str">
-        <v>중복 {n}건 필터링</v>
+        <v>조건</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B203" t="str">
-        <v>중앙값</v>
+        <v>중복 {n}건 필터링</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B204" t="str">
-        <v>평균값</v>
+        <v>중앙값</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B205" t="str">
-        <v>패치</v>
+        <v>평균값</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B206" t="str">
-        <v>중복 {n}건</v>
+        <v>패치</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B207" t="str">
-        <v>변환 결과</v>
+        <v>중복 {n}건</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B208" t="str">
-        <v>{src} → {dst} · 패치 {n}개</v>
+        <v>변환 결과</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B209" t="str">
-        <v>전체 {total}건 중 처음 {shown}건 표시 중 — 저장하면 전체가 기록됩니다.</v>
+        <v>{src} → {dst} · 패치 {n}개</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B210" t="str">
-        <v>다른 이름으로 저장</v>
+        <v>전체 {total}건 중 처음 {shown}건 표시 중 — 저장하면 전체가 기록됩니다.</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B211" t="str">
-        <v>저장</v>
+        <v>다른 이름으로 저장</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B212" t="str">
-        <v>변환 반전</v>
+        <v>저장</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B213" t="str">
-        <v>반전 중…</v>
+        <v>변환 반전</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B214" t="str">
-        <v>반전</v>
+        <v>반전 중…</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B215" t="str">
-        <v>마지막 단계</v>
+        <v>반전</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B216" t="str">
-        <v>첫 단계</v>
+        <v>마지막 단계</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B217" t="str">
-        <v>{in} 데이터 → {out} 검색</v>
+        <v>첫 단계</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B218" t="str">
-        <v>반전에는 2–3개 프로파일로 이루어진 체인이 필요합니다</v>
+        <v>{in} 데이터 → {out} 검색</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B219" t="str">
-        <v>데이터셋은 {in}이어야 합니다. 역검색은 {out}과 패치별 역변환 가능성 비용을 산출합니다.</v>
+        <v>반전에는 2–3개 프로파일로 이루어진 체인이 필요합니다</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B220" t="str">
-        <v>ΔE 비용</v>
+        <v>데이터셋은 {in}이어야 합니다. 역검색은 {out}과 패치별 역변환 가능성 비용을 산출합니다.</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B221" t="str">
-        <v>이 이미지에는 내장된 ICC 프로파일이 있습니다.</v>
+        <v>ΔE 비용</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B222" t="str">
-        <v>추출 후 체인에 추가</v>
+        <v>이 이미지에는 내장된 ICC 프로파일이 있습니다.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B223" t="str">
-        <v>추출 중…</v>
+        <v>추출 후 체인에 추가</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B224" t="str">
-        <v>닫기</v>
+        <v>추출 중…</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B225" t="str">
-        <v>내장된 프로파일을 추출했습니다 — 풀에 추가되고 체인의 첫 번째 자리에 배치되었습니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B226" t="str">
-        <v>이미지 출력 옵션</v>
+        <v>내장된 프로파일을 추출했습니다 — 풀에 추가되고 체인의 첫 번째 자리에 배치되었습니다.</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B227" t="str">
-        <v>인코딩</v>
+        <v>이미지 출력 옵션</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B228" t="str">
-        <v>원본과 동일</v>
+        <v>인코딩</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B229" t="str">
-        <v>8비트</v>
+        <v>원본과 동일</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>16비트</v>
+        <v>8비트</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B231" t="str">
-        <v>부동소수점 (32비트)</v>
+        <v>16비트</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B232" t="str">
-        <v>압축</v>
+        <v>부동소수점 (32비트)</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B233" t="str">
-        <v>없음</v>
+        <v>압축</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B234" t="str">
-        <v>플레이너</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B235" t="str">
-        <v>컴포지트</v>
+        <v>플레이너</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B236" t="str">
-        <v>분리</v>
+        <v>컴포지트</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B237" t="str">
-        <v>CMM 보간</v>
+        <v>분리</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B238" t="str">
-        <v>사면체</v>
+        <v>CMM 보간</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B239" t="str">
-        <v>선형</v>
+        <v>사면체</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B240" t="str">
-        <v>ICC 포함</v>
+        <v>선형</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B241" t="str">
-        <v>인코딩, 압축, 플레이너 방식은 저장되는 TIFF에 반영됩니다. TIFF 전용 옵션(부동소수점, LZW/ZIP, 분리)을 설정하지 않으면 RGB/Gray 출력은 PNG로 유지됩니다.</v>
+        <v>ICC 포함</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B242" t="str">
-        <v>스펙트럴 TIFF 조합</v>
+        <v>인코딩, 압축, 플레이너 방식은 저장되는 TIFF에 반영됩니다. TIFF 전용 옵션(부동소수점, LZW/ZIP, 분리)을 설정하지 않으면 RGB/Gray 출력은 PNG로 유지됩니다.</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B243" t="str">
-        <v>단일 채널 스펙트럴 이미지를 채널 순서대로 드롭하면 하나의 다중 채널 TIFF로 조합됩니다.</v>
+        <v>스펙트럴 TIFF 조합</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B244" t="str">
-        <v>스펙트럴 이미지를 여기에 드롭하세요 (또는 클릭하여 선택)</v>
+        <v>단일 채널 스펙트럴 이미지를 채널 순서대로 드롭하면 하나의 다중 채널 TIFF로 조합됩니다.</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B245" t="str">
-        <v>ch</v>
+        <v>스펙트럴 이미지를 여기에 드롭하세요 (또는 클릭하여 선택)</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B246" t="str">
-        <v>조합 후 저장</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B247" t="str">
-        <v>조합 중…</v>
+        <v>조합 후 저장</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B248" t="str">
-        <v>{n}개 채널을 조합했습니다.</v>
+        <v>조합 중…</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B249" t="str">
-        <v>이미지로 인식되는 파일이 없습니다 (TIFF, PNG 또는 JPEG).</v>
+        <v>{n}개 채널을 조합했습니다.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B250" t="str">
-        <v>취소</v>
+        <v>이미지로 인식되는 파일이 없습니다 (TIFF, PNG 또는 JPEG).</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B251" t="str">
-        <v>{n}개 파일을 불러오지 못했습니다</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B252" t="str">
-        <v>이 파일들은 ICC 프로파일이 아니므로 풀에 추가되지 않았습니다:</v>
+        <v>{n}개 파일을 불러오지 못했습니다</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B253" t="str">
-        <v>확인</v>
+        <v>이 파일들은 ICC 프로파일이 아니므로 풀에 추가되지 않았습니다:</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B254" t="str">
-        <v>ICC 프로파일을 여기에 놓기</v>
+        <v>확인</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B255" t="str">
-        <v>또는</v>
+        <v>ICC 프로파일을 여기에 놓기</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B256" t="str">
-        <v>파일 선택</v>
+        <v>또는</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B257" t="str">
-        <v>.icc 및 .icm 파일</v>
+        <v>파일 선택</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B258" t="str">
-        <v>헤더</v>
+        <v>.icc 및 .icm 파일</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B259" t="str">
-        <v>태그</v>
+        <v>헤더</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B260" t="str">
-        <v>검증</v>
+        <v>태그</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B261" t="str">
-        <v>분석</v>
+        <v>검증</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B262" t="str">
-        <v>중립축 잉킹</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B263" t="str">
-        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
+        <v>중립축 잉킹</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B264" t="str">
-        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B265" t="str">
-        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
+        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B266" t="str">
-        <v>렌더링 의도</v>
+        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B267" t="str">
-        <v>% 잉크</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Perceptual</v>
+        <v>% ink</v>
       </c>
       <c r="B268" t="str">
-        <v>지각적</v>
+        <v>% 잉크</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B269" t="str">
-        <v>상대 색도</v>
+        <v>지각적</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B270" t="str">
-        <v>채도</v>
+        <v>상대 색도</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B271" t="str">
-        <v>절대 색도</v>
+        <v>채도</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>프로파일 통계</v>
+        <v>절대 색도</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B273" t="str">
-        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
+        <v>프로파일 통계</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B274" t="str">
-        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
+        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B275" t="str">
-        <v>렌더링 의도</v>
+        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B276" t="str">
-        <v>색역 부피 (ΔE³)</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B277" t="str">
-        <v>왕복 ΔE</v>
+        <v>색역 부피 (ΔE³)</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B278" t="str">
-        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
+        <v>왕복 ΔE</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B279" t="str">
-        <v>평균</v>
+        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B280" t="str">
-        <v>P90</v>
+        <v>평균</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B281" t="str">
-        <v>최대</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B282" t="str">
-        <v>분석 중…</v>
+        <v>최대</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B283" t="str">
-        <v>분석</v>
+        <v>분석 중…</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B284" t="str">
-        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B285" t="str">
-        <v>플롯</v>
+        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B286" t="str">
-        <v>원시 출력</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B287" t="str">
-        <v>XML</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B289" t="str">
-        <v>곡선</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B290" t="str">
-        <v>입력 곡선</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B291" t="str">
-        <v>출력 곡선</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B292" t="str">
-        <v>CLUT 이미지</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B293" t="str">
-        <v>색역 이미지</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B294" t="str">
-        <v>색도</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B295" t="str">
-        <v>산점도</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B296" t="str">
-        <v>톤 응답 곡선</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B297" t="str">
-        <v>곡선 표</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B298" t="str">
-        <v>표</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B299" t="str">
-        <v>데이터</v>
+        <v>표</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B300" t="str">
-        <v>평가</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B301" t="str">
-        <v>불러오는 중…</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B302" t="str">
-        <v>입력</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B303" t="str">
-        <v>출력</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B304" t="str">
-        <v>부동 소수점</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B305" t="str">
-        <v>격자점</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B306" t="str">
-        <v>정규화</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B307" t="str">
-        <v>사람용</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B308" t="str">
-        <v>장치 → PCS</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B309" t="str">
-        <v>PCS → 장치</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B310" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B311" t="str">
-        <v>불러오는 중…</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B312" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B313" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B314" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B315" t="str">
-        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B316" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B317" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B318" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B319" t="str">
-        <v>보안</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B320" t="str">
-        <v>적합성</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B321" t="str">
-        <v>품질</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B322" t="str">
-        <v>보고서</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B323" t="str">
-        <v>실패</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B324" t="str">
-        <v>개 검사</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B325" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B326" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B327" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B328" t="str">
-        <v>{lib} 기반</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B329" t="str">
-        <v>구독</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B330" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B331" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B332" t="str">
-        <v>닫기</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B333" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B334" t="str">
-        <v>이메일 주소</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B335" t="str">
-        <v>you@example.com</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B336" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B337" t="str">
-        <v>(선택)</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B338" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B339" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B340" t="str">
-        <v>취소</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B341" t="str">
-        <v>구독</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B342" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B343" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B344" t="str">
-        <v>닫기</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B345" t="str">
-        <v>개인정보 처리방침</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B346" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B347" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B348" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B351" t="str">
-        <v>오류:</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B352" t="str">
-        <v>XML로 변환</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B353" t="str">
-        <v>JSON으로 변환</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B354" t="str">
-        <v>ICC로 변환</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B355" t="str">
-        <v>XML로 변환 중…</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B356" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B357" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B358" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B359" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B360" t="str">
-        <v>프로파일 ID</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B361" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B362" t="str">
-        <v>태그 이름</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B363" t="str">
-        <v>ID</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B364" t="str">
-        <v>오프셋</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B365" t="str">
-        <v>크기</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B366" t="str">
-        <v>패딩</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B367" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B368" t="str">
-        <v>유형</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B369" t="str">
-        <v>{type} 배열</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B370" t="str">
-        <v>(내용 없음)</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B371" t="str">
-        <v>바이트</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B372" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B373" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B374" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B375" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B376" t="str">
-        <v>검증 출력 없음</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B377" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B378" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B379" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B380" t="str">
-        <v>심각한 검증 오류</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B381" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B382" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B383" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B384" t="str">
-        <v>유효</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B385" t="str">
-        <v>경고</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B386" t="str">
-        <v>오류</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B387" t="str">
-        <v>알 수 없음</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B388" t="str">
-        <v>통과</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B389" t="str">
-        <v>실패</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B390" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B391" t="str">
-        <v>검증 세부 정보</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B392" t="str">
-        <v>트리거 항목</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B393" t="str">
-        <v>항목</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B394" t="str">
-        <v>현재 값</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B395" t="str">
-        <v>필수: 0</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B396" t="str">
-        <v>예상: {value}</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B397" t="str">
-        <v>잘못됨</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B398" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B399" t="str">
-        <v>닫기</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B402" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B404" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B405" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B406" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B408" t="str">
-        <v>들여쓰기</v>
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B409" t="str">
-        <v>키 정렬</v>
+        <v>들여쓰기</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B410" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B410" t="str">
+      <c r="B411" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B410"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B411"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B411"/>
+  <dimension ref="A1:B445"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -2555,1151 +2555,1423 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Perceptual</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B269" t="str">
-        <v>지각적</v>
+        <v>L* 출력(톤)</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B270" t="str">
-        <v>상대 색도</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Saturation</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B271" t="str">
-        <v>채도</v>
+        <v>극값 측색</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B272" t="str">
-        <v>절대 색도</v>
+        <v>프로파일 재현 범위의 양 끝: 기재의 백색, 인쇄할 수 있는 가장 어두운 검정, 그 검정에 드는 잉크량, 그리고 각 색상이 가장 진해지는 지점.</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Profile Statistics</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B273" t="str">
-        <v>프로파일 통계</v>
+        <v>백색점은 색료가 0일 때의 색 — 즉 아무것도 인쇄하지 않은 기재입니다. 흑색점은 PCS 검정(L*=0, a*=b*=0)을 선택한 B2A 테이블에 통과시켜 프로파일이 검정에 대해 선택하는 잉킹을 얻은 뒤, 그 잉킹을 A2B1로 되읽어 구합니다. 총 잉크량(TAC)은 그 잉킹의 합입니다. 절대 측색은 기재 자체의 색을 보여 주고, 상대 측색은 이를 완전한 백색 기준으로 다시 맞춥니다.</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative</v>
       </c>
       <c r="B274" t="str">
-        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
+        <v>상대</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Absolute</v>
       </c>
       <c r="B275" t="str">
-        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
+        <v>절대</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Rendering intent</v>
+        <v>White point</v>
       </c>
       <c r="B276" t="str">
-        <v>렌더링 의도</v>
+        <v>백색점</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Black point</v>
       </c>
       <c r="B277" t="str">
-        <v>색역 부피 (ΔE³)</v>
+        <v>흑색점</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B278" t="str">
-        <v>왕복 ΔE</v>
+        <v>흑색점에서의 잉킹</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>TAC</v>
       </c>
       <c r="B279" t="str">
-        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>mean</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B280" t="str">
-        <v>평균</v>
+        <v>이 프로파일에는 매체 백색점 태그가 없으므로 절대 측색을 사용할 수 없습니다.</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>P90</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B281" t="str">
-        <v>P90</v>
+        <v>극값 측색은 출력(프린터) 프로파일에서만 사용할 수 있습니다 — 색료가 0이면 아무것도 인쇄하지 않은 기재라고 가정합니다.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>max</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B282" t="str">
-        <v>최대</v>
+        <v>솔리드 대 최대 크로마</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysing…</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B283" t="str">
-        <v>분석 중…</v>
+        <v>각 잉크 꼭짓점의 위치와 거기에 이르는 도중 크로마가 가장 높은 지점입니다. A2B1을 통해 측정하므로 이 행들은 위의 렌더링 의도에 따라 바뀌지 않습니다. 정상적인 프로파일에서는 두 행이 일치합니다. 최대 크로마가 솔리드보다 먼저 도달하면 그 지점을 넘어선 잉크는 어둡게만 만듭니다.</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Analysis</v>
+        <v>Hue</v>
       </c>
       <c r="B284" t="str">
-        <v>분석</v>
+        <v>색상</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Full tone</v>
       </c>
       <c r="B285" t="str">
-        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
+        <v>솔리드</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Plot</v>
+        <v>Max C*</v>
       </c>
       <c r="B286" t="str">
-        <v>플롯</v>
+        <v>최대 C*</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Raw Output</v>
+        <v>At ink</v>
       </c>
       <c r="B287" t="str">
-        <v>원시 출력</v>
+        <v>해당 잉킹</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>XML</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B288" t="str">
-        <v>XML</v>
+        <v>최대 크로마가 솔리드보다 먼저 도달합니다 — 이 지점을 넘어선 잉크는 어둡게만 만듭니다.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>JSON</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B289" t="str">
-        <v>JSON</v>
+        <v>섀도 영역의 잉크 사용량</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Curves</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B290" t="str">
-        <v>곡선</v>
+        <v>의도적으로 어둡게 고정한 하나의 명도에서 a*b* 평면을 가로지르는 네 개의 직선 경로를 선택한 B2A 테이블에 통과시킵니다. 모든 샘플이 같은 L*를 공유하므로 어떤 색료에 나타나는 급격한 단차나 반전은 오직 색상과 크로마 처리에서 비롯됩니다 — 섀도 영역 색역 매핑 아티팩트의 특징입니다.</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Input curves</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B291" t="str">
-        <v>입력 곡선</v>
+        <v>섀도 영역의 잉크 사용량은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Output curves</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B292" t="str">
-        <v>출력 곡선</v>
+        <v>L* 고정 평면</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>CLUT image</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B293" t="str">
-        <v>CLUT 이미지</v>
+        <v>흑색점 보정 기준</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Gamut image</v>
+        <v>Position along path</v>
       </c>
       <c r="B294" t="str">
-        <v>색역 이미지</v>
+        <v>경로상 위치</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Chromaticity</v>
+        <v>Path</v>
       </c>
       <c r="B295" t="str">
-        <v>색도</v>
+        <v>경로</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Scatter plot</v>
+        <v>Cyan</v>
       </c>
       <c r="B296" t="str">
-        <v>산점도</v>
+        <v>시안</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Tone response curve</v>
+        <v>Magenta</v>
       </c>
       <c r="B297" t="str">
-        <v>톤 응답 곡선</v>
+        <v>마젠타</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Curve table</v>
+        <v>Yellow</v>
       </c>
       <c r="B298" t="str">
-        <v>곡선 표</v>
+        <v>옐로</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tables</v>
+        <v>Red</v>
       </c>
       <c r="B299" t="str">
-        <v>표</v>
+        <v>레드</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Data</v>
+        <v>Green</v>
       </c>
       <c r="B300" t="str">
-        <v>데이터</v>
+        <v>그린</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Evaluate</v>
+        <v>Blue</v>
       </c>
       <c r="B301" t="str">
-        <v>평가</v>
+        <v>블루</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Loading…</v>
+        <v>Black</v>
       </c>
       <c r="B302" t="str">
-        <v>불러오는 중…</v>
+        <v>블랙</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Input</v>
+        <v>Perceptual</v>
       </c>
       <c r="B303" t="str">
-        <v>입력</v>
+        <v>지각적</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B304" t="str">
-        <v>출력</v>
+        <v>상대 색도</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Floating point</v>
+        <v>Saturation</v>
       </c>
       <c r="B305" t="str">
-        <v>부동 소수점</v>
+        <v>채도</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Grid point</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B306" t="str">
-        <v>격자점</v>
+        <v>절대 색도</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Normalized</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B307" t="str">
-        <v>정규화</v>
+        <v>프로파일 통계</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Human</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B308" t="str">
-        <v>사람용</v>
+        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Device → PCS</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B309" t="str">
-        <v>장치 → PCS</v>
+        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>PCS → Device</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B310" t="str">
-        <v>PCS → 장치</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B311" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>색역 부피 (ΔE³)</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B312" t="str">
-        <v>불러오는 중…</v>
+        <v>왕복 ΔE</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B313" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Invalid profile URL:</v>
+        <v>mean</v>
       </c>
       <c r="B314" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>평균</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>P90</v>
       </c>
       <c r="B315" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>max</v>
       </c>
       <c r="B316" t="str">
-        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
+        <v>최대</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Analysing…</v>
       </c>
       <c r="B317" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>분석 중…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Analysis</v>
       </c>
       <c r="B318" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B319" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Security</v>
+        <v>Plot</v>
       </c>
       <c r="B320" t="str">
-        <v>보안</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Conformance</v>
+        <v>Raw Output</v>
       </c>
       <c r="B321" t="str">
-        <v>적합성</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Quality</v>
+        <v>XML</v>
       </c>
       <c r="B322" t="str">
-        <v>품질</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>REPORT</v>
+        <v>JSON</v>
       </c>
       <c r="B323" t="str">
-        <v>보고서</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>FAIL</v>
+        <v>Curves</v>
       </c>
       <c r="B324" t="str">
-        <v>실패</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>checks</v>
+        <v>Input curves</v>
       </c>
       <c r="B325" t="str">
-        <v>개 검사</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Output curves</v>
       </c>
       <c r="B326" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>CLUT image</v>
       </c>
       <c r="B327" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Gamut image</v>
       </c>
       <c r="B328" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Powered by {lib}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B329" t="str">
-        <v>{lib} 기반</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Subscribe</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B330" t="str">
-        <v>구독</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B331" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Get notified about new releases</v>
+        <v>Curve table</v>
       </c>
       <c r="B332" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Close</v>
+        <v>Tables</v>
       </c>
       <c r="B333" t="str">
-        <v>닫기</v>
+        <v>표</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Data</v>
       </c>
       <c r="B334" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Email address</v>
+        <v>Evaluate</v>
       </c>
       <c r="B335" t="str">
-        <v>이메일 주소</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>you@example.com</v>
+        <v>Loading…</v>
       </c>
       <c r="B336" t="str">
-        <v>you@example.com</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Input</v>
       </c>
       <c r="B337" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>(optional)</v>
+        <v>Output</v>
       </c>
       <c r="B338" t="str">
-        <v>(선택)</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Floating point</v>
       </c>
       <c r="B339" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Grid point</v>
       </c>
       <c r="B340" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Cancel</v>
+        <v>Normalized</v>
       </c>
       <c r="B341" t="str">
-        <v>취소</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Subscribe</v>
+        <v>Human</v>
       </c>
       <c r="B342" t="str">
-        <v>구독</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B343" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B344" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Close</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B345" t="str">
-        <v>닫기</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Privacy notice</v>
+        <v>Loading…</v>
       </c>
       <c r="B346" t="str">
-        <v>개인정보 처리방침</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B347" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B348" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B349" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B350" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B351" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Error:</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B352" t="str">
-        <v>오류:</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to XML</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B353" t="str">
-        <v>XML로 변환</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to JSON</v>
+        <v>Security</v>
       </c>
       <c r="B354" t="str">
-        <v>JSON으로 변환</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to ICC</v>
+        <v>Conformance</v>
       </c>
       <c r="B355" t="str">
-        <v>ICC로 변환</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to XML…</v>
+        <v>Quality</v>
       </c>
       <c r="B356" t="str">
-        <v>XML로 변환 중…</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to JSON…</v>
+        <v>REPORT</v>
       </c>
       <c r="B357" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to ICC…</v>
+        <v>FAIL</v>
       </c>
       <c r="B358" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Load ICC profile</v>
+        <v>checks</v>
       </c>
       <c r="B359" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B360" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Profile ID</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B361" t="str">
-        <v>프로파일 ID</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B362" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Tag Name</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B363" t="str">
-        <v>태그 이름</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>ID</v>
+        <v>Subscribe</v>
       </c>
       <c r="B364" t="str">
-        <v>ID</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Offset</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B365" t="str">
-        <v>오프셋</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Size</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B366" t="str">
-        <v>크기</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Pad</v>
+        <v>Close</v>
       </c>
       <c r="B367" t="str">
-        <v>패딩</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Bytes changed since load</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B368" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Type</v>
+        <v>Email address</v>
       </c>
       <c r="B369" t="str">
-        <v>유형</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Array of {type}</v>
+        <v>you@example.com</v>
       </c>
       <c r="B370" t="str">
-        <v>{type} 배열</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>(No content)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B371" t="str">
-        <v>(내용 없음)</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>bytes</v>
+        <v>(optional)</v>
       </c>
       <c r="B372" t="str">
-        <v>바이트</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Loading full description…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B373" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Could not load full description:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B374" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Cancel</v>
       </c>
       <c r="B375" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B376" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>No validation output</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B377" t="str">
-        <v>검증 출력 없음</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile is valid</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B378" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Close</v>
       </c>
       <c r="B379" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B380" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Critical validation error</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B381" t="str">
-        <v>심각한 검증 오류</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Unknown validation status</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B382" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B383" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B384" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Valid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B385" t="str">
-        <v>유효</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Warning</v>
+        <v>Error:</v>
       </c>
       <c r="B386" t="str">
-        <v>경고</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Error</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B387" t="str">
-        <v>오류</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Unknown</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B388" t="str">
-        <v>알 수 없음</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Pass</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B389" t="str">
-        <v>통과</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Fail</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B390" t="str">
-        <v>실패</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>View in context</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B391" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Validation detail</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B392" t="str">
-        <v>검증 세부 정보</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Triggered by</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B393" t="str">
-        <v>트리거 항목</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Field</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B394" t="str">
-        <v>항목</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Current value</v>
+        <v>Profile ID</v>
       </c>
       <c r="B395" t="str">
-        <v>현재 값</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Required: 0</v>
+        <v>No tags found.</v>
       </c>
       <c r="B396" t="str">
-        <v>필수: 0</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Expected: {value}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B397" t="str">
-        <v>예상: {value}</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Invalid</v>
+        <v>ID</v>
       </c>
       <c r="B398" t="str">
-        <v>잘못됨</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Offset</v>
       </c>
       <c r="B399" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Size</v>
       </c>
       <c r="B400" t="str">
-        <v>닫기</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pad</v>
       </c>
       <c r="B401" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B402" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Type</v>
       </c>
       <c r="B403" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B404" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved XML edits</v>
+        <v>(No content)</v>
       </c>
       <c r="B405" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>bytes</v>
       </c>
       <c r="B406" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B407" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B408" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>indent</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B409" t="str">
-        <v>들여쓰기</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>sort keys</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B410" t="str">
-        <v>키 정렬</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B411" t="str">
+        <v>검증 출력 없음</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B412" t="str">
+        <v>프로파일이 유효합니다</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B413" t="str">
+        <v>프로파일에 경고가 있습니다</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B414" t="str">
+        <v>프로파일이 규격을 준수하지 않습니다</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B415" t="str">
+        <v>심각한 검증 오류</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B416" t="str">
+        <v>알 수 없는 검증 상태</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B417" t="str">
+        <v>심각 — 검사용으로만 표시</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B418" t="str">
+        <v>경고나 오류를 찾지 못했습니다.</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B419" t="str">
+        <v>유효</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B420" t="str">
+        <v>경고</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B421" t="str">
+        <v>오류</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B422" t="str">
+        <v>알 수 없음</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B423" t="str">
+        <v>통과</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B424" t="str">
+        <v>실패</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B425" t="str">
+        <v>컨텍스트에서 보기</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B426" t="str">
+        <v>검증 세부 정보</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B427" t="str">
+        <v>트리거 항목</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B428" t="str">
+        <v>항목</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B429" t="str">
+        <v>현재 값</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B430" t="str">
+        <v>필수: 0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B431" t="str">
+        <v>예상: {value}</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B432" t="str">
+        <v>잘못됨</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B433" t="str">
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B434" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B435" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B436" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B437" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B438" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B439" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B440" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B441" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B442" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B443" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B444" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B411" t="str">
+      <c r="B445" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B411"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B445"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B445"/>
+  <dimension ref="A1:B449"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -533,3445 +533,3477 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Specified gamut</v>
+        <v>Round-trip ΔE by lightness</v>
       </c>
       <c r="B17" t="str">
-        <v>지정된 색역</v>
+        <v>명도별 왕복 ΔE</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (lightness of the requested colour)</v>
       </c>
       <c r="B18" t="str">
-        <v>지각 참조 매체 색역</v>
+        <v>L*(요청한 색상의 명도)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not specified</v>
+        <v>ΔE*ab</v>
       </c>
       <c r="B19" t="str">
-        <v>지정 안 됨</v>
+        <v>ΔE*ab</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Not evaluated</v>
+        <v>points, gamut boundary → neutral</v>
       </c>
       <c r="B20" t="str">
-        <v>평가 안 됨</v>
+        <v>개 지점, 색역 경계 → 중립</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PRMG interoperability</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B21" t="str">
-        <v>PRMG 상호 운용성</v>
+        <v>지정된 색역</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B22" t="str">
-        <v>왕복 ΔE</v>
+        <v>지각 참조 매체 색역</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Count</v>
+        <v>Not specified</v>
       </c>
       <c r="B23" t="str">
-        <v>개수</v>
+        <v>지정 안 됨</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Share</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B24" t="str">
-        <v>비율</v>
+        <v>평가 안 됨</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Total</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B25" t="str">
-        <v>합계</v>
+        <v>PRMG 상호 운용성</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B26" t="str">
-        <v>PRMG 평가 안 됨</v>
+        <v>왕복 ΔE</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>Count</v>
       </c>
       <c r="B27" t="str">
-        <v>하나의 렌더링 의도에 대한 전체 프로파일 지표: 장치→PCS 변환이 둘러싸는 색역 부피 (ΔE*ab³)와 왕복 정확도 지표입니다. 렌더링 의도와 왕복 유형을 선택하면 표와 히스토그램이 그에 맞게 업데이트됩니다.</v>
+        <v>개수</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Round-trip type</v>
+        <v>Share</v>
       </c>
       <c r="B28" t="str">
-        <v>왕복 유형</v>
+        <v>비율</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Total</v>
       </c>
       <c r="B29" t="str">
-        <v>이 왕복 유형에는 영향을 주지 않습니다</v>
+        <v>합계</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B30" t="str">
-        <v>이 왕복 유형은 이 프로파일에서 사용할 수 없습니다.</v>
+        <v>PRMG 평가 안 됨</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B31" t="str">
-        <v>왕복 ΔE 분포</v>
+        <v>하나의 렌더링 의도에 대한 전체 프로파일 지표: 장치→PCS 변환이 둘러싸는 색역 부피 (ΔE*ab³)와 왕복 정확도 지표입니다. 렌더링 의도와 왕복 유형을 선택하면 표와 히스토그램이 그에 맞게 업데이트됩니다.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B32" t="str">
-        <v>평가 영역 안에 들어온 왕복 샘플이 없습니다.</v>
+        <v>왕복 유형</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Std Dev</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B33" t="str">
-        <v>표준편차</v>
+        <v>이 왕복 유형에는 영향을 주지 않습니다</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Relative frequency</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B34" t="str">
-        <v>상대 빈도</v>
+        <v>이 왕복 유형은 이 프로파일에서 사용할 수 없습니다.</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Cumulative frequency</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B35" t="str">
-        <v>누적 빈도</v>
+        <v>왕복 ΔE 분포</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Horizontal scale</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B36" t="str">
-        <v>가로 배율</v>
+        <v>평가 영역 안에 들어온 왕복 샘플이 없습니다.</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Integer ΔE</v>
+        <v>Std Dev</v>
       </c>
       <c r="B37" t="str">
-        <v>정수 ΔE</v>
+        <v>표준편차</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Auto-scale</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B38" t="str">
-        <v>자동 배율</v>
+        <v>상대 빈도</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bins</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B39" t="str">
-        <v>구간</v>
+        <v>누적 빈도</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>CLUT Image</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B40" t="str">
-        <v>CLUT 이미지</v>
+        <v>가로 배율</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B41" t="str">
-        <v>장치↔PCS 변환의 색상 조회 테이블(CLUT)을 하나의 이미지로 타일 형태로 배열한 것입니다. 볼 렌더링 의도 테이블을 선택하세요.</v>
+        <v>정수 ΔE</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B42" t="str">
-        <v>이 프로파일에는 시각화할 CLUT 기반 장치↔PCS 테이블이 없습니다.</v>
+        <v>자동 배율</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Gamut Image</v>
+        <v>Bins</v>
       </c>
       <c r="B43" t="str">
-        <v>색역 이미지</v>
+        <v>구간</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B44" t="str">
-        <v>색역 태그의 색역 내/외 맵: PCS 색상이 재현 가능한 곳은 중립, 장치 색역을 벗어나는 곳은 빨강으로 표시됩니다.</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B45" t="str">
-        <v>이 프로파일에는 시각화할 색역 태그가 없습니다.</v>
+        <v>장치↔PCS 변환의 색상 조회 테이블(CLUT)을 하나의 이미지로 타일 형태로 배열한 것입니다. 볼 렌더링 의도 테이블을 선택하세요.</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B46" t="str">
-        <v>세로 배율</v>
+        <v>이 프로파일에는 시각화할 CLUT 기반 장치↔PCS 테이블이 없습니다.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>X–Y</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B47" t="str">
-        <v>X–Y</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B48" t="str">
-        <v>톤 증가</v>
+        <v>색역 태그의 색역 내/외 맵: PCS 색상이 재현 가능한 곳은 중립, 장치 색역을 벗어나는 곳은 빨강으로 표시됩니다.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B49" t="str">
-        <v>톤 증가(출력 − 입력)</v>
+        <v>이 프로파일에는 시각화할 색역 태그가 없습니다.</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Show full dump</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B50" t="str">
-        <v>전체 덤프 표시</v>
+        <v>세로 배율</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Output truncated for performance.</v>
+        <v>X–Y</v>
       </c>
       <c r="B51" t="str">
-        <v>성능을 위해 출력이 잘렸습니다.</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B52" t="str">
-        <v>색역 내 개요 (RT0)</v>
+        <v>톤 증가</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B53" t="str">
-        <v>역변환 + 색역 (RT1)</v>
+        <v>톤 증가(출력 − 입력)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Show full dump</v>
       </c>
       <c r="B54" t="str">
-        <v>재현성 (RT2)</v>
+        <v>전체 덤프 표시</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PRMG interoperability</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B55" t="str">
-        <v>PRMG 상호운용성</v>
+        <v>성능을 위해 출력이 잘렸습니다.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B56" t="str">
-        <v>iccviz 개요: 장치 값 격자를 PCS로, 다시 장치로, 그리고 다시 PCS로 변환하여 두 PCS 결과 사이의 ΔE*ab를 측정합니다. 색역 내 안정성을 빠르게 확인합니다.</v>
+        <v>색역 내 개요 (RT0)</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip 왕복 1: 각 장치 색상의 PCS와 Lab → 장치 → Lab 왕복을 한 번 거친 후의 PCS 사이의 ΔE*ab. 역변환 정확도와 색역 매핑을 반영합니다.</v>
+        <v>역변환 + 색역 (RT1)</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip 왕복 2: 첫 번째와 두 번째 왕복 사이의 ΔE*ab — 반복되는 PCS 왕복이 얼마나 안정적인지(재현성, 첫 왕복의 색역 클리핑과 무관)를 나타냅니다.</v>
+        <v>재현성 (RT2)</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B59" t="str">
-        <v>iccRoundTrip PRMG: Perceptual Reference Medium Gamut 내의 PCS 색상을 한 번 왕복(Lab → 장치 → Lab)합니다. ΔE*ab 분포는 프로파일 간 상호운용성을 나타냅니다.</v>
+        <v>PRMG 상호운용성</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Settings</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B60" t="str">
-        <v>설정</v>
+        <v>iccviz 개요: 장치 값 격자를 PCS로, 다시 장치로, 그리고 다시 PCS로 변환하여 두 PCS 결과 사이의 ΔE*ab를 측정합니다. 색역 내 안정성을 빠르게 확인합니다.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Display</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B61" t="str">
-        <v>표시</v>
+        <v>iccRoundTrip 왕복 1: 각 장치 색상의 PCS와 Lab → 장치 → Lab 왕복을 한 번 거친 후의 PCS 사이의 ΔE*ab. 역변환 정확도와 색역 매핑을 반영합니다.</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Background</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B62" t="str">
-        <v>배경</v>
+        <v>iccRoundTrip 왕복 2: 첫 번째와 두 번째 왕복 사이의 ΔE*ab — 반복되는 PCS 왕복이 얼마나 안정적인지(재현성, 첫 왕복의 색역 클리핑과 무관)를 나타냅니다.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Language</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B63" t="str">
-        <v>언어</v>
+        <v>iccRoundTrip PRMG: Perceptual Reference Medium Gamut 내의 PCS 색상을 한 번 왕복(Lab → 장치 → Lab)합니다. ΔE*ab 분포는 프로파일 간 상호운용성을 나타냅니다.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>System</v>
+        <v>Settings</v>
       </c>
       <c r="B64" t="str">
-        <v>시스템</v>
+        <v>설정</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Light</v>
+        <v>Display</v>
       </c>
       <c r="B65" t="str">
-        <v>밝게</v>
+        <v>표시</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Dark</v>
+        <v>Background</v>
       </c>
       <c r="B66" t="str">
-        <v>어둡게</v>
+        <v>배경</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>System default</v>
+        <v>Language</v>
       </c>
       <c r="B67" t="str">
-        <v>시스템 기본값</v>
+        <v>언어</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Number format</v>
+        <v>System</v>
       </c>
       <c r="B68" t="str">
-        <v>숫자 형식</v>
+        <v>시스템</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Hexadecimal</v>
+        <v>Light</v>
       </c>
       <c r="B69" t="str">
-        <v>16진수</v>
+        <v>밝게</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Decimal</v>
+        <v>Dark</v>
       </c>
       <c r="B70" t="str">
-        <v>10진수</v>
+        <v>어둡게</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Help</v>
+        <v>System default</v>
       </c>
       <c r="B71" t="str">
-        <v>도움말</v>
+        <v>시스템 기본값</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Contact</v>
+        <v>Number format</v>
       </c>
       <c r="B72" t="str">
-        <v>문의</v>
+        <v>숫자 형식</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>User guide</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B73" t="str">
-        <v>사용자 가이드</v>
+        <v>16진수</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search guide</v>
+        <v>Decimal</v>
       </c>
       <c r="B74" t="str">
-        <v>가이드 검색</v>
+        <v>10진수</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Search the user guide</v>
+        <v>Help</v>
       </c>
       <c r="B75" t="str">
-        <v>사용자 가이드 검색</v>
+        <v>도움말</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Previous match</v>
+        <v>Contact</v>
       </c>
       <c r="B76" t="str">
-        <v>이전 검색 결과</v>
+        <v>문의</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Next match</v>
+        <v>User guide</v>
       </c>
       <c r="B77" t="str">
-        <v>다음 검색 결과</v>
+        <v>사용자 가이드</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Close user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B78" t="str">
-        <v>사용자 가이드 닫기</v>
+        <v>가이드 검색</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B79" t="str">
-        <v>불러오는 중…</v>
+        <v>사용자 가이드 검색</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Previous match</v>
       </c>
       <c r="B80" t="str">
-        <v>사용자 가이드를 불러올 수 없습니다.</v>
+        <v>이전 검색 결과</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>None</v>
+        <v>Next match</v>
       </c>
       <c r="B81" t="str">
-        <v>없음</v>
+        <v>다음 검색 결과</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Close user guide</v>
       </c>
       <c r="B82" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>사용자 가이드 닫기</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Based on</v>
+        <v>Loading…</v>
       </c>
       <c r="B83" t="str">
-        <v/>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B84" t="str">
-        <v>데모 구현 기반</v>
+        <v>사용자 가이드를 불러올 수 없습니다.</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Validating…</v>
+        <v>None</v>
       </c>
       <c r="B85" t="str">
-        <v>검증 중…</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Save ICC profile</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B86" t="str">
-        <v>ICC 프로파일 저장</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Based on</v>
       </c>
       <c r="B87" t="str">
-        <v>● 변경됨 — 저장되지 않음</v>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Profiles</v>
+        <v>demo implementation</v>
       </c>
       <c r="B88" t="str">
-        <v>프로파일</v>
+        <v>데모 구현 기반</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Show profile pool</v>
+        <v>Validating…</v>
       </c>
       <c r="B89" t="str">
-        <v>프로파일 풀 표시</v>
+        <v>검증 중…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Collapse</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B90" t="str">
-        <v>접기</v>
+        <v>ICC 프로파일 저장</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Load Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B91" t="str">
-        <v>프로파일 불러오기</v>
+        <v>● 변경됨 — 저장되지 않음</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Remove</v>
+        <v>Profiles</v>
       </c>
       <c r="B92" t="str">
-        <v>제거</v>
+        <v>프로파일</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B93" t="str">
-        <v>여기에 ICC 프로파일을 놓으세요</v>
+        <v>프로파일 풀 표시</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Collapse</v>
       </c>
       <c r="B94" t="str">
-        <v>또는 이미지(TIFF/PNG/JPEG)를 놓아 내장된 프로파일을 추출하세요 — 파일은 사용자 장치에 그대로 남습니다.</v>
+        <v>접기</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>New from .cube</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B95" t="str">
-        <v>.cube에서 새로 만들기</v>
+        <v>프로파일 불러오기</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Sort by name</v>
+        <v>Remove</v>
       </c>
       <c r="B96" t="str">
-        <v>이름순 정렬</v>
+        <v>제거</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>A–Z</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B97" t="str">
-        <v>A–Z</v>
+        <v>여기에 ICC 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>New profile from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B98" t="str">
-        <v>.cube에서 새 프로파일</v>
+        <v>또는 이미지(TIFF/PNG/JPEG)를 놓아 내장된 프로파일을 추출하세요 — 파일은 사용자 장치에 그대로 남습니다.</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New from .cube</v>
       </c>
       <c r="B99" t="str">
-        <v>Adobe/Resolve의 .cube 3D LUT에서 ICC DeviceLink를 만듭니다. 결과는 풀에 추가되고 다운로드됩니다.</v>
+        <v>.cube에서 새로 만들기</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Choose .cube file</v>
+        <v>Sort by name</v>
       </c>
       <c r="B100" t="str">
-        <v>.cube 파일 선택</v>
+        <v>이름순 정렬</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>A–Z</v>
+      </c>
+      <c r="B101" t="str">
+        <v>A–Z</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>New profile from .cube</v>
+      </c>
+      <c r="B102" t="str">
+        <v>.cube에서 새 프로파일</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Adobe/Resolve의 .cube 3D LUT에서 ICC DeviceLink를 만듭니다. 결과는 풀에 추가되고 다운로드됩니다.</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B104" t="str">
+        <v>.cube 파일 선택</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B101" t="str">
+      <c r="B105" t="str">
         <v>또는 여기에 놓거나 아래에 붙여넣으세요</v>
       </c>
     </row>
-    <row r="102" xml:space="preserve">
-      <c r="A102" t="str" xml:space="preserve">
+    <row r="106" xml:space="preserve">
+      <c r="A106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B102" t="str" xml:space="preserve">
+      <c r="B106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B103" t="str">
-        <v>취소</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Create DeviceLink</v>
-      </c>
-      <c r="B104" t="str">
-        <v>DeviceLink 만들기</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Creating…</v>
-      </c>
-      <c r="B105" t="str">
-        <v>만드는 중…</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Could not read that file.</v>
-      </c>
-      <c r="B106" t="str">
-        <v>해당 파일을 읽을 수 없습니다.</v>
-      </c>
-    </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Profile</v>
+        <v>Cancel</v>
       </c>
       <c r="B107" t="str">
-        <v>프로파일</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Compare</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B108" t="str">
-        <v>비교</v>
+        <v>DeviceLink 만들기</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Combine</v>
+        <v>Creating…</v>
       </c>
       <c r="B109" t="str">
-        <v>링크</v>
+        <v>만드는 중…</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Spectral</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B110" t="str">
-        <v>스펙트럴</v>
+        <v>해당 파일을 읽을 수 없습니다.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Profile</v>
       </c>
       <c r="B111" t="str">
-        <v>풀에서 이 탭으로 프로파일을 끌어다 놓으세요</v>
+        <v>프로파일</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Remove</v>
+        <v>Compare</v>
       </c>
       <c r="B112" t="str">
-        <v>제거</v>
+        <v>비교</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>No profile selected</v>
+        <v>Combine</v>
       </c>
       <c r="B113" t="str">
-        <v>선택된 프로파일 없음</v>
+        <v>링크</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Spectral</v>
       </c>
       <c r="B114" t="str">
-        <v>풀에서 프로파일을 '프로파일' 탭으로 끌어다 놓아 검사하세요.</v>
+        <v>스펙트럴</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B115" t="str">
-        <v>아직 비교할 항목이 없습니다</v>
+        <v>풀에서 이 탭으로 프로파일을 끌어다 놓으세요</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Remove</v>
       </c>
       <c r="B116" t="str">
-        <v>하나 이상의 프로파일을 '비교' 탭으로 끌어다 놓으세요.</v>
+        <v>제거</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Gamut comparison</v>
+        <v>No profile selected</v>
       </c>
       <c r="B117" t="str">
-        <v>색역 비교</v>
+        <v>선택된 프로파일 없음</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B118" t="str">
-        <v>3D 색역 및 2D 슬라이스 보기가 여기에 추가됩니다. 누적:</v>
+        <v>풀에서 프로파일을 '프로파일' 탭으로 끌어다 놓아 검사하세요.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Rendering intent</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B119" t="str">
-        <v>렌더링 의도</v>
+        <v>아직 비교할 항목이 없습니다</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Shell</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B120" t="str">
-        <v>셸</v>
+        <v>하나 이상의 프로파일을 '비교' 탭으로 끌어다 놓으세요.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Wireframe</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B121" t="str">
-        <v>와이어프레임</v>
+        <v>색역 비교</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Axis numbers</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B122" t="str">
-        <v>축 번호</v>
+        <v>3D 색역 및 2D 슬라이스 보기가 여기에 추가됩니다. 누적:</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B123" t="str">
-        <v>불투명도</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Shell</v>
       </c>
       <c r="B124" t="str">
-        <v>색상</v>
+        <v>셸</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Wireframe</v>
       </c>
       <c r="B125" t="str">
-        <v>단색</v>
+        <v>와이어프레임</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B126" t="str">
-        <v>값 기준</v>
+        <v>축 번호</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Opacity</v>
       </c>
       <c r="B127" t="str">
-        <v>색상(Hue) 기준</v>
+        <v>불투명도</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>Colour</v>
       </c>
       <c r="B128" t="str">
-        <v>회전</v>
+        <v>색상</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>Solid</v>
       </c>
       <c r="B129" t="str">
-        <v>턴테이블</v>
+        <v>단색</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>By value</v>
       </c>
       <c r="B130" t="str">
-        <v>궤도</v>
+        <v>값 기준</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>By hue</v>
       </c>
       <c r="B131" t="str">
-        <v>드래그 속도</v>
+        <v>색상(Hue) 기준</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Rotation</v>
       </c>
       <c r="B132" t="str">
-        <v>롤</v>
+        <v>회전</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B133" t="str">
-        <v>롤 속도</v>
+        <v>턴테이블</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Orbit</v>
       </c>
       <c r="B134" t="str">
-        <v>색역 생성 중…</v>
+        <v>궤도</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Drag speed</v>
       </c>
       <c r="B135" t="str">
-        <v>색역 없음</v>
+        <v>드래그 속도</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Roll</v>
       </c>
       <c r="B136" t="str">
-        <v>표시/숨기기</v>
+        <v>롤</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>Roll speed</v>
       </c>
       <c r="B137" t="str">
-        <v>3D 색역 셸</v>
+        <v>롤 속도</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B138" t="str">
-        <v>2D 색역 슬라이스</v>
+        <v>색역 생성 중…</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>no gamut</v>
       </c>
       <c r="B139" t="str">
-        <v>평면</v>
+        <v>색역 없음</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>Show / hide</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>표시/숨기기</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>3D 색역 셸</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>2D 색역 슬라이스</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>Plane</v>
       </c>
       <c r="B143" t="str">
-        <v>선택한 프로파일 중 색역을 도출할 장치→PCS 변환을 가진 것이 없습니다.</v>
+        <v>평면</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>L*</v>
       </c>
       <c r="B144" t="str">
-        <v>링크</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>a*</v>
       </c>
       <c r="B145" t="str">
-        <v>DeviceLink 생성과 다중 프로파일 변환은 이후 단계에서 제공됩니다.</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>b*</v>
       </c>
       <c r="B146" t="str">
-        <v>더 많은 링크 메이커(DeviceLink, …)가 여기에 추가됩니다.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Observer Change</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B147" t="str">
-        <v>V4 디스플레이 메이커</v>
+        <v>선택한 프로파일 중 색역을 도출할 장치→PCS 변환을 가진 것이 없습니다.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Linking</v>
       </c>
       <c r="B148" t="str">
-        <v>V5 RGB 디스플레이와 V5 관찰자 프로파일을 여기에 끌어다 놓아 V4 디스플레이 프로파일을 만드세요.</v>
+        <v>링크</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B149" t="str">
-        <v>V5 RGB 디스플레이</v>
+        <v>DeviceLink 생성과 다중 프로파일 변환은 이후 단계에서 제공됩니다.</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B150" t="str">
-        <v>디스플레이 프로파일을 놓으세요</v>
+        <v>더 많은 링크 메이커(DeviceLink, …)가 여기에 추가됩니다.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Observer Change</v>
       </c>
       <c r="B151" t="str">
-        <v>V5 관찰자 (PCC)</v>
+        <v>V4 디스플레이 메이커</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B152" t="str">
-        <v>관찰자 프로파일을 놓으세요</v>
+        <v>V5 RGB 디스플레이와 V5 관찰자 프로파일을 여기에 끌어다 놓아 V4 디스플레이 프로파일을 만드세요.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B153" t="str">
-        <v>V5 RGB 디스플레이도 관찰자도 아닌 프로파일은 무시되었습니다.</v>
+        <v>V5 RGB 디스플레이</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B154" t="str">
-        <v>V4 디스플레이 프로파일 만들기</v>
+        <v>디스플레이 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B155" t="str">
-        <v>프로파일 이름</v>
+        <v>V5 관찰자 (PCC)</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B156" t="str">
-        <v>만들기</v>
+        <v>관찰자 프로파일을 놓으세요</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B157" t="str">
-        <v>만드는 중…</v>
+        <v>V5 RGB 디스플레이도 관찰자도 아닌 프로파일은 무시되었습니다.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B158" t="str">
-        <v>'{name}'을(를) 만들었습니다 — 풀과 이 탭에 추가되었습니다.</v>
+        <v>V4 디스플레이 프로파일 만들기</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Link Pipeline</v>
+        <v>Profile name</v>
       </c>
       <c r="B159" t="str">
-        <v>링크 파이프라인</v>
+        <v>프로파일 이름</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Create</v>
       </c>
       <c r="B160" t="str">
-        <v>프로파일 체인을 구성한 다음 DeviceLink를 만들거나, 이미지를 변환하거나, 색상 데이터셋을 변환하세요.</v>
+        <v>만들기</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Done</v>
+        <v>Making…</v>
       </c>
       <c r="B161" t="str">
-        <v>완료</v>
+        <v>만드는 중…</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B162" t="str">
-        <v>변환할 이미지를 드롭하세요 (TIFF/PNG/JPEG)</v>
+        <v>'{name}'을(를) 만들었습니다 — 풀과 이 탭에 추가되었습니다.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Checking image…</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B163" t="str">
-        <v>이미지 확인 중…</v>
+        <v>링크 파이프라인</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B164" t="str">
-        <v>지원되지 않는 이미지입니다 (TIFF, PNG 또는 JPEG).</v>
+        <v>프로파일 체인을 구성한 다음 DeviceLink를 만들거나, 이미지를 변환하거나, 색상 데이터셋을 변환하세요.</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Done</v>
       </c>
       <c r="B165" t="str">
-        <v>이미지가 너무 큽니다 ({mp} MP, 제한 {max} MP).</v>
+        <v>완료</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transform Image</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B166" t="str">
-        <v>이미지 변환</v>
+        <v>변환할 이미지를 드롭하세요 (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Transforming…</v>
+        <v>Checking image…</v>
       </c>
       <c r="B167" t="str">
-        <v>변환 중…</v>
+        <v>이미지 확인 중…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B168" t="str">
-        <v>체인을 시작하려면 프로파일을 드롭하세요</v>
+        <v>지원되지 않는 이미지입니다 (TIFF, PNG 또는 JPEG).</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>removed</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B169" t="str">
-        <v>제거됨</v>
+        <v>이미지가 너무 큽니다 ({mp} MP, 제한 {max} MP).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move earlier</v>
+        <v>Transform Image</v>
       </c>
       <c r="B170" t="str">
-        <v>앞으로 이동</v>
+        <v>이미지 변환</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move later</v>
+        <v>Transforming…</v>
       </c>
       <c r="B171" t="str">
-        <v>뒤로 이동</v>
+        <v>변환 중…</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move up</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B172" t="str">
-        <v>위로 이동</v>
+        <v>체인을 시작하려면 프로파일을 드롭하세요</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move down</v>
+        <v>removed</v>
       </c>
       <c r="B173" t="str">
-        <v>아래로 이동</v>
+        <v>제거됨</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move earlier</v>
       </c>
       <c r="B174" t="str">
-        <v>렌더링 인텐트 (전체)</v>
+        <v>앞으로 이동</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Move later</v>
       </c>
       <c r="B175" t="str">
-        <v>이 변환의 렌더링 인텐트</v>
+        <v>뒤로 이동</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Move up</v>
       </c>
       <c r="B176" t="str">
-        <v>변환마다 렌더링 인텐트가 다릅니다</v>
+        <v>위로 이동</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Move down</v>
       </c>
       <c r="B177" t="str">
-        <v>체인 방향 전환 (첫 변환을 반전시키고 체인 전체에 반영됩니다)</v>
+        <v>아래로 이동</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B178" t="str">
-        <v>체인에 포함된 프로파일이 풀에서 제거되었습니다 — 계속하려면 제거하세요.</v>
+        <v>렌더링 인텐트 (전체)</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Chain</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B179" t="str">
-        <v>체인</v>
+        <v>이 변환의 렌더링 인텐트</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B180" t="str">
-        <v>체인을 분석할 수 없습니다.</v>
+        <v>변환마다 렌더링 인텐트가 다릅니다</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Checking chain…</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B181" t="str">
-        <v>체인 확인 중…</v>
+        <v>체인 방향 전환 (첫 변환을 반전시키고 체인 전체에 반영됩니다)</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B182" t="str">
-        <v>체인이 연결되지 않습니다 ({detail}).</v>
+        <v>체인에 포함된 프로파일이 풀에서 제거되었습니다 — 계속하려면 제거하세요.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Chain</v>
       </c>
       <c r="B183" t="str">
-        <v>프로파일 {n}이(가) 이전 단계와 연결되지 않습니다 ({detail}).</v>
+        <v>체인</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B184" t="str">
-        <v>이미지를 처리하기 전에 체인을 수정하세요</v>
+        <v>체인을 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Clear</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B185" t="str">
-        <v>지우기</v>
+        <v>체인 확인 중…</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Make DeviceLink</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B186" t="str">
-        <v>DeviceLink 만들기</v>
+        <v>체인이 연결되지 않습니다 ({detail}).</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>DeviceLink name</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>DeviceLink 이름</v>
+        <v>프로파일 {n}이(가) 이전 단계와 연결되지 않습니다 ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Making…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B188" t="str">
-        <v>생성 중…</v>
+        <v>이미지를 처리하기 전에 체인을 수정하세요</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Clear</v>
       </c>
       <c r="B189" t="str">
-        <v>"{name}" 생성됨 — 풀과 이 탭에 추가되었습니다.</v>
+        <v>지우기</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B190" t="str">
-        <v>{src} 이미지를 드롭하면 {dst}(으)로 변환됩니다 — 결과는 다운로드되며 저장되지 않습니다.</v>
+        <v>DeviceLink 만들기</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Build a chain to process images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B191" t="str">
-        <v>이미지를 처리하려면 체인을 구성하세요</v>
+        <v>DeviceLink 이름</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Making…</v>
       </c>
       <c r="B192" t="str">
-        <v>이 체인은 이미지 색공간에서 시작하고 끝나지 않습니다</v>
+        <v>생성 중…</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B193" t="str">
-        <v>변환된 이미지를 저장했습니다.</v>
+        <v>"{name}" 생성됨 — 풀과 이 탭에 추가되었습니다.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B194" t="str">
-        <v>색상 데이터셋을 드롭하세요 (CGATS/CSV/CxF/JSON)</v>
+        <v>{src} 이미지를 드롭하면 {dst}(으)로 변환됩니다 — 결과는 다운로드되며 저장되지 않습니다.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Could not read that file.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B195" t="str">
-        <v>해당 파일을 읽을 수 없습니다.</v>
+        <v>이미지를 처리하려면 체인을 구성하세요</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Data file too large.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B196" t="str">
-        <v>데이터 파일이 너무 큽니다.</v>
+        <v>이 체인은 이미지 색공간에서 시작하고 끝나지 않습니다</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transform Data</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B197" t="str">
-        <v>데이터 변환</v>
+        <v>변환된 이미지를 저장했습니다.</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Transforming…</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B198" t="str">
-        <v>변환 중…</v>
+        <v>색상 데이터셋을 드롭하세요 (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Prefer</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B199" t="str">
-        <v>선호</v>
+        <v>해당 파일을 읽을 수 없습니다.</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Observer</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B200" t="str">
-        <v>관측자</v>
+        <v>데이터 파일이 너무 큽니다.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Illuminant</v>
+        <v>Transform Data</v>
       </c>
       <c r="B201" t="str">
-        <v>광원</v>
+        <v>데이터 변환</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Condition</v>
+        <v>Transforming…</v>
       </c>
       <c r="B202" t="str">
-        <v>조건</v>
+        <v>변환 중…</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Prefer</v>
       </c>
       <c r="B203" t="str">
-        <v>중복 {n}건 필터링</v>
+        <v>선호</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>median</v>
+        <v>Observer</v>
       </c>
       <c r="B204" t="str">
-        <v>중앙값</v>
+        <v>관측자</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>mean</v>
+        <v>Illuminant</v>
       </c>
       <c r="B205" t="str">
-        <v>평균값</v>
+        <v>광원</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>patches</v>
+        <v>Condition</v>
       </c>
       <c r="B206" t="str">
-        <v>패치</v>
+        <v>조건</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>{n} duplicates</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B207" t="str">
-        <v>중복 {n}건</v>
+        <v>중복 {n}건 필터링</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Transform result</v>
+        <v>median</v>
       </c>
       <c r="B208" t="str">
-        <v>변환 결과</v>
+        <v>중앙값</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>mean</v>
       </c>
       <c r="B209" t="str">
-        <v>{src} → {dst} · 패치 {n}개</v>
+        <v>평균값</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>patches</v>
       </c>
       <c r="B210" t="str">
-        <v>전체 {total}건 중 처음 {shown}건 표시 중 — 저장하면 전체가 기록됩니다.</v>
+        <v>패치</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save as</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B211" t="str">
-        <v>다른 이름으로 저장</v>
+        <v>중복 {n}건</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Save</v>
+        <v>Transform result</v>
       </c>
       <c r="B212" t="str">
-        <v>저장</v>
+        <v>변환 결과</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Invert Transform</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B213" t="str">
-        <v>변환 반전</v>
+        <v>{src} → {dst} · 패치 {n}개</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Inverting…</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B214" t="str">
-        <v>반전 중…</v>
+        <v>전체 {total}건 중 처음 {shown}건 표시 중 — 저장하면 전체가 기록됩니다.</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert</v>
+        <v>Save as</v>
       </c>
       <c r="B215" t="str">
-        <v>반전</v>
+        <v>다른 이름으로 저장</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>last stage</v>
+        <v>Save</v>
       </c>
       <c r="B216" t="str">
-        <v>마지막 단계</v>
+        <v>저장</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>first stage</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B217" t="str">
-        <v>첫 단계</v>
+        <v>변환 반전</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>Inverting…</v>
       </c>
       <c r="B218" t="str">
-        <v>{in} 데이터 → {out} 검색</v>
+        <v>반전 중…</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Invert</v>
       </c>
       <c r="B219" t="str">
-        <v>반전에는 2–3개 프로파일로 이루어진 체인이 필요합니다</v>
+        <v>반전</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>last stage</v>
       </c>
       <c r="B220" t="str">
-        <v>데이터셋은 {in}이어야 합니다. 역검색은 {out}과 패치별 역변환 가능성 비용을 산출합니다.</v>
+        <v>마지막 단계</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>ΔE cost</v>
+        <v>first stage</v>
       </c>
       <c r="B221" t="str">
-        <v>ΔE 비용</v>
+        <v>첫 단계</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B222" t="str">
-        <v>이 이미지에는 내장된 ICC 프로파일이 있습니다.</v>
+        <v>{in} 데이터 → {out} 검색</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B223" t="str">
-        <v>추출 후 체인에 추가</v>
+        <v>반전에는 2–3개 프로파일로 이루어진 체인이 필요합니다</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Extracting…</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B224" t="str">
-        <v>추출 중…</v>
+        <v>데이터셋은 {in}이어야 합니다. 역검색은 {out}과 패치별 역변환 가능성 비용을 산출합니다.</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Dismiss</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B225" t="str">
-        <v>닫기</v>
+        <v>ΔE 비용</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B226" t="str">
-        <v>내장된 프로파일을 추출했습니다 — 풀에 추가되고 체인의 첫 번째 자리에 배치되었습니다.</v>
+        <v>이 이미지에는 내장된 ICC 프로파일이 있습니다.</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Image output options</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B227" t="str">
-        <v>이미지 출력 옵션</v>
+        <v>추출 후 체인에 추가</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Encoding</v>
+        <v>Extracting…</v>
       </c>
       <c r="B228" t="str">
-        <v>인코딩</v>
+        <v>추출 중…</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Same as source</v>
+        <v>Dismiss</v>
       </c>
       <c r="B229" t="str">
-        <v>원본과 동일</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>8-bit</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B230" t="str">
-        <v>8비트</v>
+        <v>내장된 프로파일을 추출했습니다 — 풀에 추가되고 체인의 첫 번째 자리에 배치되었습니다.</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>16-bit</v>
+        <v>Image output options</v>
       </c>
       <c r="B231" t="str">
-        <v>16비트</v>
+        <v>이미지 출력 옵션</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Float (32-bit)</v>
+        <v>Encoding</v>
       </c>
       <c r="B232" t="str">
-        <v>부동소수점 (32비트)</v>
+        <v>인코딩</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Compression</v>
+        <v>Same as source</v>
       </c>
       <c r="B233" t="str">
-        <v>압축</v>
+        <v>원본과 동일</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>None</v>
+        <v>8-bit</v>
       </c>
       <c r="B234" t="str">
-        <v>없음</v>
+        <v>8비트</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Planar</v>
+        <v>16-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>플레이너</v>
+        <v>16비트</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Composite</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B236" t="str">
-        <v>컴포지트</v>
+        <v>부동소수점 (32비트)</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Separated</v>
+        <v>Compression</v>
       </c>
       <c r="B237" t="str">
-        <v>분리</v>
+        <v>압축</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>CMM interpolation</v>
+        <v>None</v>
       </c>
       <c r="B238" t="str">
-        <v>CMM 보간</v>
+        <v>없음</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Tetrahedral</v>
+        <v>Planar</v>
       </c>
       <c r="B239" t="str">
-        <v>사면체</v>
+        <v>플레이너</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Linear</v>
+        <v>Composite</v>
       </c>
       <c r="B240" t="str">
-        <v>선형</v>
+        <v>컴포지트</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Embed ICC</v>
+        <v>Separated</v>
       </c>
       <c r="B241" t="str">
-        <v>ICC 포함</v>
+        <v>분리</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B242" t="str">
-        <v>인코딩, 압축, 플레이너 방식은 저장되는 TIFF에 반영됩니다. TIFF 전용 옵션(부동소수점, LZW/ZIP, 분리)을 설정하지 않으면 RGB/Gray 출력은 PNG로 유지됩니다.</v>
+        <v>CMM 보간</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B243" t="str">
-        <v>스펙트럴 TIFF 조합</v>
+        <v>사면체</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Linear</v>
       </c>
       <c r="B244" t="str">
-        <v>단일 채널 스펙트럴 이미지를 채널 순서대로 드롭하면 하나의 다중 채널 TIFF로 조합됩니다.</v>
+        <v>선형</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B245" t="str">
-        <v>스펙트럴 이미지를 여기에 드롭하세요 (또는 클릭하여 선택)</v>
+        <v>ICC 포함</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>ch</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B246" t="str">
-        <v>ch</v>
+        <v>인코딩, 압축, 플레이너 방식은 저장되는 TIFF에 반영됩니다. TIFF 전용 옵션(부동소수점, LZW/ZIP, 분리)을 설정하지 않으면 RGB/Gray 출력은 PNG로 유지됩니다.</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B247" t="str">
-        <v>조합 후 저장</v>
+        <v>스펙트럴 TIFF 조합</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembling…</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B248" t="str">
-        <v>조합 중…</v>
+        <v>단일 채널 스펙트럴 이미지를 채널 순서대로 드롭하면 하나의 다중 채널 TIFF로 조합됩니다.</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B249" t="str">
-        <v>{n}개 채널을 조합했습니다.</v>
+        <v>스펙트럴 이미지를 여기에 드롭하세요 (또는 클릭하여 선택)</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>ch</v>
       </c>
       <c r="B250" t="str">
-        <v>이미지로 인식되는 파일이 없습니다 (TIFF, PNG 또는 JPEG).</v>
+        <v>ch</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B251" t="str">
-        <v>취소</v>
+        <v>조합 후 저장</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Assembling…</v>
       </c>
       <c r="B252" t="str">
-        <v>{n}개 파일을 불러오지 못했습니다</v>
+        <v>조합 중…</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B253" t="str">
-        <v>이 파일들은 ICC 프로파일이 아니므로 풀에 추가되지 않았습니다:</v>
+        <v>{n}개 채널을 조합했습니다.</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>OK</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B254" t="str">
-        <v>확인</v>
+        <v>이미지로 인식되는 파일이 없습니다 (TIFF, PNG 또는 JPEG).</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Cancel</v>
       </c>
       <c r="B255" t="str">
-        <v>ICC 프로파일을 여기에 놓기</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>or</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B256" t="str">
-        <v>또는</v>
+        <v>{n}개 파일을 불러오지 못했습니다</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Choose file</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B257" t="str">
-        <v>파일 선택</v>
+        <v>이 파일들은 ICC 프로파일이 아니므로 풀에 추가되지 않았습니다:</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>.icc and .icm files</v>
+        <v>OK</v>
       </c>
       <c r="B258" t="str">
-        <v>.icc 및 .icm 파일</v>
+        <v>확인</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Header</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B259" t="str">
-        <v>헤더</v>
+        <v>ICC 프로파일을 여기에 놓기</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Tags</v>
+        <v>or</v>
       </c>
       <c r="B260" t="str">
-        <v>태그</v>
+        <v>또는</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Validation</v>
+        <v>Choose file</v>
       </c>
       <c r="B261" t="str">
-        <v>검증</v>
+        <v>파일 선택</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Analysis</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B262" t="str">
-        <v>분석</v>
+        <v>.icc 및 .icm 파일</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Header</v>
       </c>
       <c r="B263" t="str">
-        <v>중립축 잉킹</v>
+        <v>헤더</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Tags</v>
       </c>
       <c r="B264" t="str">
-        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
+        <v>태그</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Validation</v>
       </c>
       <c r="B265" t="str">
-        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>검증</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Analysis</v>
       </c>
       <c r="B266" t="str">
-        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Rendering intent</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B267" t="str">
-        <v>렌더링 의도</v>
+        <v>중립축 잉킹</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>% ink</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B268" t="str">
-        <v>% 잉크</v>
+        <v>명도가 흰색(L*=100)에서 검정(L*=0)으로 갈 때 중립축(a*=b*=0)을 따라 적용되는 장치 색료.</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>L* out (tone)</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B269" t="str">
-        <v>L* 출력(톤)</v>
+        <v>중립축 잉킹은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Δa*b*</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B270" t="str">
-        <v>Δa*b*</v>
+        <v>이 프로파일에는 샘플링할 B2A(PCS→장치) 테이블이 없습니다.</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B271" t="str">
-        <v>극값 측색</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>% ink</v>
       </c>
       <c r="B272" t="str">
-        <v>프로파일 재현 범위의 양 끝: 기재의 백색, 인쇄할 수 있는 가장 어두운 검정, 그 검정에 드는 잉크량, 그리고 각 색상이 가장 진해지는 지점.</v>
+        <v>% 잉크</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B273" t="str">
-        <v>백색점은 색료가 0일 때의 색 — 즉 아무것도 인쇄하지 않은 기재입니다. 흑색점은 PCS 검정(L*=0, a*=b*=0)을 선택한 B2A 테이블에 통과시켜 프로파일이 검정에 대해 선택하는 잉킹을 얻은 뒤, 그 잉킹을 A2B1로 되읽어 구합니다. 총 잉크량(TAC)은 그 잉킹의 합입니다. 절대 측색은 기재 자체의 색을 보여 주고, 상대 측색은 이를 완전한 백색 기준으로 다시 맞춥니다.</v>
+        <v>L* 출력(톤)</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Relative</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B274" t="str">
-        <v>상대</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Absolute</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B275" t="str">
-        <v>절대</v>
+        <v>극값 측색</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>White point</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B276" t="str">
-        <v>백색점</v>
+        <v>프로파일 재현 범위의 양 끝: 기재의 백색, 인쇄할 수 있는 가장 어두운 검정, 그 검정에 드는 잉크량, 그리고 각 색상이 가장 진해지는 지점.</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Black point</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B277" t="str">
-        <v>흑색점</v>
+        <v>백색점은 색료가 0일 때의 색 — 즉 아무것도 인쇄하지 않은 기재입니다. 흑색점은 PCS 검정(L*=0, a*=b*=0)을 선택한 B2A 테이블에 통과시켜 프로파일이 검정에 대해 선택하는 잉킹을 얻은 뒤, 그 잉킹을 A2B1로 되읽어 구합니다. 총 잉크량(TAC)은 그 잉킹의 합입니다. 절대 측색은 기재 자체의 색을 보여 주고, 상대 측색은 이를 완전한 백색 기준으로 다시 맞춥니다.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Inking at black point</v>
+        <v>Relative</v>
       </c>
       <c r="B278" t="str">
-        <v>흑색점에서의 잉킹</v>
+        <v>상대</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>TAC</v>
+        <v>Absolute</v>
       </c>
       <c r="B279" t="str">
-        <v>TAC</v>
+        <v>절대</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>White point</v>
       </c>
       <c r="B280" t="str">
-        <v>이 프로파일에는 매체 백색점 태그가 없으므로 절대 측색을 사용할 수 없습니다.</v>
+        <v>백색점</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>Black point</v>
       </c>
       <c r="B281" t="str">
-        <v>극값 측색은 출력(프린터) 프로파일에서만 사용할 수 있습니다 — 색료가 0이면 아무것도 인쇄하지 않은 기재라고 가정합니다.</v>
+        <v>흑색점</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B282" t="str">
-        <v>솔리드 대 최대 크로마</v>
+        <v>흑색점에서의 잉킹</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>TAC</v>
       </c>
       <c r="B283" t="str">
-        <v>각 잉크 꼭짓점의 위치와 거기에 이르는 도중 크로마가 가장 높은 지점입니다. A2B1을 통해 측정하므로 이 행들은 위의 렌더링 의도에 따라 바뀌지 않습니다. 정상적인 프로파일에서는 두 행이 일치합니다. 최대 크로마가 솔리드보다 먼저 도달하면 그 지점을 넘어선 잉크는 어둡게만 만듭니다.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Hue</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B284" t="str">
-        <v>색상</v>
+        <v>이 프로파일에는 매체 백색점 태그가 없으므로 절대 측색을 사용할 수 없습니다.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Full tone</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B285" t="str">
-        <v>솔리드</v>
+        <v>극값 측색은 출력(프린터) 프로파일에서만 사용할 수 있습니다 — 색료가 0이면 아무것도 인쇄하지 않은 기재라고 가정합니다.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Max C*</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B286" t="str">
-        <v>최대 C*</v>
+        <v>솔리드 대 최대 크로마</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>At ink</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B287" t="str">
-        <v>해당 잉킹</v>
+        <v>각 잉크 꼭짓점의 위치와 거기에 이르는 도중 크로마가 가장 높은 지점입니다. A2B1을 통해 측정하므로 이 행들은 위의 렌더링 의도에 따라 바뀌지 않습니다. 정상적인 프로파일에서는 두 행이 일치합니다. 최대 크로마가 솔리드보다 먼저 도달하면 그 지점을 넘어선 잉크는 어둡게만 만듭니다.</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>Hue</v>
       </c>
       <c r="B288" t="str">
-        <v>최대 크로마가 솔리드보다 먼저 도달합니다 — 이 지점을 넘어선 잉크는 어둡게만 만듭니다.</v>
+        <v>색상</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Full tone</v>
       </c>
       <c r="B289" t="str">
-        <v>섀도 영역의 잉크 사용량</v>
+        <v>솔리드</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Max C*</v>
       </c>
       <c r="B290" t="str">
-        <v>의도적으로 어둡게 고정한 하나의 명도에서 a*b* 평면을 가로지르는 네 개의 직선 경로를 선택한 B2A 테이블에 통과시킵니다. 모든 샘플이 같은 L*를 공유하므로 어떤 색료에 나타나는 급격한 단차나 반전은 오직 색상과 크로마 처리에서 비롯됩니다 — 섀도 영역 색역 매핑 아티팩트의 특징입니다.</v>
+        <v>최대 C*</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>At ink</v>
       </c>
       <c r="B291" t="str">
-        <v>섀도 영역의 잉크 사용량은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
+        <v>해당 잉킹</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Constant L* plane</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B292" t="str">
-        <v>L* 고정 평면</v>
+        <v>최대 크로마가 솔리드보다 먼저 도달합니다 — 이 지점을 넘어선 잉크는 어둡게만 만듭니다.</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>black-point compensated from</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B293" t="str">
-        <v>흑색점 보정 기준</v>
+        <v>섀도 영역의 잉크 사용량</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Position along path</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B294" t="str">
-        <v>경로상 위치</v>
+        <v>의도적으로 어둡게 고정한 하나의 명도에서 a*b* 평면을 가로지르는 네 개의 직선 경로를 선택한 B2A 테이블에 통과시킵니다. 모든 샘플이 같은 L*를 공유하므로 어떤 색료에 나타나는 급격한 단차나 반전은 오직 색상과 크로마 처리에서 비롯됩니다 — 섀도 영역 색역 매핑 아티팩트의 특징입니다.</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Path</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B295" t="str">
-        <v>경로</v>
+        <v>섀도 영역의 잉크 사용량은 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Cyan</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B296" t="str">
-        <v>시안</v>
+        <v>L* 고정 평면</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Magenta</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B297" t="str">
-        <v>마젠타</v>
+        <v>흑색점 보정 기준</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Yellow</v>
+        <v>Position along path</v>
       </c>
       <c r="B298" t="str">
-        <v>옐로</v>
+        <v>경로상 위치</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Red</v>
+        <v>Path</v>
       </c>
       <c r="B299" t="str">
-        <v>레드</v>
+        <v>경로</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Green</v>
+        <v>Cyan</v>
       </c>
       <c r="B300" t="str">
-        <v>그린</v>
+        <v>시안</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Blue</v>
+        <v>Magenta</v>
       </c>
       <c r="B301" t="str">
-        <v>블루</v>
+        <v>마젠타</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Black</v>
+        <v>Yellow</v>
       </c>
       <c r="B302" t="str">
-        <v>블랙</v>
+        <v>옐로</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Perceptual</v>
+        <v>Red</v>
       </c>
       <c r="B303" t="str">
-        <v>지각적</v>
+        <v>레드</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Green</v>
       </c>
       <c r="B304" t="str">
-        <v>상대 색도</v>
+        <v>그린</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Saturation</v>
+        <v>Blue</v>
       </c>
       <c r="B305" t="str">
-        <v>채도</v>
+        <v>블루</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Black</v>
       </c>
       <c r="B306" t="str">
-        <v>절대 색도</v>
+        <v>블랙</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Profile Statistics</v>
+        <v>Perceptual</v>
       </c>
       <c r="B307" t="str">
-        <v>프로파일 통계</v>
+        <v>지각적</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B308" t="str">
-        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
+        <v>상대 색도</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B309" t="str">
-        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
+        <v>채도</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Rendering intent</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B310" t="str">
-        <v>렌더링 의도</v>
+        <v>절대 색도</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B311" t="str">
-        <v>색역 부피 (ΔE³)</v>
+        <v>프로파일 통계</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B312" t="str">
-        <v>왕복 ΔE</v>
+        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B313" t="str">
-        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
+        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>mean</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B314" t="str">
-        <v>평균</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>P90</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B315" t="str">
-        <v>P90</v>
+        <v>색역 부피 (ΔE³)</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>max</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B316" t="str">
-        <v>최대</v>
+        <v>왕복 ΔE</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Analysing…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B317" t="str">
-        <v>분석 중…</v>
+        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Analysis</v>
+        <v>mean</v>
       </c>
       <c r="B318" t="str">
-        <v>분석</v>
+        <v>평균</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>P90</v>
       </c>
       <c r="B319" t="str">
-        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Plot</v>
+        <v>max</v>
       </c>
       <c r="B320" t="str">
-        <v>플롯</v>
+        <v>최대</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Raw Output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B321" t="str">
-        <v>원시 출력</v>
+        <v>분석 중…</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>XML</v>
+        <v>Analysis</v>
       </c>
       <c r="B322" t="str">
-        <v>XML</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>JSON</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B323" t="str">
-        <v>JSON</v>
+        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Curves</v>
+        <v>Plot</v>
       </c>
       <c r="B324" t="str">
-        <v>곡선</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Input curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B325" t="str">
-        <v>입력 곡선</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Output curves</v>
+        <v>XML</v>
       </c>
       <c r="B326" t="str">
-        <v>출력 곡선</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>CLUT image</v>
+        <v>JSON</v>
       </c>
       <c r="B327" t="str">
-        <v>CLUT 이미지</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Gamut image</v>
+        <v>Curves</v>
       </c>
       <c r="B328" t="str">
-        <v>색역 이미지</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Chromaticity</v>
+        <v>Input curves</v>
       </c>
       <c r="B329" t="str">
-        <v>색도</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Scatter plot</v>
+        <v>Output curves</v>
       </c>
       <c r="B330" t="str">
-        <v>산점도</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Tone response curve</v>
+        <v>CLUT image</v>
       </c>
       <c r="B331" t="str">
-        <v>톤 응답 곡선</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Curve table</v>
+        <v>Gamut image</v>
       </c>
       <c r="B332" t="str">
-        <v>곡선 표</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Tables</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B333" t="str">
-        <v>표</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Data</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B334" t="str">
-        <v>데이터</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Evaluate</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B335" t="str">
-        <v>평가</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Loading…</v>
+        <v>Curve table</v>
       </c>
       <c r="B336" t="str">
-        <v>불러오는 중…</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Input</v>
+        <v>Tables</v>
       </c>
       <c r="B337" t="str">
-        <v>입력</v>
+        <v>표</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Output</v>
+        <v>Data</v>
       </c>
       <c r="B338" t="str">
-        <v>출력</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Floating point</v>
+        <v>Evaluate</v>
       </c>
       <c r="B339" t="str">
-        <v>부동 소수점</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Grid point</v>
+        <v>Loading…</v>
       </c>
       <c r="B340" t="str">
-        <v>격자점</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Normalized</v>
+        <v>Input</v>
       </c>
       <c r="B341" t="str">
-        <v>정규화</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Human</v>
+        <v>Output</v>
       </c>
       <c r="B342" t="str">
-        <v>사람용</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Device → PCS</v>
+        <v>Floating point</v>
       </c>
       <c r="B343" t="str">
-        <v>장치 → PCS</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>PCS → Device</v>
+        <v>Grid point</v>
       </c>
       <c r="B344" t="str">
-        <v>PCS → 장치</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>No CLUT grid</v>
+        <v>Normalized</v>
       </c>
       <c r="B345" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Loading…</v>
+        <v>Human</v>
       </c>
       <c r="B346" t="str">
-        <v>불러오는 중…</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B347" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Invalid profile URL:</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B348" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B349" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Loading…</v>
       </c>
       <c r="B350" t="str">
-        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B351" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B352" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B353" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Security</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B354" t="str">
-        <v>보안</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Conformance</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B355" t="str">
-        <v>적합성</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Quality</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B356" t="str">
-        <v>품질</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>REPORT</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B357" t="str">
-        <v>보고서</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>FAIL</v>
+        <v>Security</v>
       </c>
       <c r="B358" t="str">
-        <v>실패</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>checks</v>
+        <v>Conformance</v>
       </c>
       <c r="B359" t="str">
-        <v>개 검사</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Quality</v>
       </c>
       <c r="B360" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B361" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B362" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B363" t="str">
-        <v>{lib} 기반</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B364" t="str">
-        <v>구독</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B365" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B366" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B367" t="str">
-        <v>닫기</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B368" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B369" t="str">
-        <v>이메일 주소</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B370" t="str">
-        <v>you@example.com</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B371" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B372" t="str">
-        <v>(선택)</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B373" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B374" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B375" t="str">
-        <v>취소</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B376" t="str">
-        <v>구독</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B377" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B378" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B379" t="str">
-        <v>닫기</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B380" t="str">
-        <v>개인정보 처리방침</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B381" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B382" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B383" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B384" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B385" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B386" t="str">
-        <v>오류:</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B387" t="str">
-        <v>XML로 변환</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B388" t="str">
-        <v>JSON으로 변환</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B389" t="str">
-        <v>ICC로 변환</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B390" t="str">
-        <v>XML로 변환 중…</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B391" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B392" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B393" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B394" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B395" t="str">
-        <v>프로파일 ID</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B396" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B397" t="str">
-        <v>태그 이름</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B398" t="str">
-        <v>ID</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B399" t="str">
-        <v>오프셋</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B400" t="str">
-        <v>크기</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B401" t="str">
-        <v>패딩</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B402" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B403" t="str">
-        <v>유형</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B404" t="str">
-        <v>{type} 배열</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B405" t="str">
-        <v>(내용 없음)</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B406" t="str">
-        <v>바이트</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B407" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B408" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B409" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B410" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B411" t="str">
-        <v>검증 출력 없음</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B412" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B413" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B414" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B415" t="str">
-        <v>심각한 검증 오류</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B416" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B417" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B418" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B419" t="str">
-        <v>유효</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B420" t="str">
-        <v>경고</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B421" t="str">
-        <v>오류</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B422" t="str">
-        <v>알 수 없음</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B423" t="str">
-        <v>통과</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B424" t="str">
-        <v>실패</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B425" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B426" t="str">
-        <v>검증 세부 정보</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B427" t="str">
-        <v>트리거 항목</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B428" t="str">
-        <v>항목</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B429" t="str">
-        <v>현재 값</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B430" t="str">
-        <v>필수: 0</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B431" t="str">
-        <v>예상: {value}</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B432" t="str">
-        <v>잘못됨</v>
+        <v>항목</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B433" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>현재 값</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B434" t="str">
-        <v>닫기</v>
+        <v>필수: 0</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B435" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>예상: {value}</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B436" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>잘못됨</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B437" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B438" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B439" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>XML 편집기 로드 중…</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B440" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>JSON 편집기 로드 중…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B441" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B442" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B443" t="str">
-        <v>들여쓰기</v>
+        <v>● 저장되지 않은 XML 편집</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B444" t="str">
-        <v>키 정렬</v>
+        <v>● 저장되지 않은 JSON 편집</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B445" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B446" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B447" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B448" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B445" t="str">
+      <c r="B449" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B445"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B449"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Ko.xlsx
+++ b/translations/Eng-Ko.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B449"/>
+  <dimension ref="A1:B466"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -2803,1207 +2803,1343 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Cyan</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B300" t="str">
-        <v>시안</v>
+        <v>중성축을 지나는 원색 잉킹 경로</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Magenta</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B301" t="str">
-        <v>마젠타</v>
+        <v>색역 내의 세 경로 — 사이언→레드, 마젠타→그린, 옐로→블루 — 각각 양 끝점 명도의 중간에서 중성축을 지나 선택한 B2A 테이블을 통과합니다. 모든 샘플이 색역 안에 있으므로, 섀도 경로와 달리 착색제의 급격한 단차나 반전은 색역 매핑 아티팩트가 아니라 CLUT 평활도 결함입니다.</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Yellow</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B302" t="str">
-        <v>옐로</v>
+        <v>원색 잉킹 경로는 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Red</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B303" t="str">
-        <v>레드</v>
+        <v>경로상의 위치(중간이 중성)</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Green</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B304" t="str">
-        <v>그린</v>
+        <v>이 인텐트에 검은점 보정을 적용했습니다.</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Blue</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B305" t="str">
-        <v>블루</v>
+        <v>잉크 사용량 통계</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Black</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B306" t="str">
-        <v>블랙</v>
+        <v>프로파일이 각 착색제를 얼마나 사용하는지 합계와 전체 대비 비율로 표시 — 분판의 잉크 소비 특성입니다.</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Perceptual</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B307" t="str">
-        <v>지각적</v>
+        <v>잉크 사용량 통계는 출력(프린터) 프로파일에서만 사용할 수 있습니다.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B308" t="str">
-        <v>상대 색도</v>
+        <v>중성축</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Saturation</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B309" t="str">
-        <v>채도</v>
+        <v>평균 커버리지</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Share of ink</v>
       </c>
       <c r="B310" t="str">
-        <v>절대 색도</v>
+        <v>잉크 비율</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Profile Statistics</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B311" t="str">
-        <v>프로파일 통계</v>
+        <v>잉크 비율은 중성 구성의 지문입니다 — 각 착색제가 사용된 전체 잉크에서 차지하는 비율로, 샘플 수와 무관합니다.</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B312" t="str">
-        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
+        <v>색역 내 점</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B313" t="str">
-        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
+        <v>색역 내 모든 색상에 대한 잉크 사용량은 B2A 방향 색역 경계가 필요하지만 아직 구축되지 않았습니다 — 대기 중.</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Rendering intent</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B314" t="str">
-        <v>렌더링 의도</v>
+        <v>요약할 착색제 데이터가 없습니다.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B315" t="str">
-        <v>색역 부피 (ΔE³)</v>
+        <v>아래에서 B2A(PCS→장치) 테이블을 선택하면 각 착색제의 회색조 잉크 커버리지 이미지도 표시됩니다.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B316" t="str">
-        <v>왕복 ΔE</v>
+        <v>동일한 격자에서 각 착색제의 잉크 커버리지(어두울수록 잉크가 많음).</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Cyan</v>
       </c>
       <c r="B317" t="str">
-        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
+        <v>시안</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>mean</v>
+        <v>Magenta</v>
       </c>
       <c r="B318" t="str">
-        <v>평균</v>
+        <v>마젠타</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>P90</v>
+        <v>Yellow</v>
       </c>
       <c r="B319" t="str">
-        <v>P90</v>
+        <v>옐로</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>max</v>
+        <v>Red</v>
       </c>
       <c r="B320" t="str">
-        <v>최대</v>
+        <v>레드</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Analysing…</v>
+        <v>Green</v>
       </c>
       <c r="B321" t="str">
-        <v>분석 중…</v>
+        <v>그린</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Analysis</v>
+        <v>Blue</v>
       </c>
       <c r="B322" t="str">
-        <v>분석</v>
+        <v>블루</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Black</v>
       </c>
       <c r="B323" t="str">
-        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
+        <v>블랙</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Plot</v>
+        <v>Perceptual</v>
       </c>
       <c r="B324" t="str">
-        <v>플롯</v>
+        <v>지각적</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Raw Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B325" t="str">
-        <v>원시 출력</v>
+        <v>상대 색도</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>XML</v>
+        <v>Saturation</v>
       </c>
       <c r="B326" t="str">
-        <v>XML</v>
+        <v>채도</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>JSON</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B327" t="str">
-        <v>JSON</v>
+        <v>절대 색도</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Curves</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B328" t="str">
-        <v>곡선</v>
+        <v>프로파일 통계</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Input curves</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B329" t="str">
-        <v>입력 곡선</v>
+        <v>렌더링 의도별 프로파일 전체 지표: 장치→PCS 변환이 둘러싸는 색역 부피(ΔE*ab³)와 B2A 왕복 정확도 — 프로파일을 통한 Lab → 장치 → Lab 왕복의 ΔE*ab.</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Output curves</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B330" t="str">
-        <v>출력 곡선</v>
+        <v>이 프로파일에는 장치↔PCS CLUT가 없습니다 — 프로파일 통계가 적용되지 않습니다(예: 행렬/TRC 디스플레이 프로파일).</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>CLUT image</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B331" t="str">
-        <v>CLUT 이미지</v>
+        <v>렌더링 의도</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut image</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B332" t="str">
-        <v>색역 이미지</v>
+        <v>색역 부피 (ΔE³)</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Chromaticity</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B333" t="str">
-        <v>색도</v>
+        <v>왕복 ΔE</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Scatter plot</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B334" t="str">
-        <v>산점도</v>
+        <v>색역 경계가 붕괴되었거나 대부분 정의되지 않아 이 색역 부피를 신뢰할 수 없습니다.</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Tone response curve</v>
+        <v>mean</v>
       </c>
       <c r="B335" t="str">
-        <v>톤 응답 곡선</v>
+        <v>평균</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Curve table</v>
+        <v>P90</v>
       </c>
       <c r="B336" t="str">
-        <v>곡선 표</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Tables</v>
+        <v>max</v>
       </c>
       <c r="B337" t="str">
-        <v>표</v>
+        <v>최대</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Data</v>
+        <v>Analysing…</v>
       </c>
       <c r="B338" t="str">
-        <v>데이터</v>
+        <v>분석 중…</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Evaluate</v>
+        <v>Analysis</v>
       </c>
       <c r="B339" t="str">
-        <v>평가</v>
+        <v>분석</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Loading…</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B340" t="str">
-        <v>불러오는 중…</v>
+        <v>장치→PCS 변환에서 도출한 프로파일 전체 품질 분석.</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Input</v>
+        <v>Plot</v>
       </c>
       <c r="B341" t="str">
-        <v>입력</v>
+        <v>플롯</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Output</v>
+        <v>Raw Output</v>
       </c>
       <c r="B342" t="str">
-        <v>출력</v>
+        <v>원시 출력</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Floating point</v>
+        <v>XML</v>
       </c>
       <c r="B343" t="str">
-        <v>부동 소수점</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Grid point</v>
+        <v>JSON</v>
       </c>
       <c r="B344" t="str">
-        <v>격자점</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Normalized</v>
+        <v>Curves</v>
       </c>
       <c r="B345" t="str">
-        <v>정규화</v>
+        <v>곡선</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Human</v>
+        <v>Input curves</v>
       </c>
       <c r="B346" t="str">
-        <v>사람용</v>
+        <v>입력 곡선</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Device → PCS</v>
+        <v>Output curves</v>
       </c>
       <c r="B347" t="str">
-        <v>장치 → PCS</v>
+        <v>출력 곡선</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>PCS → Device</v>
+        <v>CLUT image</v>
       </c>
       <c r="B348" t="str">
-        <v>PCS → 장치</v>
+        <v>CLUT 이미지</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut image</v>
       </c>
       <c r="B349" t="str">
-        <v>CLUT 격자 없음</v>
+        <v>색역 이미지</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Loading…</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B350" t="str">
-        <v>불러오는 중…</v>
+        <v>색도</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B351" t="str">
-        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
+        <v>산점도</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B352" t="str">
-        <v>잘못된 프로파일 URL:</v>
+        <v>톤 응답 곡선</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curve table</v>
       </c>
       <c r="B353" t="str">
-        <v>프로파일을 가져올 수 없습니다:</v>
+        <v>곡선 표</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Tables</v>
       </c>
       <c r="B354" t="str">
-        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
+        <v>표</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Data</v>
       </c>
       <c r="B355" t="str">
-        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
+        <v>데이터</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B356" t="str">
-        <v>Profile Assessment WG 검사를 실행하는 중…</v>
+        <v>평가</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading…</v>
       </c>
       <c r="B357" t="str">
-        <v>Profile Assessment WG 보고서</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Security</v>
+        <v>Input</v>
       </c>
       <c r="B358" t="str">
-        <v>보안</v>
+        <v>입력</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Conformance</v>
+        <v>Output</v>
       </c>
       <c r="B359" t="str">
-        <v>적합성</v>
+        <v>출력</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Quality</v>
+        <v>Floating point</v>
       </c>
       <c r="B360" t="str">
-        <v>품질</v>
+        <v>부동 소수점</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>REPORT</v>
+        <v>Grid point</v>
       </c>
       <c r="B361" t="str">
-        <v>보고서</v>
+        <v>격자점</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>FAIL</v>
+        <v>Normalized</v>
       </c>
       <c r="B362" t="str">
-        <v>실패</v>
+        <v>정규화</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>checks</v>
+        <v>Human</v>
       </c>
       <c r="B363" t="str">
-        <v>개 검사</v>
+        <v>사람용</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B364" t="str">
-        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
+        <v>장치 → PCS</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B365" t="str">
-        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
+        <v>PCS → 장치</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ICC Profile Tool</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B366" t="str">
-        <v>ICC 프로파일 도구</v>
+        <v>CLUT 격자 없음</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Powered by {lib}</v>
+        <v>Loading…</v>
       </c>
       <c r="B367" t="str">
-        <v>{lib} 기반</v>
+        <v>불러오는 중…</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Subscribe</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B368" t="str">
-        <v>구독</v>
+        <v>중립 = 색역 내 · 빨강 = 색역 외</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B369" t="str">
-        <v>profiletool 새 릴리스 알림 받기</v>
+        <v>잘못된 프로파일 URL:</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Get notified about new releases</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B370" t="str">
-        <v>새 릴리스 알림 받기</v>
+        <v>프로파일을 가져올 수 없습니다:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Close</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B371" t="str">
-        <v>닫기</v>
+        <v>이 외부 사이트에서 ICC 프로파일을 불러올까요?</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B372" t="str">
-        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
+        <v>Profile Assessment WG 보고서를 불러오는 중…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Email address</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B373" t="str">
-        <v>이메일 주소</v>
+        <v>Profile Assessment WG 검사를 실행하는 중…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>you@example.com</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B374" t="str">
-        <v>you@example.com</v>
+        <v>Profile Assessment WG 보고서</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Security</v>
       </c>
       <c r="B375" t="str">
-        <v>profiletool을 어떻게 사용하실 건가요?</v>
+        <v>보안</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>(optional)</v>
+        <v>Conformance</v>
       </c>
       <c r="B376" t="str">
-        <v>(선택)</v>
+        <v>적합성</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Quality</v>
       </c>
       <c r="B377" t="str">
-        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
+        <v>품질</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B378" t="str">
-        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
+        <v>보고서</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B379" t="str">
-        <v>취소</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B380" t="str">
-        <v>구독</v>
+        <v>개 검사</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B381" t="str">
-        <v>감사합니다 — 곧 연락드리겠습니다.</v>
+        <v>iccPawgReport (iccDEV)로 생성됨 · ICC Profile Assessment Working Group 점검표.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B382" t="str">
-        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
+        <v>ICC 프로파일 도구 · IccProfLib 기반</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B383" t="str">
-        <v>닫기</v>
+        <v>ICC 프로파일 도구</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B384" t="str">
-        <v>개인정보 처리방침</v>
+        <v>{lib} 기반</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B385" t="str">
-        <v>유효한 이메일 주소를 입력하세요.</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B386" t="str">
-        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
+        <v>profiletool 새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B387" t="str">
-        <v>양식을 확인하고 다시 시도하세요.</v>
+        <v>새 릴리스 알림 받기</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B388" t="str">
-        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B389" t="str">
-        <v>네트워크 오류입니다. 다시 시도하세요.</v>
+        <v>profiletool의 주요 또는 부수 릴리스가 출시되면 이메일로 알려드립니다. 패치 릴리스는 제외됩니다. 주소는 추가 전에 수동으로 검토됩니다.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B390" t="str">
-        <v>오류:</v>
+        <v>이메일 주소</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B391" t="str">
-        <v>XML로 변환</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B392" t="str">
-        <v>JSON으로 변환</v>
+        <v>profiletool을 어떻게 사용하실 건가요?</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B393" t="str">
-        <v>ICC로 변환</v>
+        <v>(선택)</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B394" t="str">
-        <v>XML로 변환 중…</v>
+        <v>예: 인쇄 보정용 ICC 프로파일 평가</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B395" t="str">
-        <v>JSON으로 변환 중…</v>
+        <v>profiletool 릴리스에 대한 이메일 수신에 동의합니다. 언제든지 구독을 취소할 수 있습니다.</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B396" t="str">
-        <v>ICC로 변환 중…</v>
+        <v>취소</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B397" t="str">
-        <v>ICC 프로파일 로드</v>
+        <v>구독</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B398" t="str">
-        <v>ICC 프로파일 파일용 드롭 영역</v>
+        <v>감사합니다 — 곧 연락드리겠습니다.</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B399" t="str">
-        <v>프로파일 ID</v>
+        <v>승인되면 환영 이메일을 받게 됩니다. 이후에는 profiletool 새 릴리스가 출시될 때만 알림을 받게 됩니다.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>태그를 찾을 수 없습니다.</v>
+        <v>닫기</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B401" t="str">
-        <v>태그 이름</v>
+        <v>개인정보 처리방침</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B402" t="str">
-        <v>ID</v>
+        <v>유효한 이메일 주소를 입력하세요.</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B403" t="str">
-        <v>오프셋</v>
+        <v>요청이 너무 많습니다. 나중에 다시 시도하세요.</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B404" t="str">
-        <v>크기</v>
+        <v>양식을 확인하고 다시 시도하세요.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>패딩</v>
+        <v>요청을 보낼 수 없습니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>로드 이후 바이트가 변경됨</v>
+        <v>네트워크 오류입니다. 다시 시도하세요.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B407" t="str">
-        <v>유형</v>
+        <v>오류:</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B408" t="str">
-        <v>{type} 배열</v>
+        <v>XML로 변환</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B409" t="str">
-        <v>(내용 없음)</v>
+        <v>JSON으로 변환</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B410" t="str">
-        <v>바이트</v>
+        <v>ICC로 변환</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B411" t="str">
-        <v>전체 설명을 로드하는 중…</v>
+        <v>XML로 변환 중…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B412" t="str">
-        <v>전체 설명을 로드할 수 없습니다:</v>
+        <v>JSON으로 변환 중…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B413" t="str">
-        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
+        <v>ICC로 변환 중…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B414" t="str">
-        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
+        <v>ICC 프로파일 로드</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B415" t="str">
-        <v>검증 출력 없음</v>
+        <v>ICC 프로파일 파일용 드롭 영역</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B416" t="str">
-        <v>프로파일이 유효합니다</v>
+        <v>프로파일 ID</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B417" t="str">
-        <v>프로파일에 경고가 있습니다</v>
+        <v>태그를 찾을 수 없습니다.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B418" t="str">
-        <v>프로파일이 규격을 준수하지 않습니다</v>
+        <v>태그 이름</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B419" t="str">
-        <v>심각한 검증 오류</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B420" t="str">
-        <v>알 수 없는 검증 상태</v>
+        <v>오프셋</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B421" t="str">
-        <v>심각 — 검사용으로만 표시</v>
+        <v>크기</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B422" t="str">
-        <v>경고나 오류를 찾지 못했습니다.</v>
+        <v>패딩</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B423" t="str">
-        <v>유효</v>
+        <v>로드 이후 바이트가 변경됨</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B424" t="str">
-        <v>경고</v>
+        <v>유형</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B425" t="str">
-        <v>오류</v>
+        <v>{type} 배열</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B426" t="str">
-        <v>알 수 없음</v>
+        <v>(내용 없음)</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B427" t="str">
-        <v>통과</v>
+        <v>바이트</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B428" t="str">
-        <v>실패</v>
+        <v>전체 설명을 로드하는 중…</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B429" t="str">
-        <v>컨텍스트에서 보기</v>
+        <v>전체 설명을 로드할 수 없습니다:</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B430" t="str">
-        <v>검증 세부 정보</v>
+        <v>이 프로파일은 완전히 분석할 수 없으며 적용해서는 안 됩니다. 아래의 헤더와 태그 디렉터리는 검사용으로만 표시됩니다.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B431" t="str">
-        <v>트리거 항목</v>
+        <v>태그 내용을 사용할 수 없음 — 프로파일을 완전히 분석할 수 없습니다.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B432" t="str">
-        <v>항목</v>
+        <v>검증 출력 없음</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B433" t="str">
-        <v>현재 값</v>
+        <v>프로파일이 유효합니다</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B434" t="str">
-        <v>필수: 0</v>
+        <v>프로파일에 경고가 있습니다</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B435" t="str">
-        <v>예상: {value}</v>
+        <v>프로파일이 규격을 준수하지 않습니다</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B436" t="str">
-        <v>잘못됨</v>
+        <v>심각한 검증 오류</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B437" t="str">
-        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+        <v>알 수 없는 검증 상태</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B438" t="str">
-        <v>닫기</v>
+        <v>심각 — 검사용으로만 표시</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B439" t="str">
-        <v>XML 편집기 로드 중…</v>
+        <v>경고나 오류를 찾지 못했습니다.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B440" t="str">
-        <v>JSON 편집기 로드 중…</v>
+        <v>유효</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B441" t="str">
-        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>경고</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B442" t="str">
-        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+        <v>오류</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B443" t="str">
-        <v>● 저장되지 않은 XML 편집</v>
+        <v>알 수 없음</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B444" t="str">
-        <v>● 저장되지 않은 JSON 편집</v>
+        <v>통과</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B445" t="str">
-        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+        <v>실패</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B446" t="str">
-        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+        <v>컨텍스트에서 보기</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B447" t="str">
-        <v>들여쓰기</v>
+        <v>검증 세부 정보</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B448" t="str">
-        <v>키 정렬</v>
+        <v>트리거 항목</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B449" t="str">
+        <v>항목</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B450" t="str">
+        <v>현재 값</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B451" t="str">
+        <v>필수: 0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B452" t="str">
+        <v>예상: {value}</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B453" t="str">
+        <v>잘못됨</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B454" t="str">
+        <v>이 결과를 특정 항목에 연결할 수 없습니다.</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B455" t="str">
+        <v>닫기</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B456" t="str">
+        <v>XML 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B457" t="str">
+        <v>JSON 편집기 로드 중…</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B458" t="str">
+        <v>저장되지 않은 XML 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B459" t="str">
+        <v>저장되지 않은 JSON 편집이 있습니다. ICC 프로파일에서 새로 변환하여 덮어쓸까요?</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B460" t="str">
+        <v>● 저장되지 않은 XML 편집</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B461" t="str">
+        <v>● 저장되지 않은 JSON 편집</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B462" t="str">
+        <v>&lt;em&gt;XML로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 XML 표현을 생성하세요. XML은 상위 &lt;code&gt;IccToXml&lt;/code&gt; 도구와 동일한 IccLibXML 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B463" t="str">
+        <v>&lt;em&gt;JSON으로 변환&lt;/em&gt;을 클릭하여 이 프로파일의 편집 가능한 JSON 표현을 생성하세요. JSON은 상위 &lt;code&gt;IccToJson&lt;/code&gt; 도구와 동일한 IccLibJSON 코드 경로로 생성됩니다.</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B464" t="str">
+        <v>들여쓰기</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B465" t="str">
+        <v>키 정렬</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B449" t="str">
+      <c r="B466" t="str">
         <v>편집 내용으로 프로파일을 작성했지만 재검증에 실패했습니다:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B449"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
   </ignoredErrors>
 </worksheet>
 </file>